--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
@@ -9,19 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2670" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2670" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Testmatrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="3" r:id="rId2"/>
-    <sheet name="Rollen" sheetId="2" r:id="rId3"/>
+    <sheet name="Rollen" sheetId="2" r:id="rId2"/>
+    <sheet name="Tabelle2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11450" uniqueCount="1961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11460" uniqueCount="1971">
   <si>
     <t>ID</t>
   </si>
@@ -7164,6 +7164,36 @@
   </si>
   <si>
     <t xml:space="preserve">Activity Feed nicht mehr in feed seite angezeigt wird sonder bei der Einstellungen </t>
+  </si>
+  <si>
+    <t>Wenn ich versuche verein zu bearbeiten und auf speichern klicke bekomme ich error 404 Not Found</t>
+  </si>
+  <si>
+    <t>wenn ich auf Vereine &amp; Teams seite bin soll ich dort auch die möglichkeit Daten zu Bearbeiten von Verein</t>
+  </si>
+  <si>
+    <t>die seite von Verein/Teams soll Benutzerfreundlicher werden besonders mit Ehrenamt &amp;Berufe auch besser responsive</t>
+  </si>
+  <si>
+    <t>wenn ich teams/vereine bearbeite und auf speichern klicke soll ich error or success rückmeldung bekommen</t>
+  </si>
+  <si>
+    <t>wenn ich auf usercard klicke wird es angezeigt aber wenn ich außerhalb klicke bleibt es trotzdem angezeigt, es soll geschlossen werdeb</t>
+  </si>
+  <si>
+    <t>eintrag erst angezeigt wird wenn der entsprechende permissions überhaupt für die Person aktiv ist in dem Fall club.jobs.manage</t>
+  </si>
+  <si>
+    <t>ich will auch auch für doe guäste wenn die auf jobsseite sind dass die die möglichkeit haben sich zu bewerben wenn die auf Interesse melden klicken, mann mus nicht extra angemeldet sein, bei der Anmeldungsfall werden die daten irgendwie aufgenommen</t>
+  </si>
+  <si>
+    <t>wenn man auf guastseite ist bzw jobs da soll man filtern können nach sportart und adresse, das heißt auch dass formular darauf angepasst werden soll</t>
+  </si>
+  <si>
+    <t>bei der erstellen von Jobs wird nach ljnk gefragt, wovür dient der lienk er wird danach die Gäste nicht angezeigt</t>
+  </si>
+  <si>
+    <t>ich habe ein problem wie wie wissen die jobs werden durch modal ertsellt, wenn da ein Fehermeldung ensteht wird es hinter modal angezeigt sodas man e snicht lesen kann behebe das Problem</t>
   </si>
 </sst>
 </file>
@@ -7238,7 +7268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7268,6 +7298,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7589,394 +7622,394 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="11" customFormat="1" ht="75">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:18" s="12" customFormat="1" ht="75">
+      <c r="A2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="15">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="L2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="14" t="s">
         <v>1800</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="16">
         <v>46146.75</v>
       </c>
-      <c r="R2" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="11" customFormat="1" ht="75">
-      <c r="A3" s="13" t="s">
+      <c r="R2" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="12" customFormat="1" ht="75">
+      <c r="A3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="13" t="s">
+      <c r="L3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="14" t="s">
         <v>1800</v>
       </c>
-      <c r="Q3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="105">
-      <c r="A4" s="13" t="s">
+      <c r="Q3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="12" customFormat="1" ht="105">
+      <c r="A4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="14" t="s">
         <v>1800</v>
       </c>
-      <c r="Q4" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="75">
-      <c r="A5" s="13" t="s">
+      <c r="Q4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="12" customFormat="1" ht="75">
+      <c r="A5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="13" t="s">
+      <c r="L5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="75">
-      <c r="A6" s="13" t="s">
+      <c r="P5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="12" customFormat="1" ht="75">
+      <c r="A6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="13" t="s">
+      <c r="L6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="75">
-      <c r="A7" s="13" t="s">
+      <c r="P6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="12" customFormat="1" ht="75">
+      <c r="A7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="13" t="s">
+      <c r="L7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="N7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P7" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" s="11" t="s">
+      <c r="P7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7984,8 +8017,8 @@
       <c r="A8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="16">
-        <v>0</v>
+      <c r="B8" s="17">
+        <v>1</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>19</v>
@@ -8040,8 +8073,8 @@
       <c r="A9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="16">
-        <v>0</v>
+      <c r="B9" s="17">
+        <v>1</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>19</v>
@@ -8096,8 +8129,8 @@
       <c r="A10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="16">
-        <v>0</v>
+      <c r="B10" s="17">
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>19</v>
@@ -8152,7 +8185,7 @@
       <c r="A11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="17">
         <v>0</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -8208,7 +8241,7 @@
       <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <v>0</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -8264,7 +8297,7 @@
       <c r="A13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="17">
         <v>0</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -8320,7 +8353,7 @@
       <c r="A14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <v>0</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -8376,7 +8409,7 @@
       <c r="A15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="17">
         <v>0</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -8432,7 +8465,7 @@
       <c r="A16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <v>0</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -8488,7 +8521,7 @@
       <c r="A17" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>0</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -8544,7 +8577,7 @@
       <c r="A18" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <v>0</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -8600,7 +8633,7 @@
       <c r="A19" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="17">
         <v>0</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -8656,7 +8689,7 @@
       <c r="A20" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <v>0</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -8712,7 +8745,7 @@
       <c r="A21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>0</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -8768,7 +8801,7 @@
       <c r="A22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>0</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -8824,7 +8857,7 @@
       <c r="A23" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="17">
         <v>0</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -8880,7 +8913,7 @@
       <c r="A24" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <v>0</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -8936,7 +8969,7 @@
       <c r="A25" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>0</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -8992,7 +9025,7 @@
       <c r="A26" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>0</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -9048,7 +9081,7 @@
       <c r="A27" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>0</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -9104,7 +9137,7 @@
       <c r="A28" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>0</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -9160,7 +9193,7 @@
       <c r="A29" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>0</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -9216,7 +9249,7 @@
       <c r="A30" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>0</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -9272,7 +9305,7 @@
       <c r="A31" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>0</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -9328,7 +9361,7 @@
       <c r="A32" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>0</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -9384,7 +9417,7 @@
       <c r="A33" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>0</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -9440,7 +9473,7 @@
       <c r="A34" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>0</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -9496,7 +9529,7 @@
       <c r="A35" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="17">
         <v>0</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -9552,7 +9585,7 @@
       <c r="A36" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>0</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -9608,7 +9641,7 @@
       <c r="A37" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>0</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -9664,7 +9697,7 @@
       <c r="A38" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="17">
         <v>0</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -9720,7 +9753,7 @@
       <c r="A39" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>0</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -9776,7 +9809,7 @@
       <c r="A40" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="17">
         <v>0</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -9832,7 +9865,7 @@
       <c r="A41" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>0</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -9888,7 +9921,7 @@
       <c r="A42" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>0</v>
       </c>
       <c r="C42" s="8" t="s">
@@ -9944,7 +9977,7 @@
       <c r="A43" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="17">
         <v>0</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -10000,7 +10033,7 @@
       <c r="A44" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <v>0</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -10056,7 +10089,7 @@
       <c r="A45" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="17">
         <v>0</v>
       </c>
       <c r="C45" s="8" t="s">
@@ -10112,7 +10145,7 @@
       <c r="A46" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="17">
         <v>0</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -10168,7 +10201,7 @@
       <c r="A47" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="17">
         <v>0</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -10224,7 +10257,7 @@
       <c r="A48" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <v>0</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -10280,7 +10313,7 @@
       <c r="A49" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="17">
         <v>0</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -10336,7 +10369,7 @@
       <c r="A50" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="17">
         <v>0</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -10392,7 +10425,7 @@
       <c r="A51" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="17">
         <v>0</v>
       </c>
       <c r="C51" s="8" t="s">
@@ -10448,7 +10481,7 @@
       <c r="A52" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="17">
         <v>0</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -10504,7 +10537,7 @@
       <c r="A53" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <v>0</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -10560,7 +10593,7 @@
       <c r="A54" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="17">
         <v>0</v>
       </c>
       <c r="C54" s="8" t="s">
@@ -10616,7 +10649,7 @@
       <c r="A55" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="17">
         <v>0</v>
       </c>
       <c r="C55" s="8" t="s">
@@ -10672,7 +10705,7 @@
       <c r="A56" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="17">
         <v>0</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -10728,7 +10761,7 @@
       <c r="A57" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="17">
         <v>0</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -10784,7 +10817,7 @@
       <c r="A58" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="17">
         <v>0</v>
       </c>
       <c r="C58" s="8" t="s">
@@ -10840,7 +10873,7 @@
       <c r="A59" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="17">
         <v>0</v>
       </c>
       <c r="C59" s="8" t="s">
@@ -10896,7 +10929,7 @@
       <c r="A60" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="17">
         <v>0</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -10952,7 +10985,7 @@
       <c r="A61" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <v>0</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -11008,7 +11041,7 @@
       <c r="A62" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="17">
         <v>0</v>
       </c>
       <c r="C62" s="8" t="s">
@@ -11064,7 +11097,7 @@
       <c r="A63" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <v>0</v>
       </c>
       <c r="C63" s="8" t="s">
@@ -11120,7 +11153,7 @@
       <c r="A64" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="17">
         <v>0</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -11176,7 +11209,7 @@
       <c r="A65" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="17">
         <v>0</v>
       </c>
       <c r="C65" s="8" t="s">
@@ -11232,7 +11265,7 @@
       <c r="A66" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="17">
         <v>0</v>
       </c>
       <c r="C66" s="8" t="s">
@@ -11288,7 +11321,7 @@
       <c r="A67" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="17">
         <v>0</v>
       </c>
       <c r="C67" s="8" t="s">
@@ -11344,7 +11377,7 @@
       <c r="A68" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="17">
         <v>0</v>
       </c>
       <c r="C68" s="8" t="s">
@@ -11400,7 +11433,7 @@
       <c r="A69" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="17">
         <v>0</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -11456,7 +11489,7 @@
       <c r="A70" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="17">
         <v>0</v>
       </c>
       <c r="C70" s="8" t="s">
@@ -11512,7 +11545,7 @@
       <c r="A71" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <v>0</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -11568,7 +11601,7 @@
       <c r="A72" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <v>0</v>
       </c>
       <c r="C72" s="8" t="s">
@@ -11624,7 +11657,7 @@
       <c r="A73" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="17">
         <v>0</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -11680,7 +11713,7 @@
       <c r="A74" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="17">
         <v>0</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -11736,7 +11769,7 @@
       <c r="A75" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="17">
         <v>0</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -11792,7 +11825,7 @@
       <c r="A76" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="17">
         <v>0</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -11848,7 +11881,7 @@
       <c r="A77" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="17">
         <v>0</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -11904,7 +11937,7 @@
       <c r="A78" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="17">
         <v>0</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -11960,7 +11993,7 @@
       <c r="A79" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="17">
         <v>0</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -12016,7 +12049,7 @@
       <c r="A80" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="17">
         <v>0</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -12072,7 +12105,7 @@
       <c r="A81" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <v>0</v>
       </c>
       <c r="C81" s="8" t="s">
@@ -12128,7 +12161,7 @@
       <c r="A82" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="17">
         <v>0</v>
       </c>
       <c r="C82" s="8" t="s">
@@ -12184,7 +12217,7 @@
       <c r="A83" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="17">
         <v>0</v>
       </c>
       <c r="C83" s="8" t="s">
@@ -12240,7 +12273,7 @@
       <c r="A84" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="17">
         <v>0</v>
       </c>
       <c r="C84" s="8" t="s">
@@ -12296,7 +12329,7 @@
       <c r="A85" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="17">
         <v>0</v>
       </c>
       <c r="C85" s="8" t="s">
@@ -12352,7 +12385,7 @@
       <c r="A86" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="17">
         <v>0</v>
       </c>
       <c r="C86" s="8" t="s">
@@ -12408,7 +12441,7 @@
       <c r="A87" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="17">
         <v>0</v>
       </c>
       <c r="C87" s="8" t="s">
@@ -12464,7 +12497,7 @@
       <c r="A88" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B88" s="16">
+      <c r="B88" s="17">
         <v>0</v>
       </c>
       <c r="C88" s="8" t="s">
@@ -12520,7 +12553,7 @@
       <c r="A89" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="B89" s="16">
+      <c r="B89" s="17">
         <v>0</v>
       </c>
       <c r="C89" s="8" t="s">
@@ -12576,7 +12609,7 @@
       <c r="A90" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <v>0</v>
       </c>
       <c r="C90" s="8" t="s">
@@ -12632,7 +12665,7 @@
       <c r="A91" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B91" s="17">
         <v>0</v>
       </c>
       <c r="C91" s="8" t="s">
@@ -12688,7 +12721,7 @@
       <c r="A92" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B92" s="17">
         <v>0</v>
       </c>
       <c r="C92" s="8" t="s">
@@ -12744,7 +12777,7 @@
       <c r="A93" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="17">
         <v>0</v>
       </c>
       <c r="C93" s="8" t="s">
@@ -12800,7 +12833,7 @@
       <c r="A94" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B94" s="17">
         <v>0</v>
       </c>
       <c r="C94" s="8" t="s">
@@ -12856,7 +12889,7 @@
       <c r="A95" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B95" s="17">
         <v>0</v>
       </c>
       <c r="C95" s="8" t="s">
@@ -12912,7 +12945,7 @@
       <c r="A96" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B96" s="17">
         <v>0</v>
       </c>
       <c r="C96" s="8" t="s">
@@ -12968,7 +13001,7 @@
       <c r="A97" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B97" s="17">
         <v>0</v>
       </c>
       <c r="C97" s="8" t="s">
@@ -13024,7 +13057,7 @@
       <c r="A98" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B98" s="17">
         <v>0</v>
       </c>
       <c r="C98" s="8" t="s">
@@ -13080,7 +13113,7 @@
       <c r="A99" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <v>0</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -13136,7 +13169,7 @@
       <c r="A100" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B100" s="17">
         <v>0</v>
       </c>
       <c r="C100" s="8" t="s">
@@ -13192,7 +13225,7 @@
       <c r="A101" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="17">
         <v>0</v>
       </c>
       <c r="C101" s="8" t="s">
@@ -13248,7 +13281,7 @@
       <c r="A102" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B102" s="17">
         <v>0</v>
       </c>
       <c r="C102" s="8" t="s">
@@ -13304,7 +13337,7 @@
       <c r="A103" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="17">
         <v>0</v>
       </c>
       <c r="C103" s="8" t="s">
@@ -13360,7 +13393,7 @@
       <c r="A104" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B104" s="17">
         <v>0</v>
       </c>
       <c r="C104" s="8" t="s">
@@ -13416,7 +13449,7 @@
       <c r="A105" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B105" s="17">
         <v>0</v>
       </c>
       <c r="C105" s="8" t="s">
@@ -13472,7 +13505,7 @@
       <c r="A106" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B106" s="17">
         <v>0</v>
       </c>
       <c r="C106" s="8" t="s">
@@ -13528,7 +13561,7 @@
       <c r="A107" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="17">
         <v>0</v>
       </c>
       <c r="C107" s="8" t="s">
@@ -13584,7 +13617,7 @@
       <c r="A108" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="17">
         <v>0</v>
       </c>
       <c r="C108" s="8" t="s">
@@ -13640,7 +13673,7 @@
       <c r="A109" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="17">
         <v>0</v>
       </c>
       <c r="C109" s="8" t="s">
@@ -13696,7 +13729,7 @@
       <c r="A110" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="17">
         <v>0</v>
       </c>
       <c r="C110" s="8" t="s">
@@ -13752,7 +13785,7 @@
       <c r="A111" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="17">
         <v>0</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -13808,7 +13841,7 @@
       <c r="A112" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="17">
         <v>0</v>
       </c>
       <c r="C112" s="8" t="s">
@@ -13864,7 +13897,7 @@
       <c r="A113" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="17">
         <v>0</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -13920,7 +13953,7 @@
       <c r="A114" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="17">
         <v>0</v>
       </c>
       <c r="C114" s="8" t="s">
@@ -13976,7 +14009,7 @@
       <c r="A115" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <v>0</v>
       </c>
       <c r="C115" s="8" t="s">
@@ -14032,7 +14065,7 @@
       <c r="A116" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="17">
         <v>0</v>
       </c>
       <c r="C116" s="8" t="s">
@@ -14088,7 +14121,7 @@
       <c r="A117" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="17">
         <v>0</v>
       </c>
       <c r="C117" s="8" t="s">
@@ -14144,7 +14177,7 @@
       <c r="A118" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="17">
         <v>0</v>
       </c>
       <c r="C118" s="8" t="s">
@@ -14200,7 +14233,7 @@
       <c r="A119" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="17">
         <v>0</v>
       </c>
       <c r="C119" s="8" t="s">
@@ -14256,7 +14289,7 @@
       <c r="A120" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B120" s="17">
         <v>0</v>
       </c>
       <c r="C120" s="8" t="s">
@@ -14312,7 +14345,7 @@
       <c r="A121" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B121" s="17">
         <v>0</v>
       </c>
       <c r="C121" s="8" t="s">
@@ -14368,7 +14401,7 @@
       <c r="A122" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B122" s="17">
         <v>0</v>
       </c>
       <c r="C122" s="8" t="s">
@@ -14424,7 +14457,7 @@
       <c r="A123" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B123" s="16">
+      <c r="B123" s="17">
         <v>0</v>
       </c>
       <c r="C123" s="8" t="s">
@@ -14480,7 +14513,7 @@
       <c r="A124" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="B124" s="16">
+      <c r="B124" s="17">
         <v>0</v>
       </c>
       <c r="C124" s="8" t="s">
@@ -14536,7 +14569,7 @@
       <c r="A125" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="B125" s="16">
+      <c r="B125" s="17">
         <v>0</v>
       </c>
       <c r="C125" s="8" t="s">
@@ -14592,7 +14625,7 @@
       <c r="A126" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B126" s="16">
+      <c r="B126" s="17">
         <v>0</v>
       </c>
       <c r="C126" s="8" t="s">
@@ -14648,7 +14681,7 @@
       <c r="A127" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="17">
         <v>0</v>
       </c>
       <c r="C127" s="8" t="s">
@@ -14704,7 +14737,7 @@
       <c r="A128" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="17">
         <v>0</v>
       </c>
       <c r="C128" s="8" t="s">
@@ -14760,7 +14793,7 @@
       <c r="A129" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <v>0</v>
       </c>
       <c r="C129" s="8" t="s">
@@ -14816,7 +14849,7 @@
       <c r="A130" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="17">
         <v>0</v>
       </c>
       <c r="C130" s="8" t="s">
@@ -14872,7 +14905,7 @@
       <c r="A131" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="17">
         <v>0</v>
       </c>
       <c r="C131" s="8" t="s">
@@ -14928,7 +14961,7 @@
       <c r="A132" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B132" s="16">
+      <c r="B132" s="17">
         <v>0</v>
       </c>
       <c r="C132" s="8" t="s">
@@ -14984,7 +15017,7 @@
       <c r="A133" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="17">
         <v>0</v>
       </c>
       <c r="C133" s="8" t="s">
@@ -15040,7 +15073,7 @@
       <c r="A134" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="17">
         <v>0</v>
       </c>
       <c r="C134" s="8" t="s">
@@ -15096,7 +15129,7 @@
       <c r="A135" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B135" s="16">
+      <c r="B135" s="17">
         <v>0</v>
       </c>
       <c r="C135" s="8" t="s">
@@ -15152,7 +15185,7 @@
       <c r="A136" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="B136" s="16">
+      <c r="B136" s="17">
         <v>0</v>
       </c>
       <c r="C136" s="8" t="s">
@@ -15208,7 +15241,7 @@
       <c r="A137" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="17">
         <v>0</v>
       </c>
       <c r="C137" s="8" t="s">
@@ -15264,7 +15297,7 @@
       <c r="A138" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="B138" s="16">
+      <c r="B138" s="17">
         <v>0</v>
       </c>
       <c r="C138" s="8" t="s">
@@ -15320,7 +15353,7 @@
       <c r="A139" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B139" s="16">
+      <c r="B139" s="17">
         <v>0</v>
       </c>
       <c r="C139" s="8" t="s">
@@ -15376,7 +15409,7 @@
       <c r="A140" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="B140" s="16">
+      <c r="B140" s="17">
         <v>0</v>
       </c>
       <c r="C140" s="8" t="s">
@@ -15432,7 +15465,7 @@
       <c r="A141" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="B141" s="16">
+      <c r="B141" s="17">
         <v>0</v>
       </c>
       <c r="C141" s="8" t="s">
@@ -15488,7 +15521,7 @@
       <c r="A142" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <v>0</v>
       </c>
       <c r="C142" s="8" t="s">
@@ -15544,7 +15577,7 @@
       <c r="A143" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="B143" s="16">
+      <c r="B143" s="17">
         <v>0</v>
       </c>
       <c r="C143" s="8" t="s">
@@ -15600,7 +15633,7 @@
       <c r="A144" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="B144" s="16">
+      <c r="B144" s="17">
         <v>0</v>
       </c>
       <c r="C144" s="8" t="s">
@@ -15656,7 +15689,7 @@
       <c r="A145" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B145" s="16">
+      <c r="B145" s="17">
         <v>0</v>
       </c>
       <c r="C145" s="8" t="s">
@@ -15712,7 +15745,7 @@
       <c r="A146" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="17">
         <v>0</v>
       </c>
       <c r="C146" s="8" t="s">
@@ -15768,7 +15801,7 @@
       <c r="A147" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="B147" s="16">
+      <c r="B147" s="17">
         <v>0</v>
       </c>
       <c r="C147" s="8" t="s">
@@ -15824,7 +15857,7 @@
       <c r="A148" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="B148" s="16">
+      <c r="B148" s="17">
         <v>0</v>
       </c>
       <c r="C148" s="8" t="s">
@@ -15880,7 +15913,7 @@
       <c r="A149" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="B149" s="16">
+      <c r="B149" s="17">
         <v>0</v>
       </c>
       <c r="C149" s="8" t="s">
@@ -15936,7 +15969,7 @@
       <c r="A150" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B150" s="16">
+      <c r="B150" s="17">
         <v>0</v>
       </c>
       <c r="C150" s="8" t="s">
@@ -15992,7 +16025,7 @@
       <c r="A151" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="B151" s="16">
+      <c r="B151" s="17">
         <v>0</v>
       </c>
       <c r="C151" s="8" t="s">
@@ -16048,7 +16081,7 @@
       <c r="A152" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B152" s="16">
+      <c r="B152" s="17">
         <v>0</v>
       </c>
       <c r="C152" s="8" t="s">
@@ -16104,7 +16137,7 @@
       <c r="A153" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="17">
         <v>0</v>
       </c>
       <c r="C153" s="8" t="s">
@@ -16160,7 +16193,7 @@
       <c r="A154" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="B154" s="16">
+      <c r="B154" s="17">
         <v>0</v>
       </c>
       <c r="C154" s="8" t="s">
@@ -16216,7 +16249,7 @@
       <c r="A155" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <v>0</v>
       </c>
       <c r="C155" s="8" t="s">
@@ -16272,7 +16305,7 @@
       <c r="A156" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="B156" s="16">
+      <c r="B156" s="17">
         <v>0</v>
       </c>
       <c r="C156" s="8" t="s">
@@ -16328,7 +16361,7 @@
       <c r="A157" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="B157" s="16">
+      <c r="B157" s="17">
         <v>0</v>
       </c>
       <c r="C157" s="8" t="s">
@@ -16384,7 +16417,7 @@
       <c r="A158" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="B158" s="16">
+      <c r="B158" s="17">
         <v>0</v>
       </c>
       <c r="C158" s="8" t="s">
@@ -16440,7 +16473,7 @@
       <c r="A159" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="B159" s="16">
+      <c r="B159" s="17">
         <v>0</v>
       </c>
       <c r="C159" s="8" t="s">
@@ -16496,7 +16529,7 @@
       <c r="A160" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="B160" s="16">
+      <c r="B160" s="17">
         <v>0</v>
       </c>
       <c r="C160" s="8" t="s">
@@ -16552,7 +16585,7 @@
       <c r="A161" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="B161" s="16">
+      <c r="B161" s="17">
         <v>0</v>
       </c>
       <c r="C161" s="8" t="s">
@@ -16608,7 +16641,7 @@
       <c r="A162" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="B162" s="16">
+      <c r="B162" s="17">
         <v>0</v>
       </c>
       <c r="C162" s="8" t="s">
@@ -16664,7 +16697,7 @@
       <c r="A163" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="B163" s="16">
+      <c r="B163" s="17">
         <v>0</v>
       </c>
       <c r="C163" s="8" t="s">
@@ -16720,7 +16753,7 @@
       <c r="A164" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="B164" s="16">
+      <c r="B164" s="17">
         <v>0</v>
       </c>
       <c r="C164" s="8" t="s">
@@ -16776,7 +16809,7 @@
       <c r="A165" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="B165" s="16">
+      <c r="B165" s="17">
         <v>0</v>
       </c>
       <c r="C165" s="8" t="s">
@@ -16832,7 +16865,7 @@
       <c r="A166" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="B166" s="16">
+      <c r="B166" s="17">
         <v>0</v>
       </c>
       <c r="C166" s="8" t="s">
@@ -16888,7 +16921,7 @@
       <c r="A167" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="B167" s="16">
+      <c r="B167" s="17">
         <v>0</v>
       </c>
       <c r="C167" s="8" t="s">
@@ -16944,7 +16977,7 @@
       <c r="A168" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <v>0</v>
       </c>
       <c r="C168" s="8" t="s">
@@ -17000,7 +17033,7 @@
       <c r="A169" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="17">
         <v>0</v>
       </c>
       <c r="C169" s="8" t="s">
@@ -17056,7 +17089,7 @@
       <c r="A170" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="17">
         <v>0</v>
       </c>
       <c r="C170" s="8" t="s">
@@ -17112,7 +17145,7 @@
       <c r="A171" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="17">
         <v>0</v>
       </c>
       <c r="C171" s="8" t="s">
@@ -17168,7 +17201,7 @@
       <c r="A172" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="17">
         <v>0</v>
       </c>
       <c r="C172" s="8" t="s">
@@ -17224,7 +17257,7 @@
       <c r="A173" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="B173" s="16">
+      <c r="B173" s="17">
         <v>0</v>
       </c>
       <c r="C173" s="8" t="s">
@@ -17280,7 +17313,7 @@
       <c r="A174" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="B174" s="16">
+      <c r="B174" s="17">
         <v>0</v>
       </c>
       <c r="C174" s="8" t="s">
@@ -17336,7 +17369,7 @@
       <c r="A175" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="B175" s="16">
+      <c r="B175" s="17">
         <v>0</v>
       </c>
       <c r="C175" s="8" t="s">
@@ -17392,7 +17425,7 @@
       <c r="A176" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="B176" s="16">
+      <c r="B176" s="17">
         <v>0</v>
       </c>
       <c r="C176" s="8" t="s">
@@ -17448,7 +17481,7 @@
       <c r="A177" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="B177" s="16">
+      <c r="B177" s="17">
         <v>0</v>
       </c>
       <c r="C177" s="8" t="s">
@@ -17504,7 +17537,7 @@
       <c r="A178" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="B178" s="16">
+      <c r="B178" s="17">
         <v>0</v>
       </c>
       <c r="C178" s="8" t="s">
@@ -17560,7 +17593,7 @@
       <c r="A179" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="B179" s="16">
+      <c r="B179" s="17">
         <v>0</v>
       </c>
       <c r="C179" s="8" t="s">
@@ -17616,7 +17649,7 @@
       <c r="A180" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="B180" s="16">
+      <c r="B180" s="17">
         <v>0</v>
       </c>
       <c r="C180" s="8" t="s">
@@ -17672,7 +17705,7 @@
       <c r="A181" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <v>0</v>
       </c>
       <c r="C181" s="8" t="s">
@@ -17728,7 +17761,7 @@
       <c r="A182" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="B182" s="16">
+      <c r="B182" s="17">
         <v>0</v>
       </c>
       <c r="C182" s="8" t="s">
@@ -17784,7 +17817,7 @@
       <c r="A183" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="B183" s="16">
+      <c r="B183" s="17">
         <v>0</v>
       </c>
       <c r="C183" s="8" t="s">
@@ -17840,7 +17873,7 @@
       <c r="A184" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="B184" s="16">
+      <c r="B184" s="17">
         <v>0</v>
       </c>
       <c r="C184" s="8" t="s">
@@ -17896,7 +17929,7 @@
       <c r="A185" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="B185" s="16">
+      <c r="B185" s="17">
         <v>0</v>
       </c>
       <c r="C185" s="8" t="s">
@@ -17952,7 +17985,7 @@
       <c r="A186" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="B186" s="16">
+      <c r="B186" s="17">
         <v>0</v>
       </c>
       <c r="C186" s="8" t="s">
@@ -18008,7 +18041,7 @@
       <c r="A187" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="B187" s="16">
+      <c r="B187" s="17">
         <v>0</v>
       </c>
       <c r="C187" s="8" t="s">
@@ -18064,7 +18097,7 @@
       <c r="A188" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="B188" s="16">
+      <c r="B188" s="17">
         <v>0</v>
       </c>
       <c r="C188" s="8" t="s">
@@ -18120,7 +18153,7 @@
       <c r="A189" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="B189" s="16">
+      <c r="B189" s="17">
         <v>0</v>
       </c>
       <c r="C189" s="8" t="s">
@@ -18176,7 +18209,7 @@
       <c r="A190" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="B190" s="16">
+      <c r="B190" s="17">
         <v>0</v>
       </c>
       <c r="C190" s="8" t="s">
@@ -18232,7 +18265,7 @@
       <c r="A191" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="B191" s="16">
+      <c r="B191" s="17">
         <v>0</v>
       </c>
       <c r="C191" s="8" t="s">
@@ -18288,7 +18321,7 @@
       <c r="A192" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="B192" s="16">
+      <c r="B192" s="17">
         <v>0</v>
       </c>
       <c r="C192" s="8" t="s">
@@ -18344,7 +18377,7 @@
       <c r="A193" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="B193" s="16">
+      <c r="B193" s="17">
         <v>0</v>
       </c>
       <c r="C193" s="8" t="s">
@@ -18400,7 +18433,7 @@
       <c r="A194" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <v>0</v>
       </c>
       <c r="C194" s="8" t="s">
@@ -18456,7 +18489,7 @@
       <c r="A195" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="B195" s="16">
+      <c r="B195" s="17">
         <v>0</v>
       </c>
       <c r="C195" s="8" t="s">
@@ -18512,7 +18545,7 @@
       <c r="A196" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="B196" s="16">
+      <c r="B196" s="17">
         <v>0</v>
       </c>
       <c r="C196" s="8" t="s">
@@ -18568,7 +18601,7 @@
       <c r="A197" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="B197" s="16">
+      <c r="B197" s="17">
         <v>0</v>
       </c>
       <c r="C197" s="8" t="s">
@@ -18624,7 +18657,7 @@
       <c r="A198" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="B198" s="16">
+      <c r="B198" s="17">
         <v>0</v>
       </c>
       <c r="C198" s="8" t="s">
@@ -18680,7 +18713,7 @@
       <c r="A199" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199" s="17">
         <v>0</v>
       </c>
       <c r="C199" s="8" t="s">
@@ -18736,7 +18769,7 @@
       <c r="A200" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="B200" s="16">
+      <c r="B200" s="17">
         <v>0</v>
       </c>
       <c r="C200" s="8" t="s">
@@ -18792,7 +18825,7 @@
       <c r="A201" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="B201" s="16">
+      <c r="B201" s="17">
         <v>0</v>
       </c>
       <c r="C201" s="8" t="s">
@@ -18848,7 +18881,7 @@
       <c r="A202" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="B202" s="16">
+      <c r="B202" s="17">
         <v>0</v>
       </c>
       <c r="C202" s="8" t="s">
@@ -18904,7 +18937,7 @@
       <c r="A203" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="B203" s="16">
+      <c r="B203" s="17">
         <v>0</v>
       </c>
       <c r="C203" s="8" t="s">
@@ -18960,7 +18993,7 @@
       <c r="A204" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="B204" s="16">
+      <c r="B204" s="17">
         <v>0</v>
       </c>
       <c r="C204" s="8" t="s">
@@ -19016,7 +19049,7 @@
       <c r="A205" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="B205" s="16">
+      <c r="B205" s="17">
         <v>0</v>
       </c>
       <c r="C205" s="8" t="s">
@@ -19072,7 +19105,7 @@
       <c r="A206" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="B206" s="16">
+      <c r="B206" s="17">
         <v>0</v>
       </c>
       <c r="C206" s="8" t="s">
@@ -19128,7 +19161,7 @@
       <c r="A207" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <v>0</v>
       </c>
       <c r="C207" s="8" t="s">
@@ -19184,7 +19217,7 @@
       <c r="A208" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="B208" s="16">
+      <c r="B208" s="17">
         <v>0</v>
       </c>
       <c r="C208" s="8" t="s">
@@ -19240,7 +19273,7 @@
       <c r="A209" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209" s="17">
         <v>0</v>
       </c>
       <c r="C209" s="8" t="s">
@@ -19296,7 +19329,7 @@
       <c r="A210" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="B210" s="16">
+      <c r="B210" s="17">
         <v>0</v>
       </c>
       <c r="C210" s="8" t="s">
@@ -19352,7 +19385,7 @@
       <c r="A211" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="B211" s="16">
+      <c r="B211" s="17">
         <v>0</v>
       </c>
       <c r="C211" s="8" t="s">
@@ -19408,7 +19441,7 @@
       <c r="A212" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="B212" s="16">
+      <c r="B212" s="17">
         <v>0</v>
       </c>
       <c r="C212" s="8" t="s">
@@ -19464,7 +19497,7 @@
       <c r="A213" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="B213" s="16">
+      <c r="B213" s="17">
         <v>0</v>
       </c>
       <c r="C213" s="8" t="s">
@@ -19520,7 +19553,7 @@
       <c r="A214" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="B214" s="16">
+      <c r="B214" s="17">
         <v>0</v>
       </c>
       <c r="C214" s="8" t="s">
@@ -19576,7 +19609,7 @@
       <c r="A215" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="B215" s="16">
+      <c r="B215" s="17">
         <v>0</v>
       </c>
       <c r="C215" s="8" t="s">
@@ -19632,7 +19665,7 @@
       <c r="A216" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="B216" s="16">
+      <c r="B216" s="17">
         <v>0</v>
       </c>
       <c r="C216" s="8" t="s">
@@ -19688,7 +19721,7 @@
       <c r="A217" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="B217" s="16">
+      <c r="B217" s="17">
         <v>0</v>
       </c>
       <c r="C217" s="8" t="s">
@@ -19744,7 +19777,7 @@
       <c r="A218" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B218" s="16">
+      <c r="B218" s="17">
         <v>0</v>
       </c>
       <c r="C218" s="8" t="s">
@@ -19800,7 +19833,7 @@
       <c r="A219" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="B219" s="16">
+      <c r="B219" s="17">
         <v>0</v>
       </c>
       <c r="C219" s="8" t="s">
@@ -19856,7 +19889,7 @@
       <c r="A220" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <v>0</v>
       </c>
       <c r="C220" s="8" t="s">
@@ -19912,7 +19945,7 @@
       <c r="A221" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B221" s="16">
+      <c r="B221" s="17">
         <v>0</v>
       </c>
       <c r="C221" s="8" t="s">
@@ -19968,7 +20001,7 @@
       <c r="A222" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="B222" s="16">
+      <c r="B222" s="17">
         <v>0</v>
       </c>
       <c r="C222" s="8" t="s">
@@ -20024,7 +20057,7 @@
       <c r="A223" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="B223" s="16">
+      <c r="B223" s="17">
         <v>0</v>
       </c>
       <c r="C223" s="8" t="s">
@@ -20080,7 +20113,7 @@
       <c r="A224" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="B224" s="16">
+      <c r="B224" s="17">
         <v>0</v>
       </c>
       <c r="C224" s="8" t="s">
@@ -20136,7 +20169,7 @@
       <c r="A225" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="B225" s="16">
+      <c r="B225" s="17">
         <v>0</v>
       </c>
       <c r="C225" s="8" t="s">
@@ -20192,7 +20225,7 @@
       <c r="A226" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="B226" s="16">
+      <c r="B226" s="17">
         <v>0</v>
       </c>
       <c r="C226" s="8" t="s">
@@ -20248,7 +20281,7 @@
       <c r="A227" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="B227" s="16">
+      <c r="B227" s="17">
         <v>0</v>
       </c>
       <c r="C227" s="8" t="s">
@@ -20304,7 +20337,7 @@
       <c r="A228" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="B228" s="16">
+      <c r="B228" s="17">
         <v>0</v>
       </c>
       <c r="C228" s="8" t="s">
@@ -20360,7 +20393,7 @@
       <c r="A229" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="B229" s="16">
+      <c r="B229" s="17">
         <v>0</v>
       </c>
       <c r="C229" s="8" t="s">
@@ -20416,7 +20449,7 @@
       <c r="A230" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="B230" s="16">
+      <c r="B230" s="17">
         <v>0</v>
       </c>
       <c r="C230" s="8" t="s">
@@ -20472,7 +20505,7 @@
       <c r="A231" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="B231" s="16">
+      <c r="B231" s="17">
         <v>0</v>
       </c>
       <c r="C231" s="8" t="s">
@@ -20528,7 +20561,7 @@
       <c r="A232" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="B232" s="16">
+      <c r="B232" s="17">
         <v>0</v>
       </c>
       <c r="C232" s="8" t="s">
@@ -20584,7 +20617,7 @@
       <c r="A233" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <v>0</v>
       </c>
       <c r="C233" s="8" t="s">
@@ -20640,7 +20673,7 @@
       <c r="A234" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="B234" s="16">
+      <c r="B234" s="17">
         <v>0</v>
       </c>
       <c r="C234" s="8" t="s">
@@ -20696,7 +20729,7 @@
       <c r="A235" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="B235" s="16">
+      <c r="B235" s="17">
         <v>0</v>
       </c>
       <c r="C235" s="8" t="s">
@@ -20752,7 +20785,7 @@
       <c r="A236" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="B236" s="16">
+      <c r="B236" s="17">
         <v>0</v>
       </c>
       <c r="C236" s="8" t="s">
@@ -20808,7 +20841,7 @@
       <c r="A237" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B237" s="16">
+      <c r="B237" s="17">
         <v>0</v>
       </c>
       <c r="C237" s="8" t="s">
@@ -20864,7 +20897,7 @@
       <c r="A238" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="B238" s="16">
+      <c r="B238" s="17">
         <v>0</v>
       </c>
       <c r="C238" s="8" t="s">
@@ -20920,7 +20953,7 @@
       <c r="A239" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="B239" s="16">
+      <c r="B239" s="17">
         <v>0</v>
       </c>
       <c r="C239" s="8" t="s">
@@ -20976,7 +21009,7 @@
       <c r="A240" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="B240" s="16">
+      <c r="B240" s="17">
         <v>0</v>
       </c>
       <c r="C240" s="8" t="s">
@@ -21032,7 +21065,7 @@
       <c r="A241" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="B241" s="16">
+      <c r="B241" s="17">
         <v>0</v>
       </c>
       <c r="C241" s="8" t="s">
@@ -21088,7 +21121,7 @@
       <c r="A242" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="B242" s="16">
+      <c r="B242" s="17">
         <v>0</v>
       </c>
       <c r="C242" s="8" t="s">
@@ -21144,7 +21177,7 @@
       <c r="A243" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="B243" s="16">
+      <c r="B243" s="17">
         <v>0</v>
       </c>
       <c r="C243" s="8" t="s">
@@ -21200,7 +21233,7 @@
       <c r="A244" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="B244" s="16">
+      <c r="B244" s="17">
         <v>0</v>
       </c>
       <c r="C244" s="8" t="s">
@@ -21256,7 +21289,7 @@
       <c r="A245" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="B245" s="16">
+      <c r="B245" s="17">
         <v>0</v>
       </c>
       <c r="C245" s="8" t="s">
@@ -21312,7 +21345,7 @@
       <c r="A246" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <v>0</v>
       </c>
       <c r="C246" s="8" t="s">
@@ -21368,7 +21401,7 @@
       <c r="A247" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="B247" s="16">
+      <c r="B247" s="17">
         <v>0</v>
       </c>
       <c r="C247" s="8" t="s">
@@ -21424,7 +21457,7 @@
       <c r="A248" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="B248" s="16">
+      <c r="B248" s="17">
         <v>0</v>
       </c>
       <c r="C248" s="8" t="s">
@@ -21480,7 +21513,7 @@
       <c r="A249" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="B249" s="16">
+      <c r="B249" s="17">
         <v>0</v>
       </c>
       <c r="C249" s="8" t="s">
@@ -21536,7 +21569,7 @@
       <c r="A250" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="B250" s="16">
+      <c r="B250" s="17">
         <v>0</v>
       </c>
       <c r="C250" s="8" t="s">
@@ -21592,7 +21625,7 @@
       <c r="A251" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="B251" s="16">
+      <c r="B251" s="17">
         <v>0</v>
       </c>
       <c r="C251" s="8" t="s">
@@ -21648,7 +21681,7 @@
       <c r="A252" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="B252" s="16">
+      <c r="B252" s="17">
         <v>0</v>
       </c>
       <c r="C252" s="8" t="s">
@@ -21704,7 +21737,7 @@
       <c r="A253" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="B253" s="16">
+      <c r="B253" s="17">
         <v>0</v>
       </c>
       <c r="C253" s="8" t="s">
@@ -21760,7 +21793,7 @@
       <c r="A254" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="B254" s="16">
+      <c r="B254" s="17">
         <v>0</v>
       </c>
       <c r="C254" s="8" t="s">
@@ -21816,7 +21849,7 @@
       <c r="A255" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="B255" s="16">
+      <c r="B255" s="17">
         <v>0</v>
       </c>
       <c r="C255" s="8" t="s">
@@ -21872,7 +21905,7 @@
       <c r="A256" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="B256" s="16">
+      <c r="B256" s="17">
         <v>0</v>
       </c>
       <c r="C256" s="8" t="s">
@@ -21928,7 +21961,7 @@
       <c r="A257" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="B257" s="16">
+      <c r="B257" s="17">
         <v>0</v>
       </c>
       <c r="C257" s="8" t="s">
@@ -21984,7 +22017,7 @@
       <c r="A258" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B258" s="16">
+      <c r="B258" s="17">
         <v>0</v>
       </c>
       <c r="C258" s="8" t="s">
@@ -22040,7 +22073,7 @@
       <c r="A259" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <v>0</v>
       </c>
       <c r="C259" s="8" t="s">
@@ -22096,7 +22129,7 @@
       <c r="A260" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="B260" s="16">
+      <c r="B260" s="17">
         <v>0</v>
       </c>
       <c r="C260" s="8" t="s">
@@ -22152,7 +22185,7 @@
       <c r="A261" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="B261" s="16">
+      <c r="B261" s="17">
         <v>0</v>
       </c>
       <c r="C261" s="8" t="s">
@@ -22208,7 +22241,7 @@
       <c r="A262" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="B262" s="16">
+      <c r="B262" s="17">
         <v>0</v>
       </c>
       <c r="C262" s="8" t="s">
@@ -22264,7 +22297,7 @@
       <c r="A263" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="B263" s="16">
+      <c r="B263" s="17">
         <v>0</v>
       </c>
       <c r="C263" s="8" t="s">
@@ -22320,7 +22353,7 @@
       <c r="A264" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="B264" s="16">
+      <c r="B264" s="17">
         <v>0</v>
       </c>
       <c r="C264" s="8" t="s">
@@ -22376,7 +22409,7 @@
       <c r="A265" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="B265" s="16">
+      <c r="B265" s="17">
         <v>0</v>
       </c>
       <c r="C265" s="8" t="s">
@@ -22432,7 +22465,7 @@
       <c r="A266" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="B266" s="16">
+      <c r="B266" s="17">
         <v>0</v>
       </c>
       <c r="C266" s="8" t="s">
@@ -22488,7 +22521,7 @@
       <c r="A267" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="B267" s="16">
+      <c r="B267" s="17">
         <v>0</v>
       </c>
       <c r="C267" s="8" t="s">
@@ -22544,7 +22577,7 @@
       <c r="A268" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="B268" s="16">
+      <c r="B268" s="17">
         <v>0</v>
       </c>
       <c r="C268" s="8" t="s">
@@ -22600,7 +22633,7 @@
       <c r="A269" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="B269" s="16">
+      <c r="B269" s="17">
         <v>0</v>
       </c>
       <c r="C269" s="8" t="s">
@@ -22656,7 +22689,7 @@
       <c r="A270" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="B270" s="16">
+      <c r="B270" s="17">
         <v>0</v>
       </c>
       <c r="C270" s="8" t="s">
@@ -22712,7 +22745,7 @@
       <c r="A271" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="B271" s="16">
+      <c r="B271" s="17">
         <v>0</v>
       </c>
       <c r="C271" s="8" t="s">
@@ -22768,7 +22801,7 @@
       <c r="A272" s="8" t="s">
         <v>735</v>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <v>0</v>
       </c>
       <c r="C272" s="8" t="s">
@@ -22824,7 +22857,7 @@
       <c r="A273" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="B273" s="16">
+      <c r="B273" s="17">
         <v>0</v>
       </c>
       <c r="C273" s="8" t="s">
@@ -22880,7 +22913,7 @@
       <c r="A274" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="B274" s="16">
+      <c r="B274" s="17">
         <v>0</v>
       </c>
       <c r="C274" s="8" t="s">
@@ -22936,7 +22969,7 @@
       <c r="A275" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="B275" s="16">
+      <c r="B275" s="17">
         <v>0</v>
       </c>
       <c r="C275" s="8" t="s">
@@ -22992,7 +23025,7 @@
       <c r="A276" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B276" s="16">
+      <c r="B276" s="17">
         <v>0</v>
       </c>
       <c r="C276" s="8" t="s">
@@ -23048,7 +23081,7 @@
       <c r="A277" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="B277" s="16">
+      <c r="B277" s="17">
         <v>0</v>
       </c>
       <c r="C277" s="8" t="s">
@@ -23104,7 +23137,7 @@
       <c r="A278" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="B278" s="16">
+      <c r="B278" s="17">
         <v>0</v>
       </c>
       <c r="C278" s="8" t="s">
@@ -23160,7 +23193,7 @@
       <c r="A279" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="B279" s="16">
+      <c r="B279" s="17">
         <v>0</v>
       </c>
       <c r="C279" s="8" t="s">
@@ -23216,7 +23249,7 @@
       <c r="A280" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="B280" s="16">
+      <c r="B280" s="17">
         <v>0</v>
       </c>
       <c r="C280" s="8" t="s">
@@ -23272,7 +23305,7 @@
       <c r="A281" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="B281" s="16">
+      <c r="B281" s="17">
         <v>0</v>
       </c>
       <c r="C281" s="8" t="s">
@@ -23328,7 +23361,7 @@
       <c r="A282" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="B282" s="16">
+      <c r="B282" s="17">
         <v>0</v>
       </c>
       <c r="C282" s="8" t="s">
@@ -23384,7 +23417,7 @@
       <c r="A283" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="B283" s="16">
+      <c r="B283" s="17">
         <v>0</v>
       </c>
       <c r="C283" s="8" t="s">
@@ -23440,7 +23473,7 @@
       <c r="A284" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="B284" s="16">
+      <c r="B284" s="17">
         <v>0</v>
       </c>
       <c r="C284" s="8" t="s">
@@ -23496,7 +23529,7 @@
       <c r="A285" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="17">
         <v>0</v>
       </c>
       <c r="C285" s="8" t="s">
@@ -23552,7 +23585,7 @@
       <c r="A286" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="B286" s="16">
+      <c r="B286" s="17">
         <v>0</v>
       </c>
       <c r="C286" s="8" t="s">
@@ -23608,7 +23641,7 @@
       <c r="A287" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="B287" s="16">
+      <c r="B287" s="17">
         <v>0</v>
       </c>
       <c r="C287" s="8" t="s">
@@ -23664,7 +23697,7 @@
       <c r="A288" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="B288" s="16">
+      <c r="B288" s="17">
         <v>0</v>
       </c>
       <c r="C288" s="8" t="s">
@@ -23720,7 +23753,7 @@
       <c r="A289" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="B289" s="16">
+      <c r="B289" s="17">
         <v>0</v>
       </c>
       <c r="C289" s="8" t="s">
@@ -23776,7 +23809,7 @@
       <c r="A290" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="B290" s="16">
+      <c r="B290" s="17">
         <v>0</v>
       </c>
       <c r="C290" s="8" t="s">
@@ -23832,7 +23865,7 @@
       <c r="A291" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="B291" s="16">
+      <c r="B291" s="17">
         <v>0</v>
       </c>
       <c r="C291" s="8" t="s">
@@ -23888,7 +23921,7 @@
       <c r="A292" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="B292" s="16">
+      <c r="B292" s="17">
         <v>0</v>
       </c>
       <c r="C292" s="8" t="s">
@@ -23944,7 +23977,7 @@
       <c r="A293" s="8" t="s">
         <v>789</v>
       </c>
-      <c r="B293" s="16">
+      <c r="B293" s="17">
         <v>0</v>
       </c>
       <c r="C293" s="8" t="s">
@@ -24000,7 +24033,7 @@
       <c r="A294" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="B294" s="16">
+      <c r="B294" s="17">
         <v>0</v>
       </c>
       <c r="C294" s="8" t="s">
@@ -24056,7 +24089,7 @@
       <c r="A295" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="B295" s="16">
+      <c r="B295" s="17">
         <v>0</v>
       </c>
       <c r="C295" s="8" t="s">
@@ -24112,7 +24145,7 @@
       <c r="A296" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="B296" s="16">
+      <c r="B296" s="17">
         <v>0</v>
       </c>
       <c r="C296" s="8" t="s">
@@ -24168,7 +24201,7 @@
       <c r="A297" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="B297" s="16">
+      <c r="B297" s="17">
         <v>0</v>
       </c>
       <c r="C297" s="8" t="s">
@@ -24224,7 +24257,7 @@
       <c r="A298" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="B298" s="16">
+      <c r="B298" s="17">
         <v>0</v>
       </c>
       <c r="C298" s="8" t="s">
@@ -24280,7 +24313,7 @@
       <c r="A299" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="B299" s="16">
+      <c r="B299" s="17">
         <v>0</v>
       </c>
       <c r="C299" s="8" t="s">
@@ -24336,7 +24369,7 @@
       <c r="A300" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="B300" s="16">
+      <c r="B300" s="17">
         <v>0</v>
       </c>
       <c r="C300" s="8" t="s">
@@ -24392,7 +24425,7 @@
       <c r="A301" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="B301" s="16">
+      <c r="B301" s="17">
         <v>0</v>
       </c>
       <c r="C301" s="8" t="s">
@@ -24448,7 +24481,7 @@
       <c r="A302" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="B302" s="16">
+      <c r="B302" s="17">
         <v>0</v>
       </c>
       <c r="C302" s="8" t="s">
@@ -24504,7 +24537,7 @@
       <c r="A303" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="B303" s="16">
+      <c r="B303" s="17">
         <v>0</v>
       </c>
       <c r="C303" s="8" t="s">
@@ -24560,7 +24593,7 @@
       <c r="A304" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="B304" s="16">
+      <c r="B304" s="17">
         <v>0</v>
       </c>
       <c r="C304" s="8" t="s">
@@ -24616,7 +24649,7 @@
       <c r="A305" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="B305" s="16">
+      <c r="B305" s="17">
         <v>0</v>
       </c>
       <c r="C305" s="8" t="s">
@@ -24672,7 +24705,7 @@
       <c r="A306" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="B306" s="16">
+      <c r="B306" s="17">
         <v>0</v>
       </c>
       <c r="C306" s="8" t="s">
@@ -24728,7 +24761,7 @@
       <c r="A307" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="B307" s="16">
+      <c r="B307" s="17">
         <v>0</v>
       </c>
       <c r="C307" s="8" t="s">
@@ -24784,7 +24817,7 @@
       <c r="A308" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="B308" s="16">
+      <c r="B308" s="17">
         <v>0</v>
       </c>
       <c r="C308" s="8" t="s">
@@ -24840,7 +24873,7 @@
       <c r="A309" s="8" t="s">
         <v>822</v>
       </c>
-      <c r="B309" s="16">
+      <c r="B309" s="17">
         <v>0</v>
       </c>
       <c r="C309" s="8" t="s">
@@ -24896,7 +24929,7 @@
       <c r="A310" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="B310" s="16">
+      <c r="B310" s="17">
         <v>0</v>
       </c>
       <c r="C310" s="8" t="s">
@@ -24952,7 +24985,7 @@
       <c r="A311" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="B311" s="16">
+      <c r="B311" s="17">
         <v>0</v>
       </c>
       <c r="C311" s="8" t="s">
@@ -25008,7 +25041,7 @@
       <c r="A312" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="B312" s="16">
+      <c r="B312" s="17">
         <v>0</v>
       </c>
       <c r="C312" s="8" t="s">
@@ -25064,7 +25097,7 @@
       <c r="A313" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="B313" s="16">
+      <c r="B313" s="17">
         <v>0</v>
       </c>
       <c r="C313" s="8" t="s">
@@ -25120,7 +25153,7 @@
       <c r="A314" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="B314" s="16">
+      <c r="B314" s="17">
         <v>0</v>
       </c>
       <c r="C314" s="8" t="s">
@@ -25176,7 +25209,7 @@
       <c r="A315" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="B315" s="16">
+      <c r="B315" s="17">
         <v>0</v>
       </c>
       <c r="C315" s="8" t="s">
@@ -25232,7 +25265,7 @@
       <c r="A316" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="B316" s="16">
+      <c r="B316" s="17">
         <v>0</v>
       </c>
       <c r="C316" s="8" t="s">
@@ -25288,7 +25321,7 @@
       <c r="A317" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="B317" s="16">
+      <c r="B317" s="17">
         <v>0</v>
       </c>
       <c r="C317" s="8" t="s">
@@ -25344,7 +25377,7 @@
       <c r="A318" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="B318" s="16">
+      <c r="B318" s="17">
         <v>0</v>
       </c>
       <c r="C318" s="8" t="s">
@@ -25400,7 +25433,7 @@
       <c r="A319" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="B319" s="16">
+      <c r="B319" s="17">
         <v>0</v>
       </c>
       <c r="C319" s="8" t="s">
@@ -25456,7 +25489,7 @@
       <c r="A320" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="B320" s="16">
+      <c r="B320" s="17">
         <v>0</v>
       </c>
       <c r="C320" s="8" t="s">
@@ -25512,7 +25545,7 @@
       <c r="A321" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="B321" s="16">
+      <c r="B321" s="17">
         <v>0</v>
       </c>
       <c r="C321" s="8" t="s">
@@ -25568,7 +25601,7 @@
       <c r="A322" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="B322" s="16">
+      <c r="B322" s="17">
         <v>0</v>
       </c>
       <c r="C322" s="8" t="s">
@@ -25624,7 +25657,7 @@
       <c r="A323" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="B323" s="16">
+      <c r="B323" s="17">
         <v>0</v>
       </c>
       <c r="C323" s="8" t="s">
@@ -25680,7 +25713,7 @@
       <c r="A324" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="B324" s="16">
+      <c r="B324" s="17">
         <v>0</v>
       </c>
       <c r="C324" s="8" t="s">
@@ -25736,7 +25769,7 @@
       <c r="A325" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="B325" s="16">
+      <c r="B325" s="17">
         <v>0</v>
       </c>
       <c r="C325" s="8" t="s">
@@ -25792,7 +25825,7 @@
       <c r="A326" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="B326" s="16">
+      <c r="B326" s="17">
         <v>0</v>
       </c>
       <c r="C326" s="8" t="s">
@@ -25848,7 +25881,7 @@
       <c r="A327" s="8" t="s">
         <v>863</v>
       </c>
-      <c r="B327" s="16">
+      <c r="B327" s="17">
         <v>0</v>
       </c>
       <c r="C327" s="8" t="s">
@@ -25904,7 +25937,7 @@
       <c r="A328" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="B328" s="16">
+      <c r="B328" s="17">
         <v>0</v>
       </c>
       <c r="C328" s="8" t="s">
@@ -25960,7 +25993,7 @@
       <c r="A329" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="B329" s="16">
+      <c r="B329" s="17">
         <v>0</v>
       </c>
       <c r="C329" s="8" t="s">
@@ -26016,7 +26049,7 @@
       <c r="A330" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="B330" s="16">
+      <c r="B330" s="17">
         <v>0</v>
       </c>
       <c r="C330" s="8" t="s">
@@ -26072,7 +26105,7 @@
       <c r="A331" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="B331" s="16">
+      <c r="B331" s="17">
         <v>0</v>
       </c>
       <c r="C331" s="8" t="s">
@@ -26128,7 +26161,7 @@
       <c r="A332" s="8" t="s">
         <v>874</v>
       </c>
-      <c r="B332" s="16">
+      <c r="B332" s="17">
         <v>0</v>
       </c>
       <c r="C332" s="8" t="s">
@@ -26184,7 +26217,7 @@
       <c r="A333" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="B333" s="16">
+      <c r="B333" s="17">
         <v>0</v>
       </c>
       <c r="C333" s="8" t="s">
@@ -26240,7 +26273,7 @@
       <c r="A334" s="8" t="s">
         <v>879</v>
       </c>
-      <c r="B334" s="16">
+      <c r="B334" s="17">
         <v>0</v>
       </c>
       <c r="C334" s="8" t="s">
@@ -26296,7 +26329,7 @@
       <c r="A335" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="B335" s="16">
+      <c r="B335" s="17">
         <v>0</v>
       </c>
       <c r="C335" s="8" t="s">
@@ -26352,7 +26385,7 @@
       <c r="A336" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="B336" s="16">
+      <c r="B336" s="17">
         <v>0</v>
       </c>
       <c r="C336" s="8" t="s">
@@ -26408,7 +26441,7 @@
       <c r="A337" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="B337" s="16">
+      <c r="B337" s="17">
         <v>0</v>
       </c>
       <c r="C337" s="8" t="s">
@@ -26464,7 +26497,7 @@
       <c r="A338" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="B338" s="16">
+      <c r="B338" s="17">
         <v>0</v>
       </c>
       <c r="C338" s="8" t="s">
@@ -26520,7 +26553,7 @@
       <c r="A339" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="B339" s="16">
+      <c r="B339" s="17">
         <v>0</v>
       </c>
       <c r="C339" s="8" t="s">
@@ -26576,7 +26609,7 @@
       <c r="A340" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="B340" s="16">
+      <c r="B340" s="17">
         <v>0</v>
       </c>
       <c r="C340" s="8" t="s">
@@ -26632,7 +26665,7 @@
       <c r="A341" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="B341" s="16">
+      <c r="B341" s="17">
         <v>0</v>
       </c>
       <c r="C341" s="8" t="s">
@@ -26688,7 +26721,7 @@
       <c r="A342" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="B342" s="16">
+      <c r="B342" s="17">
         <v>0</v>
       </c>
       <c r="C342" s="8" t="s">
@@ -26744,7 +26777,7 @@
       <c r="A343" s="8" t="s">
         <v>897</v>
       </c>
-      <c r="B343" s="16">
+      <c r="B343" s="17">
         <v>0</v>
       </c>
       <c r="C343" s="8" t="s">
@@ -26800,7 +26833,7 @@
       <c r="A344" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="B344" s="16">
+      <c r="B344" s="17">
         <v>0</v>
       </c>
       <c r="C344" s="8" t="s">
@@ -26856,7 +26889,7 @@
       <c r="A345" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="B345" s="16">
+      <c r="B345" s="17">
         <v>0</v>
       </c>
       <c r="C345" s="8" t="s">
@@ -26912,7 +26945,7 @@
       <c r="A346" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="B346" s="16">
+      <c r="B346" s="17">
         <v>0</v>
       </c>
       <c r="C346" s="8" t="s">
@@ -26968,7 +27001,7 @@
       <c r="A347" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="B347" s="16">
+      <c r="B347" s="17">
         <v>0</v>
       </c>
       <c r="C347" s="8" t="s">
@@ -27024,7 +27057,7 @@
       <c r="A348" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="B348" s="16">
+      <c r="B348" s="17">
         <v>0</v>
       </c>
       <c r="C348" s="8" t="s">
@@ -27080,7 +27113,7 @@
       <c r="A349" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="B349" s="16">
+      <c r="B349" s="17">
         <v>0</v>
       </c>
       <c r="C349" s="8" t="s">
@@ -27136,7 +27169,7 @@
       <c r="A350" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="B350" s="16">
+      <c r="B350" s="17">
         <v>0</v>
       </c>
       <c r="C350" s="8" t="s">
@@ -27192,7 +27225,7 @@
       <c r="A351" s="8" t="s">
         <v>924</v>
       </c>
-      <c r="B351" s="16">
+      <c r="B351" s="17">
         <v>0</v>
       </c>
       <c r="C351" s="8" t="s">
@@ -27248,7 +27281,7 @@
       <c r="A352" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="B352" s="16">
+      <c r="B352" s="17">
         <v>0</v>
       </c>
       <c r="C352" s="8" t="s">
@@ -27304,7 +27337,7 @@
       <c r="A353" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="B353" s="16">
+      <c r="B353" s="17">
         <v>0</v>
       </c>
       <c r="C353" s="8" t="s">
@@ -27360,7 +27393,7 @@
       <c r="A354" s="8" t="s">
         <v>933</v>
       </c>
-      <c r="B354" s="16">
+      <c r="B354" s="17">
         <v>0</v>
       </c>
       <c r="C354" s="8" t="s">
@@ -27416,7 +27449,7 @@
       <c r="A355" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="B355" s="16">
+      <c r="B355" s="17">
         <v>0</v>
       </c>
       <c r="C355" s="8" t="s">
@@ -27472,7 +27505,7 @@
       <c r="A356" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="B356" s="16">
+      <c r="B356" s="17">
         <v>0</v>
       </c>
       <c r="C356" s="8" t="s">
@@ -27528,7 +27561,7 @@
       <c r="A357" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="B357" s="16">
+      <c r="B357" s="17">
         <v>0</v>
       </c>
       <c r="C357" s="8" t="s">
@@ -27584,7 +27617,7 @@
       <c r="A358" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="B358" s="16">
+      <c r="B358" s="17">
         <v>0</v>
       </c>
       <c r="C358" s="8" t="s">
@@ -27640,7 +27673,7 @@
       <c r="A359" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B359" s="16">
+      <c r="B359" s="17">
         <v>0</v>
       </c>
       <c r="C359" s="8" t="s">
@@ -27696,7 +27729,7 @@
       <c r="A360" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="B360" s="16">
+      <c r="B360" s="17">
         <v>0</v>
       </c>
       <c r="C360" s="8" t="s">
@@ -27752,7 +27785,7 @@
       <c r="A361" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="B361" s="16">
+      <c r="B361" s="17">
         <v>0</v>
       </c>
       <c r="C361" s="8" t="s">
@@ -27808,7 +27841,7 @@
       <c r="A362" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="B362" s="16">
+      <c r="B362" s="17">
         <v>0</v>
       </c>
       <c r="C362" s="8" t="s">
@@ -27864,7 +27897,7 @@
       <c r="A363" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="B363" s="16">
+      <c r="B363" s="17">
         <v>0</v>
       </c>
       <c r="C363" s="8" t="s">
@@ -27920,7 +27953,7 @@
       <c r="A364" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="B364" s="16">
+      <c r="B364" s="17">
         <v>0</v>
       </c>
       <c r="C364" s="8" t="s">
@@ -27976,7 +28009,7 @@
       <c r="A365" s="8" t="s">
         <v>962</v>
       </c>
-      <c r="B365" s="16">
+      <c r="B365" s="17">
         <v>0</v>
       </c>
       <c r="C365" s="8" t="s">
@@ -28032,7 +28065,7 @@
       <c r="A366" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="B366" s="16">
+      <c r="B366" s="17">
         <v>0</v>
       </c>
       <c r="C366" s="8" t="s">
@@ -28088,7 +28121,7 @@
       <c r="A367" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="B367" s="16">
+      <c r="B367" s="17">
         <v>0</v>
       </c>
       <c r="C367" s="8" t="s">
@@ -28144,7 +28177,7 @@
       <c r="A368" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="B368" s="16">
+      <c r="B368" s="17">
         <v>0</v>
       </c>
       <c r="C368" s="8" t="s">
@@ -28200,7 +28233,7 @@
       <c r="A369" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="B369" s="16">
+      <c r="B369" s="17">
         <v>0</v>
       </c>
       <c r="C369" s="8" t="s">
@@ -28256,7 +28289,7 @@
       <c r="A370" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="B370" s="16">
+      <c r="B370" s="17">
         <v>0</v>
       </c>
       <c r="C370" s="8" t="s">
@@ -28312,7 +28345,7 @@
       <c r="A371" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="B371" s="16">
+      <c r="B371" s="17">
         <v>0</v>
       </c>
       <c r="C371" s="8" t="s">
@@ -28368,7 +28401,7 @@
       <c r="A372" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="B372" s="16">
+      <c r="B372" s="17">
         <v>0</v>
       </c>
       <c r="C372" s="8" t="s">
@@ -28424,7 +28457,7 @@
       <c r="A373" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="B373" s="16">
+      <c r="B373" s="17">
         <v>0</v>
       </c>
       <c r="C373" s="8" t="s">
@@ -28480,7 +28513,7 @@
       <c r="A374" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="B374" s="16">
+      <c r="B374" s="17">
         <v>0</v>
       </c>
       <c r="C374" s="8" t="s">
@@ -28536,7 +28569,7 @@
       <c r="A375" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="B375" s="16">
+      <c r="B375" s="17">
         <v>0</v>
       </c>
       <c r="C375" s="8" t="s">
@@ -28592,7 +28625,7 @@
       <c r="A376" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="B376" s="16">
+      <c r="B376" s="17">
         <v>0</v>
       </c>
       <c r="C376" s="8" t="s">
@@ -28648,7 +28681,7 @@
       <c r="A377" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="B377" s="16">
+      <c r="B377" s="17">
         <v>0</v>
       </c>
       <c r="C377" s="8" t="s">
@@ -28704,7 +28737,7 @@
       <c r="A378" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="B378" s="16">
+      <c r="B378" s="17">
         <v>0</v>
       </c>
       <c r="C378" s="8" t="s">
@@ -28760,7 +28793,7 @@
       <c r="A379" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="B379" s="16">
+      <c r="B379" s="17">
         <v>0</v>
       </c>
       <c r="C379" s="8" t="s">
@@ -28816,7 +28849,7 @@
       <c r="A380" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="B380" s="16">
+      <c r="B380" s="17">
         <v>0</v>
       </c>
       <c r="C380" s="8" t="s">
@@ -28872,7 +28905,7 @@
       <c r="A381" s="8" t="s">
         <v>1016</v>
       </c>
-      <c r="B381" s="16">
+      <c r="B381" s="17">
         <v>0</v>
       </c>
       <c r="C381" s="8" t="s">
@@ -28928,7 +28961,7 @@
       <c r="A382" s="8" t="s">
         <v>1019</v>
       </c>
-      <c r="B382" s="16">
+      <c r="B382" s="17">
         <v>0</v>
       </c>
       <c r="C382" s="8" t="s">
@@ -28984,7 +29017,7 @@
       <c r="A383" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="B383" s="16">
+      <c r="B383" s="17">
         <v>0</v>
       </c>
       <c r="C383" s="8" t="s">
@@ -29040,7 +29073,7 @@
       <c r="A384" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="B384" s="16">
+      <c r="B384" s="17">
         <v>0</v>
       </c>
       <c r="C384" s="8" t="s">
@@ -29096,7 +29129,7 @@
       <c r="A385" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="B385" s="16">
+      <c r="B385" s="17">
         <v>0</v>
       </c>
       <c r="C385" s="8" t="s">
@@ -29152,7 +29185,7 @@
       <c r="A386" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="B386" s="16">
+      <c r="B386" s="17">
         <v>0</v>
       </c>
       <c r="C386" s="8" t="s">
@@ -29208,7 +29241,7 @@
       <c r="A387" s="8" t="s">
         <v>1034</v>
       </c>
-      <c r="B387" s="16">
+      <c r="B387" s="17">
         <v>0</v>
       </c>
       <c r="C387" s="8" t="s">
@@ -29264,7 +29297,7 @@
       <c r="A388" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="B388" s="16">
+      <c r="B388" s="17">
         <v>0</v>
       </c>
       <c r="C388" s="8" t="s">
@@ -29320,7 +29353,7 @@
       <c r="A389" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="B389" s="16">
+      <c r="B389" s="17">
         <v>0</v>
       </c>
       <c r="C389" s="8" t="s">
@@ -29376,7 +29409,7 @@
       <c r="A390" s="8" t="s">
         <v>1042</v>
       </c>
-      <c r="B390" s="16">
+      <c r="B390" s="17">
         <v>0</v>
       </c>
       <c r="C390" s="8" t="s">
@@ -29432,7 +29465,7 @@
       <c r="A391" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="B391" s="16">
+      <c r="B391" s="17">
         <v>0</v>
       </c>
       <c r="C391" s="8" t="s">
@@ -29488,7 +29521,7 @@
       <c r="A392" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="B392" s="16">
+      <c r="B392" s="17">
         <v>0</v>
       </c>
       <c r="C392" s="8" t="s">
@@ -29544,7 +29577,7 @@
       <c r="A393" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="B393" s="16">
+      <c r="B393" s="17">
         <v>0</v>
       </c>
       <c r="C393" s="8" t="s">
@@ -29600,7 +29633,7 @@
       <c r="A394" s="8" t="s">
         <v>1054</v>
       </c>
-      <c r="B394" s="16">
+      <c r="B394" s="17">
         <v>0</v>
       </c>
       <c r="C394" s="8" t="s">
@@ -29656,7 +29689,7 @@
       <c r="A395" s="8" t="s">
         <v>1057</v>
       </c>
-      <c r="B395" s="16">
+      <c r="B395" s="17">
         <v>0</v>
       </c>
       <c r="C395" s="8" t="s">
@@ -29712,7 +29745,7 @@
       <c r="A396" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="B396" s="16">
+      <c r="B396" s="17">
         <v>0</v>
       </c>
       <c r="C396" s="8" t="s">
@@ -29768,7 +29801,7 @@
       <c r="A397" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="B397" s="16">
+      <c r="B397" s="17">
         <v>0</v>
       </c>
       <c r="C397" s="8" t="s">
@@ -29824,7 +29857,7 @@
       <c r="A398" s="8" t="s">
         <v>1066</v>
       </c>
-      <c r="B398" s="16">
+      <c r="B398" s="17">
         <v>0</v>
       </c>
       <c r="C398" s="8" t="s">
@@ -29880,7 +29913,7 @@
       <c r="A399" s="8" t="s">
         <v>1069</v>
       </c>
-      <c r="B399" s="16">
+      <c r="B399" s="17">
         <v>0</v>
       </c>
       <c r="C399" s="8" t="s">
@@ -29936,7 +29969,7 @@
       <c r="A400" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="B400" s="16">
+      <c r="B400" s="17">
         <v>0</v>
       </c>
       <c r="C400" s="8" t="s">
@@ -29992,7 +30025,7 @@
       <c r="A401" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="B401" s="16">
+      <c r="B401" s="17">
         <v>0</v>
       </c>
       <c r="C401" s="8" t="s">
@@ -30048,7 +30081,7 @@
       <c r="A402" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="B402" s="16">
+      <c r="B402" s="17">
         <v>0</v>
       </c>
       <c r="C402" s="8" t="s">
@@ -30104,7 +30137,7 @@
       <c r="A403" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="B403" s="16">
+      <c r="B403" s="17">
         <v>0</v>
       </c>
       <c r="C403" s="8" t="s">
@@ -30160,7 +30193,7 @@
       <c r="A404" s="8" t="s">
         <v>1082</v>
       </c>
-      <c r="B404" s="16">
+      <c r="B404" s="17">
         <v>0</v>
       </c>
       <c r="C404" s="8" t="s">
@@ -30216,7 +30249,7 @@
       <c r="A405" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="B405" s="16">
+      <c r="B405" s="17">
         <v>0</v>
       </c>
       <c r="C405" s="8" t="s">
@@ -30272,7 +30305,7 @@
       <c r="A406" s="8" t="s">
         <v>1086</v>
       </c>
-      <c r="B406" s="16">
+      <c r="B406" s="17">
         <v>0</v>
       </c>
       <c r="C406" s="8" t="s">
@@ -30328,7 +30361,7 @@
       <c r="A407" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="B407" s="16">
+      <c r="B407" s="17">
         <v>0</v>
       </c>
       <c r="C407" s="8" t="s">
@@ -30384,7 +30417,7 @@
       <c r="A408" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="B408" s="16">
+      <c r="B408" s="17">
         <v>0</v>
       </c>
       <c r="C408" s="8" t="s">
@@ -30440,7 +30473,7 @@
       <c r="A409" s="8" t="s">
         <v>1094</v>
       </c>
-      <c r="B409" s="16">
+      <c r="B409" s="17">
         <v>0</v>
       </c>
       <c r="C409" s="8" t="s">
@@ -30496,7 +30529,7 @@
       <c r="A410" s="8" t="s">
         <v>1097</v>
       </c>
-      <c r="B410" s="16">
+      <c r="B410" s="17">
         <v>0</v>
       </c>
       <c r="C410" s="8" t="s">
@@ -30552,7 +30585,7 @@
       <c r="A411" s="8" t="s">
         <v>1099</v>
       </c>
-      <c r="B411" s="16">
+      <c r="B411" s="17">
         <v>0</v>
       </c>
       <c r="C411" s="8" t="s">
@@ -30608,7 +30641,7 @@
       <c r="A412" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="B412" s="16">
+      <c r="B412" s="17">
         <v>0</v>
       </c>
       <c r="C412" s="8" t="s">
@@ -30664,7 +30697,7 @@
       <c r="A413" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="B413" s="16">
+      <c r="B413" s="17">
         <v>0</v>
       </c>
       <c r="C413" s="8" t="s">
@@ -30720,7 +30753,7 @@
       <c r="A414" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="B414" s="16">
+      <c r="B414" s="17">
         <v>0</v>
       </c>
       <c r="C414" s="8" t="s">
@@ -30776,7 +30809,7 @@
       <c r="A415" s="8" t="s">
         <v>1110</v>
       </c>
-      <c r="B415" s="16">
+      <c r="B415" s="17">
         <v>0</v>
       </c>
       <c r="C415" s="8" t="s">
@@ -30832,7 +30865,7 @@
       <c r="A416" s="8" t="s">
         <v>1113</v>
       </c>
-      <c r="B416" s="16">
+      <c r="B416" s="17">
         <v>0</v>
       </c>
       <c r="C416" s="8" t="s">
@@ -30888,7 +30921,7 @@
       <c r="A417" s="8" t="s">
         <v>1115</v>
       </c>
-      <c r="B417" s="16">
+      <c r="B417" s="17">
         <v>0</v>
       </c>
       <c r="C417" s="8" t="s">
@@ -30944,7 +30977,7 @@
       <c r="A418" s="8" t="s">
         <v>1117</v>
       </c>
-      <c r="B418" s="16">
+      <c r="B418" s="17">
         <v>0</v>
       </c>
       <c r="C418" s="8" t="s">
@@ -31000,7 +31033,7 @@
       <c r="A419" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="B419" s="16">
+      <c r="B419" s="17">
         <v>0</v>
       </c>
       <c r="C419" s="8" t="s">
@@ -31056,7 +31089,7 @@
       <c r="A420" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="B420" s="16">
+      <c r="B420" s="17">
         <v>0</v>
       </c>
       <c r="C420" s="8" t="s">
@@ -31112,7 +31145,7 @@
       <c r="A421" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="B421" s="16">
+      <c r="B421" s="17">
         <v>0</v>
       </c>
       <c r="C421" s="8" t="s">
@@ -31168,7 +31201,7 @@
       <c r="A422" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="B422" s="16">
+      <c r="B422" s="17">
         <v>0</v>
       </c>
       <c r="C422" s="8" t="s">
@@ -31224,7 +31257,7 @@
       <c r="A423" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="B423" s="16">
+      <c r="B423" s="17">
         <v>0</v>
       </c>
       <c r="C423" s="8" t="s">
@@ -31280,7 +31313,7 @@
       <c r="A424" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="B424" s="16">
+      <c r="B424" s="17">
         <v>0</v>
       </c>
       <c r="C424" s="8" t="s">
@@ -31336,7 +31369,7 @@
       <c r="A425" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="B425" s="16">
+      <c r="B425" s="17">
         <v>0</v>
       </c>
       <c r="C425" s="8" t="s">
@@ -31392,7 +31425,7 @@
       <c r="A426" s="8" t="s">
         <v>1140</v>
       </c>
-      <c r="B426" s="16">
+      <c r="B426" s="17">
         <v>0</v>
       </c>
       <c r="C426" s="8" t="s">
@@ -31448,7 +31481,7 @@
       <c r="A427" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="B427" s="16">
+      <c r="B427" s="17">
         <v>0</v>
       </c>
       <c r="C427" s="8" t="s">
@@ -31504,7 +31537,7 @@
       <c r="A428" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="B428" s="16">
+      <c r="B428" s="17">
         <v>0</v>
       </c>
       <c r="C428" s="8" t="s">
@@ -31560,7 +31593,7 @@
       <c r="A429" s="8" t="s">
         <v>1150</v>
       </c>
-      <c r="B429" s="16">
+      <c r="B429" s="17">
         <v>0</v>
       </c>
       <c r="C429" s="8" t="s">
@@ -31616,7 +31649,7 @@
       <c r="A430" s="8" t="s">
         <v>1153</v>
       </c>
-      <c r="B430" s="16">
+      <c r="B430" s="17">
         <v>0</v>
       </c>
       <c r="C430" s="8" t="s">
@@ -31672,7 +31705,7 @@
       <c r="A431" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="B431" s="16">
+      <c r="B431" s="17">
         <v>0</v>
       </c>
       <c r="C431" s="8" t="s">
@@ -31728,7 +31761,7 @@
       <c r="A432" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="B432" s="16">
+      <c r="B432" s="17">
         <v>0</v>
       </c>
       <c r="C432" s="8" t="s">
@@ -31784,7 +31817,7 @@
       <c r="A433" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="B433" s="16">
+      <c r="B433" s="17">
         <v>0</v>
       </c>
       <c r="C433" s="8" t="s">
@@ -31840,7 +31873,7 @@
       <c r="A434" s="8" t="s">
         <v>1164</v>
       </c>
-      <c r="B434" s="16">
+      <c r="B434" s="17">
         <v>0</v>
       </c>
       <c r="C434" s="8" t="s">
@@ -31896,7 +31929,7 @@
       <c r="A435" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="B435" s="16">
+      <c r="B435" s="17">
         <v>0</v>
       </c>
       <c r="C435" s="8" t="s">
@@ -31952,7 +31985,7 @@
       <c r="A436" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="B436" s="16">
+      <c r="B436" s="17">
         <v>0</v>
       </c>
       <c r="C436" s="8" t="s">
@@ -32008,7 +32041,7 @@
       <c r="A437" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="B437" s="16">
+      <c r="B437" s="17">
         <v>0</v>
       </c>
       <c r="C437" s="8" t="s">
@@ -32064,7 +32097,7 @@
       <c r="A438" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="B438" s="16">
+      <c r="B438" s="17">
         <v>0</v>
       </c>
       <c r="C438" s="8" t="s">
@@ -32120,7 +32153,7 @@
       <c r="A439" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="B439" s="16">
+      <c r="B439" s="17">
         <v>0</v>
       </c>
       <c r="C439" s="8" t="s">
@@ -32176,7 +32209,7 @@
       <c r="A440" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="B440" s="16">
+      <c r="B440" s="17">
         <v>0</v>
       </c>
       <c r="C440" s="8" t="s">
@@ -32232,7 +32265,7 @@
       <c r="A441" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="B441" s="16">
+      <c r="B441" s="17">
         <v>0</v>
       </c>
       <c r="C441" s="8" t="s">
@@ -32288,7 +32321,7 @@
       <c r="A442" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="B442" s="16">
+      <c r="B442" s="17">
         <v>0</v>
       </c>
       <c r="C442" s="8" t="s">
@@ -32344,7 +32377,7 @@
       <c r="A443" s="8" t="s">
         <v>1192</v>
       </c>
-      <c r="B443" s="16">
+      <c r="B443" s="17">
         <v>0</v>
       </c>
       <c r="C443" s="8" t="s">
@@ -32400,7 +32433,7 @@
       <c r="A444" s="8" t="s">
         <v>1195</v>
       </c>
-      <c r="B444" s="16">
+      <c r="B444" s="17">
         <v>0</v>
       </c>
       <c r="C444" s="8" t="s">
@@ -32456,7 +32489,7 @@
       <c r="A445" s="8" t="s">
         <v>1198</v>
       </c>
-      <c r="B445" s="16">
+      <c r="B445" s="17">
         <v>0</v>
       </c>
       <c r="C445" s="8" t="s">
@@ -32512,7 +32545,7 @@
       <c r="A446" s="8" t="s">
         <v>1201</v>
       </c>
-      <c r="B446" s="16">
+      <c r="B446" s="17">
         <v>0</v>
       </c>
       <c r="C446" s="8" t="s">
@@ -32568,7 +32601,7 @@
       <c r="A447" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="B447" s="16">
+      <c r="B447" s="17">
         <v>0</v>
       </c>
       <c r="C447" s="8" t="s">
@@ -32624,7 +32657,7 @@
       <c r="A448" s="8" t="s">
         <v>1207</v>
       </c>
-      <c r="B448" s="16">
+      <c r="B448" s="17">
         <v>0</v>
       </c>
       <c r="C448" s="8" t="s">
@@ -32680,7 +32713,7 @@
       <c r="A449" s="8" t="s">
         <v>1210</v>
       </c>
-      <c r="B449" s="16">
+      <c r="B449" s="17">
         <v>0</v>
       </c>
       <c r="C449" s="8" t="s">
@@ -32736,7 +32769,7 @@
       <c r="A450" s="8" t="s">
         <v>1213</v>
       </c>
-      <c r="B450" s="16">
+      <c r="B450" s="17">
         <v>0</v>
       </c>
       <c r="C450" s="8" t="s">
@@ -32792,7 +32825,7 @@
       <c r="A451" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="B451" s="16">
+      <c r="B451" s="17">
         <v>0</v>
       </c>
       <c r="C451" s="8" t="s">
@@ -32848,7 +32881,7 @@
       <c r="A452" s="8" t="s">
         <v>1219</v>
       </c>
-      <c r="B452" s="16">
+      <c r="B452" s="17">
         <v>0</v>
       </c>
       <c r="C452" s="8" t="s">
@@ -32904,7 +32937,7 @@
       <c r="A453" s="8" t="s">
         <v>1222</v>
       </c>
-      <c r="B453" s="16">
+      <c r="B453" s="17">
         <v>0</v>
       </c>
       <c r="C453" s="8" t="s">
@@ -32960,7 +32993,7 @@
       <c r="A454" s="8" t="s">
         <v>1224</v>
       </c>
-      <c r="B454" s="16">
+      <c r="B454" s="17">
         <v>0</v>
       </c>
       <c r="C454" s="8" t="s">
@@ -33016,7 +33049,7 @@
       <c r="A455" s="8" t="s">
         <v>1228</v>
       </c>
-      <c r="B455" s="16">
+      <c r="B455" s="17">
         <v>0</v>
       </c>
       <c r="C455" s="8" t="s">
@@ -33072,7 +33105,7 @@
       <c r="A456" s="8" t="s">
         <v>1231</v>
       </c>
-      <c r="B456" s="16">
+      <c r="B456" s="17">
         <v>0</v>
       </c>
       <c r="C456" s="8" t="s">
@@ -33128,7 +33161,7 @@
       <c r="A457" s="8" t="s">
         <v>1234</v>
       </c>
-      <c r="B457" s="16">
+      <c r="B457" s="17">
         <v>0</v>
       </c>
       <c r="C457" s="8" t="s">
@@ -33184,7 +33217,7 @@
       <c r="A458" s="8" t="s">
         <v>1237</v>
       </c>
-      <c r="B458" s="16">
+      <c r="B458" s="17">
         <v>0</v>
       </c>
       <c r="C458" s="8" t="s">
@@ -33240,7 +33273,7 @@
       <c r="A459" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="B459" s="16">
+      <c r="B459" s="17">
         <v>0</v>
       </c>
       <c r="C459" s="8" t="s">
@@ -33296,7 +33329,7 @@
       <c r="A460" s="8" t="s">
         <v>1243</v>
       </c>
-      <c r="B460" s="16">
+      <c r="B460" s="17">
         <v>0</v>
       </c>
       <c r="C460" s="8" t="s">
@@ -33352,7 +33385,7 @@
       <c r="A461" s="8" t="s">
         <v>1246</v>
       </c>
-      <c r="B461" s="16">
+      <c r="B461" s="17">
         <v>0</v>
       </c>
       <c r="C461" s="8" t="s">
@@ -33408,7 +33441,7 @@
       <c r="A462" s="8" t="s">
         <v>1249</v>
       </c>
-      <c r="B462" s="16">
+      <c r="B462" s="17">
         <v>0</v>
       </c>
       <c r="C462" s="8" t="s">
@@ -33464,7 +33497,7 @@
       <c r="A463" s="8" t="s">
         <v>1252</v>
       </c>
-      <c r="B463" s="16">
+      <c r="B463" s="17">
         <v>0</v>
       </c>
       <c r="C463" s="8" t="s">
@@ -33520,7 +33553,7 @@
       <c r="A464" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="B464" s="16">
+      <c r="B464" s="17">
         <v>0</v>
       </c>
       <c r="C464" s="8" t="s">
@@ -33576,7 +33609,7 @@
       <c r="A465" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="B465" s="16">
+      <c r="B465" s="17">
         <v>0</v>
       </c>
       <c r="C465" s="8" t="s">
@@ -33632,7 +33665,7 @@
       <c r="A466" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="B466" s="16">
+      <c r="B466" s="17">
         <v>0</v>
       </c>
       <c r="C466" s="8" t="s">
@@ -33688,7 +33721,7 @@
       <c r="A467" s="8" t="s">
         <v>1263</v>
       </c>
-      <c r="B467" s="16">
+      <c r="B467" s="17">
         <v>0</v>
       </c>
       <c r="C467" s="8" t="s">
@@ -33744,7 +33777,7 @@
       <c r="A468" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="B468" s="16">
+      <c r="B468" s="17">
         <v>0</v>
       </c>
       <c r="C468" s="8" t="s">
@@ -33800,7 +33833,7 @@
       <c r="A469" s="8" t="s">
         <v>1269</v>
       </c>
-      <c r="B469" s="16">
+      <c r="B469" s="17">
         <v>0</v>
       </c>
       <c r="C469" s="8" t="s">
@@ -33856,7 +33889,7 @@
       <c r="A470" s="8" t="s">
         <v>1272</v>
       </c>
-      <c r="B470" s="16">
+      <c r="B470" s="17">
         <v>0</v>
       </c>
       <c r="C470" s="8" t="s">
@@ -33912,7 +33945,7 @@
       <c r="A471" s="8" t="s">
         <v>1276</v>
       </c>
-      <c r="B471" s="16">
+      <c r="B471" s="17">
         <v>0</v>
       </c>
       <c r="C471" s="8" t="s">
@@ -33968,7 +34001,7 @@
       <c r="A472" s="8" t="s">
         <v>1279</v>
       </c>
-      <c r="B472" s="16">
+      <c r="B472" s="17">
         <v>0</v>
       </c>
       <c r="C472" s="8" t="s">
@@ -34024,7 +34057,7 @@
       <c r="A473" s="8" t="s">
         <v>1282</v>
       </c>
-      <c r="B473" s="16">
+      <c r="B473" s="17">
         <v>0</v>
       </c>
       <c r="C473" s="8" t="s">
@@ -34080,7 +34113,7 @@
       <c r="A474" s="8" t="s">
         <v>1285</v>
       </c>
-      <c r="B474" s="16">
+      <c r="B474" s="17">
         <v>0</v>
       </c>
       <c r="C474" s="8" t="s">
@@ -34136,7 +34169,7 @@
       <c r="A475" s="8" t="s">
         <v>1288</v>
       </c>
-      <c r="B475" s="16">
+      <c r="B475" s="17">
         <v>0</v>
       </c>
       <c r="C475" s="8" t="s">
@@ -34192,7 +34225,7 @@
       <c r="A476" s="8" t="s">
         <v>1291</v>
       </c>
-      <c r="B476" s="16">
+      <c r="B476" s="17">
         <v>0</v>
       </c>
       <c r="C476" s="8" t="s">
@@ -34248,7 +34281,7 @@
       <c r="A477" s="8" t="s">
         <v>1296</v>
       </c>
-      <c r="B477" s="16">
+      <c r="B477" s="17">
         <v>0</v>
       </c>
       <c r="C477" s="8" t="s">
@@ -34304,7 +34337,7 @@
       <c r="A478" s="8" t="s">
         <v>1300</v>
       </c>
-      <c r="B478" s="16">
+      <c r="B478" s="17">
         <v>0</v>
       </c>
       <c r="C478" s="8" t="s">
@@ -34360,7 +34393,7 @@
       <c r="A479" s="8" t="s">
         <v>1303</v>
       </c>
-      <c r="B479" s="16">
+      <c r="B479" s="17">
         <v>0</v>
       </c>
       <c r="C479" s="8" t="s">
@@ -34416,7 +34449,7 @@
       <c r="A480" s="8" t="s">
         <v>1306</v>
       </c>
-      <c r="B480" s="16">
+      <c r="B480" s="17">
         <v>0</v>
       </c>
       <c r="C480" s="8" t="s">
@@ -34472,7 +34505,7 @@
       <c r="A481" s="8" t="s">
         <v>1309</v>
       </c>
-      <c r="B481" s="16">
+      <c r="B481" s="17">
         <v>0</v>
       </c>
       <c r="C481" s="8" t="s">
@@ -34528,7 +34561,7 @@
       <c r="A482" s="8" t="s">
         <v>1312</v>
       </c>
-      <c r="B482" s="16">
+      <c r="B482" s="17">
         <v>0</v>
       </c>
       <c r="C482" s="8" t="s">
@@ -34584,7 +34617,7 @@
       <c r="A483" s="8" t="s">
         <v>1315</v>
       </c>
-      <c r="B483" s="16">
+      <c r="B483" s="17">
         <v>0</v>
       </c>
       <c r="C483" s="8" t="s">
@@ -34640,7 +34673,7 @@
       <c r="A484" s="8" t="s">
         <v>1318</v>
       </c>
-      <c r="B484" s="16">
+      <c r="B484" s="17">
         <v>0</v>
       </c>
       <c r="C484" s="8" t="s">
@@ -34696,7 +34729,7 @@
       <c r="A485" s="8" t="s">
         <v>1321</v>
       </c>
-      <c r="B485" s="16">
+      <c r="B485" s="17">
         <v>0</v>
       </c>
       <c r="C485" s="8" t="s">
@@ -34752,7 +34785,7 @@
       <c r="A486" s="8" t="s">
         <v>1324</v>
       </c>
-      <c r="B486" s="16">
+      <c r="B486" s="17">
         <v>0</v>
       </c>
       <c r="C486" s="8" t="s">
@@ -34808,7 +34841,7 @@
       <c r="A487" s="8" t="s">
         <v>1326</v>
       </c>
-      <c r="B487" s="16">
+      <c r="B487" s="17">
         <v>0</v>
       </c>
       <c r="C487" s="8" t="s">
@@ -34864,7 +34897,7 @@
       <c r="A488" s="8" t="s">
         <v>1328</v>
       </c>
-      <c r="B488" s="16">
+      <c r="B488" s="17">
         <v>0</v>
       </c>
       <c r="C488" s="8" t="s">
@@ -34920,7 +34953,7 @@
       <c r="A489" s="8" t="s">
         <v>1330</v>
       </c>
-      <c r="B489" s="16">
+      <c r="B489" s="17">
         <v>0</v>
       </c>
       <c r="C489" s="8" t="s">
@@ -34976,7 +35009,7 @@
       <c r="A490" s="8" t="s">
         <v>1332</v>
       </c>
-      <c r="B490" s="16">
+      <c r="B490" s="17">
         <v>0</v>
       </c>
       <c r="C490" s="8" t="s">
@@ -35032,7 +35065,7 @@
       <c r="A491" s="8" t="s">
         <v>1335</v>
       </c>
-      <c r="B491" s="16">
+      <c r="B491" s="17">
         <v>0</v>
       </c>
       <c r="C491" s="8" t="s">
@@ -35088,7 +35121,7 @@
       <c r="A492" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="B492" s="16">
+      <c r="B492" s="17">
         <v>0</v>
       </c>
       <c r="C492" s="8" t="s">
@@ -35144,7 +35177,7 @@
       <c r="A493" s="8" t="s">
         <v>1339</v>
       </c>
-      <c r="B493" s="16">
+      <c r="B493" s="17">
         <v>0</v>
       </c>
       <c r="C493" s="8" t="s">
@@ -35200,7 +35233,7 @@
       <c r="A494" s="8" t="s">
         <v>1341</v>
       </c>
-      <c r="B494" s="16">
+      <c r="B494" s="17">
         <v>0</v>
       </c>
       <c r="C494" s="8" t="s">
@@ -35256,7 +35289,7 @@
       <c r="A495" s="8" t="s">
         <v>1344</v>
       </c>
-      <c r="B495" s="16">
+      <c r="B495" s="17">
         <v>0</v>
       </c>
       <c r="C495" s="8" t="s">
@@ -35312,7 +35345,7 @@
       <c r="A496" s="8" t="s">
         <v>1346</v>
       </c>
-      <c r="B496" s="16">
+      <c r="B496" s="17">
         <v>0</v>
       </c>
       <c r="C496" s="8" t="s">
@@ -35368,7 +35401,7 @@
       <c r="A497" s="8" t="s">
         <v>1349</v>
       </c>
-      <c r="B497" s="16">
+      <c r="B497" s="17">
         <v>0</v>
       </c>
       <c r="C497" s="8" t="s">
@@ -35424,7 +35457,7 @@
       <c r="A498" s="8" t="s">
         <v>1352</v>
       </c>
-      <c r="B498" s="16">
+      <c r="B498" s="17">
         <v>0</v>
       </c>
       <c r="C498" s="8" t="s">
@@ -35480,7 +35513,7 @@
       <c r="A499" s="8" t="s">
         <v>1354</v>
       </c>
-      <c r="B499" s="16">
+      <c r="B499" s="17">
         <v>0</v>
       </c>
       <c r="C499" s="8" t="s">
@@ -35536,7 +35569,7 @@
       <c r="A500" s="8" t="s">
         <v>1356</v>
       </c>
-      <c r="B500" s="16">
+      <c r="B500" s="17">
         <v>0</v>
       </c>
       <c r="C500" s="8" t="s">
@@ -35592,7 +35625,7 @@
       <c r="A501" s="8" t="s">
         <v>1358</v>
       </c>
-      <c r="B501" s="16">
+      <c r="B501" s="17">
         <v>0</v>
       </c>
       <c r="C501" s="8" t="s">
@@ -35648,7 +35681,7 @@
       <c r="A502" s="8" t="s">
         <v>1360</v>
       </c>
-      <c r="B502" s="16">
+      <c r="B502" s="17">
         <v>0</v>
       </c>
       <c r="C502" s="8" t="s">
@@ -35704,7 +35737,7 @@
       <c r="A503" s="8" t="s">
         <v>1362</v>
       </c>
-      <c r="B503" s="16">
+      <c r="B503" s="17">
         <v>0</v>
       </c>
       <c r="C503" s="8" t="s">
@@ -35760,7 +35793,7 @@
       <c r="A504" s="8" t="s">
         <v>1363</v>
       </c>
-      <c r="B504" s="16">
+      <c r="B504" s="17">
         <v>0</v>
       </c>
       <c r="C504" s="8" t="s">
@@ -35816,7 +35849,7 @@
       <c r="A505" s="8" t="s">
         <v>1366</v>
       </c>
-      <c r="B505" s="16">
+      <c r="B505" s="17">
         <v>0</v>
       </c>
       <c r="C505" s="8" t="s">
@@ -35872,7 +35905,7 @@
       <c r="A506" s="8" t="s">
         <v>1368</v>
       </c>
-      <c r="B506" s="16">
+      <c r="B506" s="17">
         <v>0</v>
       </c>
       <c r="C506" s="8" t="s">
@@ -35928,7 +35961,7 @@
       <c r="A507" s="8" t="s">
         <v>1370</v>
       </c>
-      <c r="B507" s="16">
+      <c r="B507" s="17">
         <v>0</v>
       </c>
       <c r="C507" s="8" t="s">
@@ -35984,7 +36017,7 @@
       <c r="A508" s="8" t="s">
         <v>1372</v>
       </c>
-      <c r="B508" s="16">
+      <c r="B508" s="17">
         <v>0</v>
       </c>
       <c r="C508" s="8" t="s">
@@ -36040,7 +36073,7 @@
       <c r="A509" s="8" t="s">
         <v>1374</v>
       </c>
-      <c r="B509" s="16">
+      <c r="B509" s="17">
         <v>0</v>
       </c>
       <c r="C509" s="8" t="s">
@@ -36096,7 +36129,7 @@
       <c r="A510" s="8" t="s">
         <v>1377</v>
       </c>
-      <c r="B510" s="16">
+      <c r="B510" s="17">
         <v>0</v>
       </c>
       <c r="C510" s="8" t="s">
@@ -36152,7 +36185,7 @@
       <c r="A511" s="8" t="s">
         <v>1380</v>
       </c>
-      <c r="B511" s="16">
+      <c r="B511" s="17">
         <v>0</v>
       </c>
       <c r="C511" s="8" t="s">
@@ -36208,7 +36241,7 @@
       <c r="A512" s="8" t="s">
         <v>1383</v>
       </c>
-      <c r="B512" s="16">
+      <c r="B512" s="17">
         <v>0</v>
       </c>
       <c r="C512" s="8" t="s">
@@ -36264,7 +36297,7 @@
       <c r="A513" s="8" t="s">
         <v>1386</v>
       </c>
-      <c r="B513" s="16">
+      <c r="B513" s="17">
         <v>0</v>
       </c>
       <c r="C513" s="8" t="s">
@@ -36320,7 +36353,7 @@
       <c r="A514" s="8" t="s">
         <v>1389</v>
       </c>
-      <c r="B514" s="16">
+      <c r="B514" s="17">
         <v>0</v>
       </c>
       <c r="C514" s="8" t="s">
@@ -36376,7 +36409,7 @@
       <c r="A515" s="8" t="s">
         <v>1392</v>
       </c>
-      <c r="B515" s="16">
+      <c r="B515" s="17">
         <v>0</v>
       </c>
       <c r="C515" s="8" t="s">
@@ -36432,7 +36465,7 @@
       <c r="A516" s="8" t="s">
         <v>1395</v>
       </c>
-      <c r="B516" s="16">
+      <c r="B516" s="17">
         <v>0</v>
       </c>
       <c r="C516" s="8" t="s">
@@ -36488,7 +36521,7 @@
       <c r="A517" s="8" t="s">
         <v>1397</v>
       </c>
-      <c r="B517" s="16">
+      <c r="B517" s="17">
         <v>0</v>
       </c>
       <c r="C517" s="8" t="s">
@@ -36544,7 +36577,7 @@
       <c r="A518" s="8" t="s">
         <v>1404</v>
       </c>
-      <c r="B518" s="16">
+      <c r="B518" s="17">
         <v>0</v>
       </c>
       <c r="C518" s="8" t="s">
@@ -36600,7 +36633,7 @@
       <c r="A519" s="8" t="s">
         <v>1407</v>
       </c>
-      <c r="B519" s="16">
+      <c r="B519" s="17">
         <v>0</v>
       </c>
       <c r="C519" s="8" t="s">
@@ -36656,7 +36689,7 @@
       <c r="A520" s="8" t="s">
         <v>1410</v>
       </c>
-      <c r="B520" s="16">
+      <c r="B520" s="17">
         <v>0</v>
       </c>
       <c r="C520" s="8" t="s">
@@ -36712,7 +36745,7 @@
       <c r="A521" s="8" t="s">
         <v>1413</v>
       </c>
-      <c r="B521" s="16">
+      <c r="B521" s="17">
         <v>0</v>
       </c>
       <c r="C521" s="8" t="s">
@@ -36768,7 +36801,7 @@
       <c r="A522" s="8" t="s">
         <v>1416</v>
       </c>
-      <c r="B522" s="16">
+      <c r="B522" s="17">
         <v>0</v>
       </c>
       <c r="C522" s="8" t="s">
@@ -36824,7 +36857,7 @@
       <c r="A523" s="8" t="s">
         <v>1421</v>
       </c>
-      <c r="B523" s="16">
+      <c r="B523" s="17">
         <v>0</v>
       </c>
       <c r="C523" s="8" t="s">
@@ -36880,7 +36913,7 @@
       <c r="A524" s="8" t="s">
         <v>1424</v>
       </c>
-      <c r="B524" s="16">
+      <c r="B524" s="17">
         <v>0</v>
       </c>
       <c r="C524" s="8" t="s">
@@ -36936,7 +36969,7 @@
       <c r="A525" s="8" t="s">
         <v>1427</v>
       </c>
-      <c r="B525" s="16">
+      <c r="B525" s="17">
         <v>0</v>
       </c>
       <c r="C525" s="8" t="s">
@@ -36992,7 +37025,7 @@
       <c r="A526" s="8" t="s">
         <v>1429</v>
       </c>
-      <c r="B526" s="16">
+      <c r="B526" s="17">
         <v>0</v>
       </c>
       <c r="C526" s="8" t="s">
@@ -37048,7 +37081,7 @@
       <c r="A527" s="8" t="s">
         <v>1431</v>
       </c>
-      <c r="B527" s="16">
+      <c r="B527" s="17">
         <v>0</v>
       </c>
       <c r="C527" s="8" t="s">
@@ -37104,7 +37137,7 @@
       <c r="A528" s="8" t="s">
         <v>1433</v>
       </c>
-      <c r="B528" s="16">
+      <c r="B528" s="17">
         <v>0</v>
       </c>
       <c r="C528" s="8" t="s">
@@ -37160,7 +37193,7 @@
       <c r="A529" s="8" t="s">
         <v>1436</v>
       </c>
-      <c r="B529" s="16">
+      <c r="B529" s="17">
         <v>0</v>
       </c>
       <c r="C529" s="8" t="s">
@@ -37216,7 +37249,7 @@
       <c r="A530" s="8" t="s">
         <v>1439</v>
       </c>
-      <c r="B530" s="16">
+      <c r="B530" s="17">
         <v>0</v>
       </c>
       <c r="C530" s="8" t="s">
@@ -37272,7 +37305,7 @@
       <c r="A531" s="8" t="s">
         <v>1442</v>
       </c>
-      <c r="B531" s="16">
+      <c r="B531" s="17">
         <v>0</v>
       </c>
       <c r="C531" s="8" t="s">
@@ -37328,7 +37361,7 @@
       <c r="A532" s="8" t="s">
         <v>1444</v>
       </c>
-      <c r="B532" s="16">
+      <c r="B532" s="17">
         <v>0</v>
       </c>
       <c r="C532" s="8" t="s">
@@ -37384,7 +37417,7 @@
       <c r="A533" s="8" t="s">
         <v>1446</v>
       </c>
-      <c r="B533" s="16">
+      <c r="B533" s="17">
         <v>0</v>
       </c>
       <c r="C533" s="8" t="s">
@@ -37440,7 +37473,7 @@
       <c r="A534" s="8" t="s">
         <v>1448</v>
       </c>
-      <c r="B534" s="16">
+      <c r="B534" s="17">
         <v>0</v>
       </c>
       <c r="C534" s="8" t="s">
@@ -37496,7 +37529,7 @@
       <c r="A535" s="8" t="s">
         <v>1450</v>
       </c>
-      <c r="B535" s="16">
+      <c r="B535" s="17">
         <v>0</v>
       </c>
       <c r="C535" s="8" t="s">
@@ -37552,7 +37585,7 @@
       <c r="A536" s="8" t="s">
         <v>1452</v>
       </c>
-      <c r="B536" s="16">
+      <c r="B536" s="17">
         <v>0</v>
       </c>
       <c r="C536" s="8" t="s">
@@ -37608,7 +37641,7 @@
       <c r="A537" s="8" t="s">
         <v>1454</v>
       </c>
-      <c r="B537" s="16">
+      <c r="B537" s="17">
         <v>0</v>
       </c>
       <c r="C537" s="8" t="s">
@@ -37664,7 +37697,7 @@
       <c r="A538" s="8" t="s">
         <v>1456</v>
       </c>
-      <c r="B538" s="16">
+      <c r="B538" s="17">
         <v>0</v>
       </c>
       <c r="C538" s="8" t="s">
@@ -37720,7 +37753,7 @@
       <c r="A539" s="8" t="s">
         <v>1458</v>
       </c>
-      <c r="B539" s="16">
+      <c r="B539" s="17">
         <v>0</v>
       </c>
       <c r="C539" s="8" t="s">
@@ -37776,7 +37809,7 @@
       <c r="A540" s="8" t="s">
         <v>1460</v>
       </c>
-      <c r="B540" s="16">
+      <c r="B540" s="17">
         <v>0</v>
       </c>
       <c r="C540" s="8" t="s">
@@ -37832,7 +37865,7 @@
       <c r="A541" s="8" t="s">
         <v>1463</v>
       </c>
-      <c r="B541" s="16">
+      <c r="B541" s="17">
         <v>0</v>
       </c>
       <c r="C541" s="8" t="s">
@@ -37888,7 +37921,7 @@
       <c r="A542" s="8" t="s">
         <v>1466</v>
       </c>
-      <c r="B542" s="16">
+      <c r="B542" s="17">
         <v>0</v>
       </c>
       <c r="C542" s="8" t="s">
@@ -37944,7 +37977,7 @@
       <c r="A543" s="8" t="s">
         <v>1468</v>
       </c>
-      <c r="B543" s="16">
+      <c r="B543" s="17">
         <v>0</v>
       </c>
       <c r="C543" s="8" t="s">
@@ -38000,7 +38033,7 @@
       <c r="A544" s="8" t="s">
         <v>1470</v>
       </c>
-      <c r="B544" s="16">
+      <c r="B544" s="17">
         <v>0</v>
       </c>
       <c r="C544" s="8" t="s">
@@ -38056,7 +38089,7 @@
       <c r="A545" s="8" t="s">
         <v>1472</v>
       </c>
-      <c r="B545" s="16">
+      <c r="B545" s="17">
         <v>0</v>
       </c>
       <c r="C545" s="8" t="s">
@@ -38112,7 +38145,7 @@
       <c r="A546" s="8" t="s">
         <v>1474</v>
       </c>
-      <c r="B546" s="16">
+      <c r="B546" s="17">
         <v>0</v>
       </c>
       <c r="C546" s="8" t="s">
@@ -38168,7 +38201,7 @@
       <c r="A547" s="8" t="s">
         <v>1476</v>
       </c>
-      <c r="B547" s="16">
+      <c r="B547" s="17">
         <v>0</v>
       </c>
       <c r="C547" s="8" t="s">
@@ -38224,7 +38257,7 @@
       <c r="A548" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="B548" s="16">
+      <c r="B548" s="17">
         <v>0</v>
       </c>
       <c r="C548" s="8" t="s">
@@ -38280,7 +38313,7 @@
       <c r="A549" s="8" t="s">
         <v>1480</v>
       </c>
-      <c r="B549" s="16">
+      <c r="B549" s="17">
         <v>0</v>
       </c>
       <c r="C549" s="8" t="s">
@@ -38336,7 +38369,7 @@
       <c r="A550" s="8" t="s">
         <v>1482</v>
       </c>
-      <c r="B550" s="16">
+      <c r="B550" s="17">
         <v>0</v>
       </c>
       <c r="C550" s="8" t="s">
@@ -38392,7 +38425,7 @@
       <c r="A551" s="8" t="s">
         <v>1484</v>
       </c>
-      <c r="B551" s="16">
+      <c r="B551" s="17">
         <v>0</v>
       </c>
       <c r="C551" s="8" t="s">
@@ -38448,7 +38481,7 @@
       <c r="A552" s="8" t="s">
         <v>1487</v>
       </c>
-      <c r="B552" s="16">
+      <c r="B552" s="17">
         <v>0</v>
       </c>
       <c r="C552" s="8" t="s">
@@ -38504,7 +38537,7 @@
       <c r="A553" s="8" t="s">
         <v>1489</v>
       </c>
-      <c r="B553" s="16">
+      <c r="B553" s="17">
         <v>0</v>
       </c>
       <c r="C553" s="8" t="s">
@@ -38560,7 +38593,7 @@
       <c r="A554" s="8" t="s">
         <v>1492</v>
       </c>
-      <c r="B554" s="16">
+      <c r="B554" s="17">
         <v>0</v>
       </c>
       <c r="C554" s="8" t="s">
@@ -38616,7 +38649,7 @@
       <c r="A555" s="8" t="s">
         <v>1497</v>
       </c>
-      <c r="B555" s="16">
+      <c r="B555" s="17">
         <v>0</v>
       </c>
       <c r="C555" s="8" t="s">
@@ -38672,7 +38705,7 @@
       <c r="A556" s="8" t="s">
         <v>1500</v>
       </c>
-      <c r="B556" s="16">
+      <c r="B556" s="17">
         <v>0</v>
       </c>
       <c r="C556" s="8" t="s">
@@ -38728,7 +38761,7 @@
       <c r="A557" s="8" t="s">
         <v>1501</v>
       </c>
-      <c r="B557" s="16">
+      <c r="B557" s="17">
         <v>0</v>
       </c>
       <c r="C557" s="8" t="s">
@@ -38784,7 +38817,7 @@
       <c r="A558" s="8" t="s">
         <v>1502</v>
       </c>
-      <c r="B558" s="16">
+      <c r="B558" s="17">
         <v>0</v>
       </c>
       <c r="C558" s="8" t="s">
@@ -38840,7 +38873,7 @@
       <c r="A559" s="8" t="s">
         <v>1503</v>
       </c>
-      <c r="B559" s="16">
+      <c r="B559" s="17">
         <v>0</v>
       </c>
       <c r="C559" s="8" t="s">
@@ -38896,7 +38929,7 @@
       <c r="A560" s="8" t="s">
         <v>1506</v>
       </c>
-      <c r="B560" s="16">
+      <c r="B560" s="17">
         <v>0</v>
       </c>
       <c r="C560" s="8" t="s">
@@ -38952,7 +38985,7 @@
       <c r="A561" s="8" t="s">
         <v>1508</v>
       </c>
-      <c r="B561" s="16">
+      <c r="B561" s="17">
         <v>0</v>
       </c>
       <c r="C561" s="8" t="s">
@@ -39008,7 +39041,7 @@
       <c r="A562" s="8" t="s">
         <v>1510</v>
       </c>
-      <c r="B562" s="16">
+      <c r="B562" s="17">
         <v>0</v>
       </c>
       <c r="C562" s="8" t="s">
@@ -39064,7 +39097,7 @@
       <c r="A563" s="8" t="s">
         <v>1512</v>
       </c>
-      <c r="B563" s="16">
+      <c r="B563" s="17">
         <v>0</v>
       </c>
       <c r="C563" s="8" t="s">
@@ -39120,7 +39153,7 @@
       <c r="A564" s="8" t="s">
         <v>1514</v>
       </c>
-      <c r="B564" s="16">
+      <c r="B564" s="17">
         <v>0</v>
       </c>
       <c r="C564" s="8" t="s">
@@ -39176,7 +39209,7 @@
       <c r="A565" s="8" t="s">
         <v>1517</v>
       </c>
-      <c r="B565" s="16">
+      <c r="B565" s="17">
         <v>0</v>
       </c>
       <c r="C565" s="8" t="s">
@@ -39232,7 +39265,7 @@
       <c r="A566" s="8" t="s">
         <v>1520</v>
       </c>
-      <c r="B566" s="16">
+      <c r="B566" s="17">
         <v>0</v>
       </c>
       <c r="C566" s="8" t="s">
@@ -39288,7 +39321,7 @@
       <c r="A567" s="8" t="s">
         <v>1523</v>
       </c>
-      <c r="B567" s="16">
+      <c r="B567" s="17">
         <v>0</v>
       </c>
       <c r="C567" s="8" t="s">
@@ -39344,7 +39377,7 @@
       <c r="A568" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="B568" s="16">
+      <c r="B568" s="17">
         <v>0</v>
       </c>
       <c r="C568" s="8" t="s">
@@ -39400,7 +39433,7 @@
       <c r="A569" s="8" t="s">
         <v>1529</v>
       </c>
-      <c r="B569" s="16">
+      <c r="B569" s="17">
         <v>0</v>
       </c>
       <c r="C569" s="8" t="s">
@@ -39456,7 +39489,7 @@
       <c r="A570" s="8" t="s">
         <v>1532</v>
       </c>
-      <c r="B570" s="16">
+      <c r="B570" s="17">
         <v>0</v>
       </c>
       <c r="C570" s="8" t="s">
@@ -39512,7 +39545,7 @@
       <c r="A571" s="8" t="s">
         <v>1535</v>
       </c>
-      <c r="B571" s="16">
+      <c r="B571" s="17">
         <v>0</v>
       </c>
       <c r="C571" s="8" t="s">
@@ -39568,7 +39601,7 @@
       <c r="A572" s="8" t="s">
         <v>1538</v>
       </c>
-      <c r="B572" s="16">
+      <c r="B572" s="17">
         <v>0</v>
       </c>
       <c r="C572" s="8" t="s">
@@ -39624,7 +39657,7 @@
       <c r="A573" s="8" t="s">
         <v>1541</v>
       </c>
-      <c r="B573" s="16">
+      <c r="B573" s="17">
         <v>0</v>
       </c>
       <c r="C573" s="8" t="s">
@@ -39680,7 +39713,7 @@
       <c r="A574" s="8" t="s">
         <v>1544</v>
       </c>
-      <c r="B574" s="16">
+      <c r="B574" s="17">
         <v>0</v>
       </c>
       <c r="C574" s="8" t="s">
@@ -39736,7 +39769,7 @@
       <c r="A575" s="8" t="s">
         <v>1547</v>
       </c>
-      <c r="B575" s="16">
+      <c r="B575" s="17">
         <v>0</v>
       </c>
       <c r="C575" s="8" t="s">
@@ -39792,7 +39825,7 @@
       <c r="A576" s="8" t="s">
         <v>1550</v>
       </c>
-      <c r="B576" s="16">
+      <c r="B576" s="17">
         <v>0</v>
       </c>
       <c r="C576" s="8" t="s">
@@ -39848,7 +39881,7 @@
       <c r="A577" s="8" t="s">
         <v>1553</v>
       </c>
-      <c r="B577" s="16">
+      <c r="B577" s="17">
         <v>0</v>
       </c>
       <c r="C577" s="8" t="s">
@@ -39904,7 +39937,7 @@
       <c r="A578" s="8" t="s">
         <v>1556</v>
       </c>
-      <c r="B578" s="16">
+      <c r="B578" s="17">
         <v>0</v>
       </c>
       <c r="C578" s="8" t="s">
@@ -39960,7 +39993,7 @@
       <c r="A579" s="8" t="s">
         <v>1559</v>
       </c>
-      <c r="B579" s="16">
+      <c r="B579" s="17">
         <v>0</v>
       </c>
       <c r="C579" s="8" t="s">
@@ -40016,7 +40049,7 @@
       <c r="A580" s="8" t="s">
         <v>1562</v>
       </c>
-      <c r="B580" s="16">
+      <c r="B580" s="17">
         <v>0</v>
       </c>
       <c r="C580" s="8" t="s">
@@ -40072,7 +40105,7 @@
       <c r="A581" s="8" t="s">
         <v>1565</v>
       </c>
-      <c r="B581" s="16">
+      <c r="B581" s="17">
         <v>0</v>
       </c>
       <c r="C581" s="8" t="s">
@@ -40128,7 +40161,7 @@
       <c r="A582" s="8" t="s">
         <v>1568</v>
       </c>
-      <c r="B582" s="16">
+      <c r="B582" s="17">
         <v>0</v>
       </c>
       <c r="C582" s="8" t="s">
@@ -40184,7 +40217,7 @@
       <c r="A583" s="8" t="s">
         <v>1571</v>
       </c>
-      <c r="B583" s="16">
+      <c r="B583" s="17">
         <v>0</v>
       </c>
       <c r="C583" s="8" t="s">
@@ -40240,7 +40273,7 @@
       <c r="A584" s="8" t="s">
         <v>1574</v>
       </c>
-      <c r="B584" s="16">
+      <c r="B584" s="17">
         <v>0</v>
       </c>
       <c r="C584" s="8" t="s">
@@ -40296,7 +40329,7 @@
       <c r="A585" s="8" t="s">
         <v>1577</v>
       </c>
-      <c r="B585" s="16">
+      <c r="B585" s="17">
         <v>0</v>
       </c>
       <c r="C585" s="8" t="s">
@@ -40352,7 +40385,7 @@
       <c r="A586" s="8" t="s">
         <v>1580</v>
       </c>
-      <c r="B586" s="16">
+      <c r="B586" s="17">
         <v>0</v>
       </c>
       <c r="C586" s="8" t="s">
@@ -40408,7 +40441,7 @@
       <c r="A587" s="8" t="s">
         <v>1583</v>
       </c>
-      <c r="B587" s="16">
+      <c r="B587" s="17">
         <v>0</v>
       </c>
       <c r="C587" s="8" t="s">
@@ -40464,7 +40497,7 @@
       <c r="A588" s="8" t="s">
         <v>1586</v>
       </c>
-      <c r="B588" s="16">
+      <c r="B588" s="17">
         <v>0</v>
       </c>
       <c r="C588" s="8" t="s">
@@ -40520,7 +40553,7 @@
       <c r="A589" s="8" t="s">
         <v>1589</v>
       </c>
-      <c r="B589" s="16">
+      <c r="B589" s="17">
         <v>0</v>
       </c>
       <c r="C589" s="8" t="s">
@@ -40576,7 +40609,7 @@
       <c r="A590" s="8" t="s">
         <v>1592</v>
       </c>
-      <c r="B590" s="16">
+      <c r="B590" s="17">
         <v>0</v>
       </c>
       <c r="C590" s="8" t="s">
@@ -40632,7 +40665,7 @@
       <c r="A591" s="8" t="s">
         <v>1594</v>
       </c>
-      <c r="B591" s="16">
+      <c r="B591" s="17">
         <v>0</v>
       </c>
       <c r="C591" s="8" t="s">
@@ -40688,7 +40721,7 @@
       <c r="A592" s="8" t="s">
         <v>1596</v>
       </c>
-      <c r="B592" s="16">
+      <c r="B592" s="17">
         <v>0</v>
       </c>
       <c r="C592" s="8" t="s">
@@ -40744,7 +40777,7 @@
       <c r="A593" s="8" t="s">
         <v>1598</v>
       </c>
-      <c r="B593" s="16">
+      <c r="B593" s="17">
         <v>0</v>
       </c>
       <c r="C593" s="8" t="s">
@@ -40800,7 +40833,7 @@
       <c r="A594" s="8" t="s">
         <v>1601</v>
       </c>
-      <c r="B594" s="16">
+      <c r="B594" s="17">
         <v>0</v>
       </c>
       <c r="C594" s="8" t="s">
@@ -40856,7 +40889,7 @@
       <c r="A595" s="8" t="s">
         <v>1604</v>
       </c>
-      <c r="B595" s="16">
+      <c r="B595" s="17">
         <v>0</v>
       </c>
       <c r="C595" s="8" t="s">
@@ -40912,7 +40945,7 @@
       <c r="A596" s="8" t="s">
         <v>1607</v>
       </c>
-      <c r="B596" s="16">
+      <c r="B596" s="17">
         <v>0</v>
       </c>
       <c r="C596" s="8" t="s">
@@ -40968,7 +41001,7 @@
       <c r="A597" s="8" t="s">
         <v>1610</v>
       </c>
-      <c r="B597" s="16">
+      <c r="B597" s="17">
         <v>0</v>
       </c>
       <c r="C597" s="8" t="s">
@@ -41024,7 +41057,7 @@
       <c r="A598" s="8" t="s">
         <v>1612</v>
       </c>
-      <c r="B598" s="16">
+      <c r="B598" s="17">
         <v>0</v>
       </c>
       <c r="C598" s="8" t="s">
@@ -41080,7 +41113,7 @@
       <c r="A599" s="8" t="s">
         <v>1614</v>
       </c>
-      <c r="B599" s="16">
+      <c r="B599" s="17">
         <v>0</v>
       </c>
       <c r="C599" s="8" t="s">
@@ -41136,7 +41169,7 @@
       <c r="A600" s="8" t="s">
         <v>1616</v>
       </c>
-      <c r="B600" s="16">
+      <c r="B600" s="17">
         <v>0</v>
       </c>
       <c r="C600" s="8" t="s">
@@ -41192,7 +41225,7 @@
       <c r="A601" s="8" t="s">
         <v>1618</v>
       </c>
-      <c r="B601" s="16">
+      <c r="B601" s="17">
         <v>0</v>
       </c>
       <c r="C601" s="8" t="s">
@@ -41248,7 +41281,7 @@
       <c r="A602" s="8" t="s">
         <v>1619</v>
       </c>
-      <c r="B602" s="16">
+      <c r="B602" s="17">
         <v>0</v>
       </c>
       <c r="C602" s="8" t="s">
@@ -41304,7 +41337,7 @@
       <c r="A603" s="8" t="s">
         <v>1622</v>
       </c>
-      <c r="B603" s="16">
+      <c r="B603" s="17">
         <v>0</v>
       </c>
       <c r="C603" s="8" t="s">
@@ -41360,7 +41393,7 @@
       <c r="A604" s="8" t="s">
         <v>1625</v>
       </c>
-      <c r="B604" s="16">
+      <c r="B604" s="17">
         <v>0</v>
       </c>
       <c r="C604" s="8" t="s">
@@ -41416,7 +41449,7 @@
       <c r="A605" s="8" t="s">
         <v>1628</v>
       </c>
-      <c r="B605" s="16">
+      <c r="B605" s="17">
         <v>0</v>
       </c>
       <c r="C605" s="8" t="s">
@@ -41472,7 +41505,7 @@
       <c r="A606" s="8" t="s">
         <v>1631</v>
       </c>
-      <c r="B606" s="16">
+      <c r="B606" s="17">
         <v>0</v>
       </c>
       <c r="C606" s="8" t="s">
@@ -41528,7 +41561,7 @@
       <c r="A607" s="8" t="s">
         <v>1634</v>
       </c>
-      <c r="B607" s="16">
+      <c r="B607" s="17">
         <v>0</v>
       </c>
       <c r="C607" s="8" t="s">
@@ -41584,7 +41617,7 @@
       <c r="A608" s="8" t="s">
         <v>1637</v>
       </c>
-      <c r="B608" s="16">
+      <c r="B608" s="17">
         <v>0</v>
       </c>
       <c r="C608" s="8" t="s">
@@ -41640,7 +41673,7 @@
       <c r="A609" s="8" t="s">
         <v>1640</v>
       </c>
-      <c r="B609" s="16">
+      <c r="B609" s="17">
         <v>0</v>
       </c>
       <c r="C609" s="8" t="s">
@@ -41696,7 +41729,7 @@
       <c r="A610" s="8" t="s">
         <v>1643</v>
       </c>
-      <c r="B610" s="16">
+      <c r="B610" s="17">
         <v>0</v>
       </c>
       <c r="C610" s="8" t="s">
@@ -41752,7 +41785,7 @@
       <c r="A611" s="8" t="s">
         <v>1646</v>
       </c>
-      <c r="B611" s="16">
+      <c r="B611" s="17">
         <v>0</v>
       </c>
       <c r="C611" s="8" t="s">
@@ -41808,7 +41841,7 @@
       <c r="A612" s="8" t="s">
         <v>1649</v>
       </c>
-      <c r="B612" s="16">
+      <c r="B612" s="17">
         <v>0</v>
       </c>
       <c r="C612" s="8" t="s">
@@ -41864,7 +41897,7 @@
       <c r="A613" s="8" t="s">
         <v>1652</v>
       </c>
-      <c r="B613" s="16">
+      <c r="B613" s="17">
         <v>0</v>
       </c>
       <c r="C613" s="8" t="s">
@@ -41920,7 +41953,7 @@
       <c r="A614" s="8" t="s">
         <v>1655</v>
       </c>
-      <c r="B614" s="16">
+      <c r="B614" s="17">
         <v>0</v>
       </c>
       <c r="C614" s="8" t="s">
@@ -41976,7 +42009,7 @@
       <c r="A615" s="8" t="s">
         <v>1658</v>
       </c>
-      <c r="B615" s="16">
+      <c r="B615" s="17">
         <v>0</v>
       </c>
       <c r="C615" s="8" t="s">
@@ -42032,7 +42065,7 @@
       <c r="A616" s="8" t="s">
         <v>1661</v>
       </c>
-      <c r="B616" s="16">
+      <c r="B616" s="17">
         <v>0</v>
       </c>
       <c r="C616" s="8" t="s">
@@ -42088,7 +42121,7 @@
       <c r="A617" s="8" t="s">
         <v>1665</v>
       </c>
-      <c r="B617" s="16">
+      <c r="B617" s="17">
         <v>0</v>
       </c>
       <c r="C617" s="8" t="s">
@@ -42144,7 +42177,7 @@
       <c r="A618" s="8" t="s">
         <v>1668</v>
       </c>
-      <c r="B618" s="16">
+      <c r="B618" s="17">
         <v>0</v>
       </c>
       <c r="C618" s="8" t="s">
@@ -42200,7 +42233,7 @@
       <c r="A619" s="8" t="s">
         <v>1671</v>
       </c>
-      <c r="B619" s="16">
+      <c r="B619" s="17">
         <v>0</v>
       </c>
       <c r="C619" s="8" t="s">
@@ -42256,7 +42289,7 @@
       <c r="A620" s="8" t="s">
         <v>1674</v>
       </c>
-      <c r="B620" s="16">
+      <c r="B620" s="17">
         <v>0</v>
       </c>
       <c r="C620" s="8" t="s">
@@ -42312,7 +42345,7 @@
       <c r="A621" s="8" t="s">
         <v>1677</v>
       </c>
-      <c r="B621" s="16">
+      <c r="B621" s="17">
         <v>0</v>
       </c>
       <c r="C621" s="8" t="s">
@@ -42368,7 +42401,7 @@
       <c r="A622" s="8" t="s">
         <v>1680</v>
       </c>
-      <c r="B622" s="16">
+      <c r="B622" s="17">
         <v>0</v>
       </c>
       <c r="C622" s="8" t="s">
@@ -42424,7 +42457,7 @@
       <c r="A623" s="8" t="s">
         <v>1683</v>
       </c>
-      <c r="B623" s="16">
+      <c r="B623" s="17">
         <v>0</v>
       </c>
       <c r="C623" s="8" t="s">
@@ -42480,7 +42513,7 @@
       <c r="A624" s="8" t="s">
         <v>1686</v>
       </c>
-      <c r="B624" s="16">
+      <c r="B624" s="17">
         <v>0</v>
       </c>
       <c r="C624" s="8" t="s">
@@ -42536,7 +42569,7 @@
       <c r="A625" s="8" t="s">
         <v>1689</v>
       </c>
-      <c r="B625" s="16">
+      <c r="B625" s="17">
         <v>0</v>
       </c>
       <c r="C625" s="8" t="s">
@@ -42592,7 +42625,7 @@
       <c r="A626" s="8" t="s">
         <v>1692</v>
       </c>
-      <c r="B626" s="16">
+      <c r="B626" s="17">
         <v>0</v>
       </c>
       <c r="C626" s="8" t="s">
@@ -42648,7 +42681,7 @@
       <c r="A627" s="8" t="s">
         <v>1694</v>
       </c>
-      <c r="B627" s="16">
+      <c r="B627" s="17">
         <v>0</v>
       </c>
       <c r="C627" s="8" t="s">
@@ -42704,7 +42737,7 @@
       <c r="A628" s="8" t="s">
         <v>1696</v>
       </c>
-      <c r="B628" s="16">
+      <c r="B628" s="17">
         <v>0</v>
       </c>
       <c r="C628" s="8" t="s">
@@ -42760,7 +42793,7 @@
       <c r="A629" s="8" t="s">
         <v>1699</v>
       </c>
-      <c r="B629" s="16">
+      <c r="B629" s="17">
         <v>0</v>
       </c>
       <c r="C629" s="8" t="s">
@@ -42816,7 +42849,7 @@
       <c r="A630" s="8" t="s">
         <v>1702</v>
       </c>
-      <c r="B630" s="16">
+      <c r="B630" s="17">
         <v>0</v>
       </c>
       <c r="C630" s="8" t="s">
@@ -42872,7 +42905,7 @@
       <c r="A631" s="8" t="s">
         <v>1705</v>
       </c>
-      <c r="B631" s="16">
+      <c r="B631" s="17">
         <v>0</v>
       </c>
       <c r="C631" s="8" t="s">
@@ -42928,7 +42961,7 @@
       <c r="A632" s="8" t="s">
         <v>1708</v>
       </c>
-      <c r="B632" s="16">
+      <c r="B632" s="17">
         <v>0</v>
       </c>
       <c r="C632" s="8" t="s">
@@ -42984,7 +43017,7 @@
       <c r="A633" s="8" t="s">
         <v>1711</v>
       </c>
-      <c r="B633" s="16">
+      <c r="B633" s="17">
         <v>0</v>
       </c>
       <c r="C633" s="8" t="s">
@@ -43040,7 +43073,7 @@
       <c r="A634" s="8" t="s">
         <v>1714</v>
       </c>
-      <c r="B634" s="16">
+      <c r="B634" s="17">
         <v>0</v>
       </c>
       <c r="C634" s="8" t="s">
@@ -43096,7 +43129,7 @@
       <c r="A635" s="8" t="s">
         <v>1717</v>
       </c>
-      <c r="B635" s="16">
+      <c r="B635" s="17">
         <v>0</v>
       </c>
       <c r="C635" s="8" t="s">
@@ -43152,7 +43185,7 @@
       <c r="A636" s="8" t="s">
         <v>1720</v>
       </c>
-      <c r="B636" s="16">
+      <c r="B636" s="17">
         <v>0</v>
       </c>
       <c r="C636" s="8" t="s">
@@ -43208,7 +43241,7 @@
       <c r="A637" s="8" t="s">
         <v>1723</v>
       </c>
-      <c r="B637" s="16">
+      <c r="B637" s="17">
         <v>0</v>
       </c>
       <c r="C637" s="8" t="s">
@@ -43264,7 +43297,7 @@
       <c r="A638" s="8" t="s">
         <v>1726</v>
       </c>
-      <c r="B638" s="16">
+      <c r="B638" s="17">
         <v>0</v>
       </c>
       <c r="C638" s="8" t="s">
@@ -43320,7 +43353,7 @@
       <c r="A639" s="8" t="s">
         <v>1729</v>
       </c>
-      <c r="B639" s="16">
+      <c r="B639" s="17">
         <v>0</v>
       </c>
       <c r="C639" s="8" t="s">
@@ -43376,7 +43409,7 @@
       <c r="A640" s="8" t="s">
         <v>1732</v>
       </c>
-      <c r="B640" s="16">
+      <c r="B640" s="17">
         <v>0</v>
       </c>
       <c r="C640" s="8" t="s">
@@ -43432,7 +43465,7 @@
       <c r="A641" s="8" t="s">
         <v>1735</v>
       </c>
-      <c r="B641" s="16">
+      <c r="B641" s="17">
         <v>0</v>
       </c>
       <c r="C641" s="8" t="s">
@@ -43488,7 +43521,7 @@
       <c r="A642" s="8" t="s">
         <v>1739</v>
       </c>
-      <c r="B642" s="16">
+      <c r="B642" s="17">
         <v>0</v>
       </c>
       <c r="C642" s="8" t="s">
@@ -43544,7 +43577,7 @@
       <c r="A643" s="8" t="s">
         <v>1741</v>
       </c>
-      <c r="B643" s="16">
+      <c r="B643" s="17">
         <v>0</v>
       </c>
       <c r="C643" s="8" t="s">
@@ -43600,7 +43633,7 @@
       <c r="A644" s="8" t="s">
         <v>1743</v>
       </c>
-      <c r="B644" s="16">
+      <c r="B644" s="17">
         <v>0</v>
       </c>
       <c r="C644" s="8" t="s">
@@ -43656,7 +43689,7 @@
       <c r="A645" s="8" t="s">
         <v>1746</v>
       </c>
-      <c r="B645" s="16">
+      <c r="B645" s="17">
         <v>0</v>
       </c>
       <c r="C645" s="8" t="s">
@@ -43712,7 +43745,7 @@
       <c r="A646" s="8" t="s">
         <v>1749</v>
       </c>
-      <c r="B646" s="16">
+      <c r="B646" s="17">
         <v>0</v>
       </c>
       <c r="C646" s="8" t="s">
@@ -43768,7 +43801,7 @@
       <c r="A647" s="8" t="s">
         <v>1752</v>
       </c>
-      <c r="B647" s="16">
+      <c r="B647" s="17">
         <v>0</v>
       </c>
       <c r="C647" s="8" t="s">
@@ -43824,7 +43857,7 @@
       <c r="A648" s="8" t="s">
         <v>1755</v>
       </c>
-      <c r="B648" s="16">
+      <c r="B648" s="17">
         <v>0</v>
       </c>
       <c r="C648" s="8" t="s">
@@ -43880,7 +43913,7 @@
       <c r="A649" s="8" t="s">
         <v>1757</v>
       </c>
-      <c r="B649" s="16">
+      <c r="B649" s="17">
         <v>0</v>
       </c>
       <c r="C649" s="8" t="s">
@@ -43936,7 +43969,7 @@
       <c r="A650" s="8" t="s">
         <v>1760</v>
       </c>
-      <c r="B650" s="16">
+      <c r="B650" s="17">
         <v>0</v>
       </c>
       <c r="C650" s="8" t="s">
@@ -43992,7 +44025,7 @@
       <c r="A651" s="8" t="s">
         <v>1763</v>
       </c>
-      <c r="B651" s="16">
+      <c r="B651" s="17">
         <v>0</v>
       </c>
       <c r="C651" s="8" t="s">
@@ -44048,7 +44081,7 @@
       <c r="A652" s="8" t="s">
         <v>1766</v>
       </c>
-      <c r="B652" s="16">
+      <c r="B652" s="17">
         <v>0</v>
       </c>
       <c r="C652" s="8" t="s">
@@ -44104,7 +44137,7 @@
       <c r="A653" s="8" t="s">
         <v>1769</v>
       </c>
-      <c r="B653" s="16">
+      <c r="B653" s="17">
         <v>0</v>
       </c>
       <c r="C653" s="8" t="s">
@@ -44160,7 +44193,7 @@
       <c r="A654" s="8" t="s">
         <v>1772</v>
       </c>
-      <c r="B654" s="16">
+      <c r="B654" s="17">
         <v>0</v>
       </c>
       <c r="C654" s="8" t="s">
@@ -44216,7 +44249,7 @@
       <c r="A655" s="8" t="s">
         <v>1776</v>
       </c>
-      <c r="B655" s="16">
+      <c r="B655" s="17">
         <v>0</v>
       </c>
       <c r="C655" s="8" t="s">
@@ -44272,7 +44305,7 @@
       <c r="A656" s="8" t="s">
         <v>1779</v>
       </c>
-      <c r="B656" s="16">
+      <c r="B656" s="17">
         <v>0</v>
       </c>
       <c r="C656" s="8" t="s">
@@ -44328,7 +44361,7 @@
       <c r="A657" s="8" t="s">
         <v>1782</v>
       </c>
-      <c r="B657" s="16">
+      <c r="B657" s="17">
         <v>0</v>
       </c>
       <c r="C657" s="8" t="s">
@@ -44384,7 +44417,7 @@
       <c r="A658" s="8" t="s">
         <v>1785</v>
       </c>
-      <c r="B658" s="16">
+      <c r="B658" s="17">
         <v>0</v>
       </c>
       <c r="C658" s="8" t="s">
@@ -44440,7 +44473,7 @@
       <c r="A659" s="8" t="s">
         <v>1788</v>
       </c>
-      <c r="B659" s="16">
+      <c r="B659" s="17">
         <v>0</v>
       </c>
       <c r="C659" s="8" t="s">
@@ -44496,7 +44529,7 @@
       <c r="A660" s="8" t="s">
         <v>1791</v>
       </c>
-      <c r="B660" s="16">
+      <c r="B660" s="17">
         <v>0</v>
       </c>
       <c r="C660" s="8" t="s">
@@ -44552,7 +44585,7 @@
       <c r="A661" s="8" t="s">
         <v>1794</v>
       </c>
-      <c r="B661" s="16">
+      <c r="B661" s="17">
         <v>0</v>
       </c>
       <c r="C661" s="8" t="s">
@@ -44608,7 +44641,7 @@
       <c r="A662" s="8" t="s">
         <v>1797</v>
       </c>
-      <c r="B662" s="16">
+      <c r="B662" s="17">
         <v>0</v>
       </c>
       <c r="C662" s="8" t="s">
@@ -44692,159 +44725,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
-        <v>1956</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B2" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B3" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B4" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
-        <v>1959</v>
-      </c>
-      <c r="B5" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="B6" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="B7" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="B8" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="B9" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="B12" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="B14" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B2:B23">
-    <cfRule type="iconSet" priority="2">
-      <iconSet iconSet="3Symbols" showValue="0">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -45455,16 +45335,16 @@
       <c r="G31" s="8"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="11" t="s">
         <v>1941</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="11" t="s">
         <v>1827</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="11" t="s">
         <v>1832</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="11" t="s">
         <v>1836</v>
       </c>
     </row>
@@ -45629,4 +45509,188 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="10" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30">
+      <c r="A8" s="4" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30">
+      <c r="A10" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B23">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Symbols" showValue="0">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967294" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2670" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2670"/>
   </bookViews>
   <sheets>
     <sheet name="Testmatrix" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11460" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11461" uniqueCount="1972">
   <si>
     <t>ID</t>
   </si>
@@ -7195,12 +7195,15 @@
   <si>
     <t>ich habe ein problem wie wie wissen die jobs werden durch modal ertsellt, wenn da ein Fehermeldung ensteht wird es hinter modal angezeigt sodas man e snicht lesen kann behebe das Problem</t>
   </si>
+  <si>
+    <t>wenn ich mein Prilbearbeite zb noch bio hinzufüge, und auf speichern klicke bekomme ich success error meldung nicht</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -7268,7 +7271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7321,6 +7324,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7604,9 +7610,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R662"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14" style="8" customWidth="1"/>
+    <col min="1" max="1" width="14" style="17" customWidth="1"/>
+    <col min="2" max="2" width="14" style="8" customWidth="1"/>
     <col min="3" max="4" width="30" style="8" customWidth="1"/>
     <col min="5" max="5" width="28" style="8" customWidth="1"/>
     <col min="6" max="6" width="22" style="8" customWidth="1"/>
@@ -7621,8 +7628,8 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
@@ -7677,8 +7684,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="12" customFormat="1" ht="75">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:18" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="15">
@@ -7733,8 +7740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="12" customFormat="1" ht="75">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:18" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="15">
@@ -7789,8 +7796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="12" customFormat="1" ht="105">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:18" s="12" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="15">
@@ -7845,8 +7852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="12" customFormat="1" ht="75">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:18" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="15">
@@ -7901,8 +7908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="12" customFormat="1" ht="75">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:18" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="15">
@@ -7957,8 +7964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="12" customFormat="1" ht="75">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:18" s="12" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B7" s="15">
@@ -8013,8 +8020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="75">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="17">
@@ -8069,8 +8076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="75">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="17">
@@ -8125,8 +8132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="75">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="17">
@@ -8181,12 +8188,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="75">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>19</v>
@@ -8237,12 +8244,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="75">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B12" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>19</v>
@@ -8293,12 +8300,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="75">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>19</v>
@@ -8349,12 +8356,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>19</v>
@@ -8405,12 +8412,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="195">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>19</v>
@@ -8461,12 +8468,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="195">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>75</v>
       </c>
       <c r="B16" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>19</v>
@@ -8517,12 +8524,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="195">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>19</v>
@@ -8573,12 +8580,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="195">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>80</v>
       </c>
       <c r="B18" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>19</v>
@@ -8629,12 +8636,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="195">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>82</v>
       </c>
       <c r="B19" s="17">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>19</v>
@@ -8685,12 +8692,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="195">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>84</v>
       </c>
       <c r="B20" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>19</v>
@@ -8741,12 +8748,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="195">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B21" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>19</v>
@@ -8797,12 +8804,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="195">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>89</v>
       </c>
       <c r="B22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>19</v>
@@ -8853,12 +8860,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="195">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>19</v>
@@ -8909,12 +8916,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="195">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>19</v>
@@ -8965,12 +8972,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="195">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>19</v>
@@ -9021,12 +9028,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="195">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>97</v>
       </c>
       <c r="B26" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>19</v>
@@ -9077,8 +9084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="195">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>99</v>
       </c>
       <c r="B27" s="17">
@@ -9133,8 +9140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="195">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
         <v>101</v>
       </c>
       <c r="B28" s="17">
@@ -9189,8 +9196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="195">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>103</v>
       </c>
       <c r="B29" s="17">
@@ -9245,8 +9252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="75">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>105</v>
       </c>
       <c r="B30" s="17">
@@ -9301,12 +9308,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="75">
-      <c r="A31" s="8" t="s">
+    <row r="31" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>108</v>
       </c>
       <c r="B31" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>19</v>
@@ -9357,12 +9364,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="75">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
         <v>110</v>
       </c>
       <c r="B32" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>19</v>
@@ -9413,12 +9420,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="75">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
         <v>112</v>
       </c>
       <c r="B33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>19</v>
@@ -9469,12 +9476,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="75">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
         <v>114</v>
       </c>
       <c r="B34" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>19</v>
@@ -9525,12 +9532,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="75">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
         <v>116</v>
       </c>
       <c r="B35" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>19</v>
@@ -9581,8 +9588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="75">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
         <v>118</v>
       </c>
       <c r="B36" s="17">
@@ -9637,12 +9644,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="75">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
         <v>120</v>
       </c>
       <c r="B37" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>19</v>
@@ -9693,8 +9700,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="75">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B38" s="17">
@@ -9749,12 +9756,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="75">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
         <v>125</v>
       </c>
       <c r="B39" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>19</v>
@@ -9805,12 +9812,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="75">
-      <c r="A40" s="8" t="s">
+    <row r="40" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>19</v>
@@ -9861,8 +9868,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="75">
-      <c r="A41" s="8" t="s">
+    <row r="41" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
         <v>129</v>
       </c>
       <c r="B41" s="17">
@@ -9917,8 +9924,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="75">
-      <c r="A42" s="8" t="s">
+    <row r="42" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
         <v>131</v>
       </c>
       <c r="B42" s="17">
@@ -9973,8 +9980,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="75">
-      <c r="A43" s="8" t="s">
+    <row r="43" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
         <v>135</v>
       </c>
       <c r="B43" s="17">
@@ -10029,12 +10036,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="75">
-      <c r="A44" s="8" t="s">
+    <row r="44" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
         <v>137</v>
       </c>
       <c r="B44" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>19</v>
@@ -10085,12 +10092,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="75">
-      <c r="A45" s="8" t="s">
+    <row r="45" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
         <v>139</v>
       </c>
       <c r="B45" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>19</v>
@@ -10141,12 +10148,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="75">
-      <c r="A46" s="8" t="s">
+    <row r="46" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
         <v>141</v>
       </c>
       <c r="B46" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>19</v>
@@ -10197,12 +10204,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="75">
-      <c r="A47" s="8" t="s">
+    <row r="47" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
         <v>143</v>
       </c>
       <c r="B47" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>19</v>
@@ -10253,8 +10260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="75">
-      <c r="A48" s="8" t="s">
+    <row r="48" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
         <v>145</v>
       </c>
       <c r="B48" s="17">
@@ -10309,8 +10316,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="75">
-      <c r="A49" s="8" t="s">
+    <row r="49" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
         <v>147</v>
       </c>
       <c r="B49" s="17">
@@ -10365,8 +10372,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="75">
-      <c r="A50" s="8" t="s">
+    <row r="50" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
         <v>149</v>
       </c>
       <c r="B50" s="17">
@@ -10421,8 +10428,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="75">
-      <c r="A51" s="8" t="s">
+    <row r="51" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
         <v>151</v>
       </c>
       <c r="B51" s="17">
@@ -10477,12 +10484,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="345">
-      <c r="A52" s="8" t="s">
+    <row r="52" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
         <v>153</v>
       </c>
       <c r="B52" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>19</v>
@@ -10533,8 +10540,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="135">
-      <c r="A53" s="8" t="s">
+    <row r="53" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
         <v>157</v>
       </c>
       <c r="B53" s="17">
@@ -10589,8 +10596,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="409.5">
-      <c r="A54" s="8" t="s">
+    <row r="54" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B54" s="17">
@@ -10645,8 +10652,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="75">
-      <c r="A55" s="8" t="s">
+    <row r="55" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
         <v>165</v>
       </c>
       <c r="B55" s="17">
@@ -10701,8 +10708,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="75">
-      <c r="A56" s="8" t="s">
+    <row r="56" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
         <v>168</v>
       </c>
       <c r="B56" s="17">
@@ -10757,8 +10764,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="75">
-      <c r="A57" s="8" t="s">
+    <row r="57" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
         <v>170</v>
       </c>
       <c r="B57" s="17">
@@ -10813,8 +10820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="75">
-      <c r="A58" s="8" t="s">
+    <row r="58" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
         <v>173</v>
       </c>
       <c r="B58" s="17">
@@ -10869,8 +10876,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="330">
-      <c r="A59" s="8" t="s">
+    <row r="59" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
         <v>175</v>
       </c>
       <c r="B59" s="17">
@@ -10925,8 +10932,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="330">
-      <c r="A60" s="8" t="s">
+    <row r="60" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
         <v>178</v>
       </c>
       <c r="B60" s="17">
@@ -10981,8 +10988,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="330">
-      <c r="A61" s="8" t="s">
+    <row r="61" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
         <v>180</v>
       </c>
       <c r="B61" s="17">
@@ -11037,8 +11044,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="330">
-      <c r="A62" s="8" t="s">
+    <row r="62" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A62" s="17" t="s">
         <v>182</v>
       </c>
       <c r="B62" s="17">
@@ -11093,8 +11100,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="330">
-      <c r="A63" s="8" t="s">
+    <row r="63" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
         <v>184</v>
       </c>
       <c r="B63" s="17">
@@ -11149,8 +11156,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="330">
-      <c r="A64" s="8" t="s">
+    <row r="64" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
         <v>186</v>
       </c>
       <c r="B64" s="17">
@@ -11205,8 +11212,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="330">
-      <c r="A65" s="8" t="s">
+    <row r="65" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
         <v>188</v>
       </c>
       <c r="B65" s="17">
@@ -11261,8 +11268,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="330">
-      <c r="A66" s="8" t="s">
+    <row r="66" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
         <v>190</v>
       </c>
       <c r="B66" s="17">
@@ -11317,8 +11324,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="330">
-      <c r="A67" s="8" t="s">
+    <row r="67" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
         <v>192</v>
       </c>
       <c r="B67" s="17">
@@ -11373,8 +11380,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="330">
-      <c r="A68" s="8" t="s">
+    <row r="68" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
         <v>194</v>
       </c>
       <c r="B68" s="17">
@@ -11429,8 +11436,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="330">
-      <c r="A69" s="8" t="s">
+    <row r="69" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
         <v>196</v>
       </c>
       <c r="B69" s="17">
@@ -11485,8 +11492,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="330">
-      <c r="A70" s="8" t="s">
+    <row r="70" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
         <v>198</v>
       </c>
       <c r="B70" s="17">
@@ -11541,8 +11548,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="330">
-      <c r="A71" s="8" t="s">
+    <row r="71" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
         <v>200</v>
       </c>
       <c r="B71" s="17">
@@ -11597,8 +11604,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="330">
-      <c r="A72" s="8" t="s">
+    <row r="72" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
         <v>201</v>
       </c>
       <c r="B72" s="17">
@@ -11653,8 +11660,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="330">
-      <c r="A73" s="8" t="s">
+    <row r="73" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
         <v>203</v>
       </c>
       <c r="B73" s="17">
@@ -11709,8 +11716,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="330">
-      <c r="A74" s="8" t="s">
+    <row r="74" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A74" s="17" t="s">
         <v>205</v>
       </c>
       <c r="B74" s="17">
@@ -11765,8 +11772,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="330">
-      <c r="A75" s="8" t="s">
+    <row r="75" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
         <v>207</v>
       </c>
       <c r="B75" s="17">
@@ -11821,8 +11828,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="60">
-      <c r="A76" s="8" t="s">
+    <row r="76" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
         <v>209</v>
       </c>
       <c r="B76" s="17">
@@ -11877,8 +11884,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="60">
-      <c r="A77" s="8" t="s">
+    <row r="77" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
         <v>216</v>
       </c>
       <c r="B77" s="17">
@@ -11933,8 +11940,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="60">
-      <c r="A78" s="8" t="s">
+    <row r="78" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
         <v>217</v>
       </c>
       <c r="B78" s="17">
@@ -11989,8 +11996,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="60">
-      <c r="A79" s="8" t="s">
+    <row r="79" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
         <v>218</v>
       </c>
       <c r="B79" s="17">
@@ -12045,8 +12052,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="60">
-      <c r="A80" s="8" t="s">
+    <row r="80" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
         <v>221</v>
       </c>
       <c r="B80" s="17">
@@ -12101,8 +12108,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="75">
-      <c r="A81" s="8" t="s">
+    <row r="81" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
         <v>226</v>
       </c>
       <c r="B81" s="17">
@@ -12157,8 +12164,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="60">
-      <c r="A82" s="8" t="s">
+    <row r="82" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
         <v>233</v>
       </c>
       <c r="B82" s="17">
@@ -12213,8 +12220,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="60">
-      <c r="A83" s="8" t="s">
+    <row r="83" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>235</v>
       </c>
       <c r="B83" s="17">
@@ -12269,8 +12276,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="60">
-      <c r="A84" s="8" t="s">
+    <row r="84" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
         <v>238</v>
       </c>
       <c r="B84" s="17">
@@ -12325,8 +12332,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="60">
-      <c r="A85" s="8" t="s">
+    <row r="85" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>241</v>
       </c>
       <c r="B85" s="17">
@@ -12381,8 +12388,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="60">
-      <c r="A86" s="8" t="s">
+    <row r="86" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A86" s="17" t="s">
         <v>243</v>
       </c>
       <c r="B86" s="17">
@@ -12437,8 +12444,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="60">
-      <c r="A87" s="8" t="s">
+    <row r="87" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
         <v>246</v>
       </c>
       <c r="B87" s="17">
@@ -12493,8 +12500,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="60">
-      <c r="A88" s="8" t="s">
+    <row r="88" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
         <v>249</v>
       </c>
       <c r="B88" s="17">
@@ -12549,8 +12556,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="60">
-      <c r="A89" s="8" t="s">
+    <row r="89" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
         <v>251</v>
       </c>
       <c r="B89" s="17">
@@ -12605,8 +12612,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="60">
-      <c r="A90" s="8" t="s">
+    <row r="90" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
         <v>254</v>
       </c>
       <c r="B90" s="17">
@@ -12661,8 +12668,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="60">
-      <c r="A91" s="8" t="s">
+    <row r="91" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A91" s="17" t="s">
         <v>255</v>
       </c>
       <c r="B91" s="17">
@@ -12717,8 +12724,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="60">
-      <c r="A92" s="8" t="s">
+    <row r="92" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A92" s="17" t="s">
         <v>257</v>
       </c>
       <c r="B92" s="17">
@@ -12773,8 +12780,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="60">
-      <c r="A93" s="8" t="s">
+    <row r="93" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
         <v>259</v>
       </c>
       <c r="B93" s="17">
@@ -12829,8 +12836,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="60">
-      <c r="A94" s="8" t="s">
+    <row r="94" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A94" s="17" t="s">
         <v>261</v>
       </c>
       <c r="B94" s="17">
@@ -12885,8 +12892,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="60">
-      <c r="A95" s="8" t="s">
+    <row r="95" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A95" s="17" t="s">
         <v>264</v>
       </c>
       <c r="B95" s="17">
@@ -12941,8 +12948,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="60">
-      <c r="A96" s="8" t="s">
+    <row r="96" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A96" s="17" t="s">
         <v>265</v>
       </c>
       <c r="B96" s="17">
@@ -12997,8 +13004,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="60">
-      <c r="A97" s="8" t="s">
+    <row r="97" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A97" s="17" t="s">
         <v>268</v>
       </c>
       <c r="B97" s="17">
@@ -13053,8 +13060,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="75">
-      <c r="A98" s="8" t="s">
+    <row r="98" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
         <v>270</v>
       </c>
       <c r="B98" s="17">
@@ -13109,8 +13116,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="60">
-      <c r="A99" s="8" t="s">
+    <row r="99" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A99" s="17" t="s">
         <v>273</v>
       </c>
       <c r="B99" s="17">
@@ -13165,8 +13172,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="60">
-      <c r="A100" s="8" t="s">
+    <row r="100" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A100" s="17" t="s">
         <v>275</v>
       </c>
       <c r="B100" s="17">
@@ -13221,8 +13228,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="60">
-      <c r="A101" s="8" t="s">
+    <row r="101" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A101" s="17" t="s">
         <v>278</v>
       </c>
       <c r="B101" s="17">
@@ -13277,8 +13284,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="60">
-      <c r="A102" s="8" t="s">
+    <row r="102" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
         <v>281</v>
       </c>
       <c r="B102" s="17">
@@ -13333,8 +13340,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="60">
-      <c r="A103" s="8" t="s">
+    <row r="103" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A103" s="17" t="s">
         <v>284</v>
       </c>
       <c r="B103" s="17">
@@ -13389,8 +13396,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="60">
-      <c r="A104" s="8" t="s">
+    <row r="104" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
         <v>287</v>
       </c>
       <c r="B104" s="17">
@@ -13445,8 +13452,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="60">
-      <c r="A105" s="8" t="s">
+    <row r="105" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
         <v>289</v>
       </c>
       <c r="B105" s="17">
@@ -13501,8 +13508,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="60">
-      <c r="A106" s="8" t="s">
+    <row r="106" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
         <v>291</v>
       </c>
       <c r="B106" s="17">
@@ -13557,8 +13564,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="60">
-      <c r="A107" s="8" t="s">
+    <row r="107" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
         <v>294</v>
       </c>
       <c r="B107" s="17">
@@ -13613,8 +13620,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="105">
-      <c r="A108" s="8" t="s">
+    <row r="108" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
         <v>296</v>
       </c>
       <c r="B108" s="17">
@@ -13669,8 +13676,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="105">
-      <c r="A109" s="8" t="s">
+    <row r="109" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A109" s="17" t="s">
         <v>298</v>
       </c>
       <c r="B109" s="17">
@@ -13725,8 +13732,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="105">
-      <c r="A110" s="8" t="s">
+    <row r="110" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A110" s="17" t="s">
         <v>301</v>
       </c>
       <c r="B110" s="17">
@@ -13781,8 +13788,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="105">
-      <c r="A111" s="8" t="s">
+    <row r="111" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A111" s="17" t="s">
         <v>304</v>
       </c>
       <c r="B111" s="17">
@@ -13837,8 +13844,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="105">
-      <c r="A112" s="8" t="s">
+    <row r="112" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A112" s="17" t="s">
         <v>307</v>
       </c>
       <c r="B112" s="17">
@@ -13893,8 +13900,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="105">
-      <c r="A113" s="8" t="s">
+    <row r="113" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A113" s="17" t="s">
         <v>310</v>
       </c>
       <c r="B113" s="17">
@@ -13949,8 +13956,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="105">
-      <c r="A114" s="8" t="s">
+    <row r="114" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A114" s="17" t="s">
         <v>312</v>
       </c>
       <c r="B114" s="17">
@@ -14005,8 +14012,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="105">
-      <c r="A115" s="8" t="s">
+    <row r="115" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A115" s="17" t="s">
         <v>315</v>
       </c>
       <c r="B115" s="17">
@@ -14061,8 +14068,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="105">
-      <c r="A116" s="8" t="s">
+    <row r="116" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A116" s="17" t="s">
         <v>317</v>
       </c>
       <c r="B116" s="17">
@@ -14117,8 +14124,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="105">
-      <c r="A117" s="8" t="s">
+    <row r="117" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A117" s="17" t="s">
         <v>320</v>
       </c>
       <c r="B117" s="17">
@@ -14173,8 +14180,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="60">
-      <c r="A118" s="8" t="s">
+    <row r="118" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A118" s="17" t="s">
         <v>323</v>
       </c>
       <c r="B118" s="17">
@@ -14229,8 +14236,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="60">
-      <c r="A119" s="8" t="s">
+    <row r="119" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A119" s="17" t="s">
         <v>327</v>
       </c>
       <c r="B119" s="17">
@@ -14285,8 +14292,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="60">
-      <c r="A120" s="8" t="s">
+    <row r="120" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A120" s="17" t="s">
         <v>329</v>
       </c>
       <c r="B120" s="17">
@@ -14341,8 +14348,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="60">
-      <c r="A121" s="8" t="s">
+    <row r="121" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A121" s="17" t="s">
         <v>331</v>
       </c>
       <c r="B121" s="17">
@@ -14397,8 +14404,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="60">
-      <c r="A122" s="8" t="s">
+    <row r="122" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A122" s="17" t="s">
         <v>333</v>
       </c>
       <c r="B122" s="17">
@@ -14453,8 +14460,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="60">
-      <c r="A123" s="8" t="s">
+    <row r="123" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A123" s="17" t="s">
         <v>335</v>
       </c>
       <c r="B123" s="17">
@@ -14509,8 +14516,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="60">
-      <c r="A124" s="8" t="s">
+    <row r="124" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A124" s="17" t="s">
         <v>338</v>
       </c>
       <c r="B124" s="17">
@@ -14565,8 +14572,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="60">
-      <c r="A125" s="8" t="s">
+    <row r="125" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A125" s="17" t="s">
         <v>341</v>
       </c>
       <c r="B125" s="17">
@@ -14621,8 +14628,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="60">
-      <c r="A126" s="8" t="s">
+    <row r="126" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A126" s="17" t="s">
         <v>344</v>
       </c>
       <c r="B126" s="17">
@@ -14677,8 +14684,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="75">
-      <c r="A127" s="8" t="s">
+    <row r="127" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A127" s="17" t="s">
         <v>346</v>
       </c>
       <c r="B127" s="17">
@@ -14733,8 +14740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="60">
-      <c r="A128" s="8" t="s">
+    <row r="128" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A128" s="17" t="s">
         <v>349</v>
       </c>
       <c r="B128" s="17">
@@ -14789,8 +14796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="60">
-      <c r="A129" s="8" t="s">
+    <row r="129" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A129" s="17" t="s">
         <v>353</v>
       </c>
       <c r="B129" s="17">
@@ -14845,8 +14852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="60">
-      <c r="A130" s="8" t="s">
+    <row r="130" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A130" s="17" t="s">
         <v>356</v>
       </c>
       <c r="B130" s="17">
@@ -14901,8 +14908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="60">
-      <c r="A131" s="8" t="s">
+    <row r="131" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A131" s="17" t="s">
         <v>359</v>
       </c>
       <c r="B131" s="17">
@@ -14957,8 +14964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="60">
-      <c r="A132" s="8" t="s">
+    <row r="132" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A132" s="17" t="s">
         <v>362</v>
       </c>
       <c r="B132" s="17">
@@ -15013,8 +15020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="60">
-      <c r="A133" s="8" t="s">
+    <row r="133" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A133" s="17" t="s">
         <v>364</v>
       </c>
       <c r="B133" s="17">
@@ -15069,8 +15076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="60">
-      <c r="A134" s="8" t="s">
+    <row r="134" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A134" s="17" t="s">
         <v>367</v>
       </c>
       <c r="B134" s="17">
@@ -15125,8 +15132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="60">
-      <c r="A135" s="8" t="s">
+    <row r="135" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A135" s="17" t="s">
         <v>370</v>
       </c>
       <c r="B135" s="17">
@@ -15181,8 +15188,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="60">
-      <c r="A136" s="8" t="s">
+    <row r="136" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A136" s="17" t="s">
         <v>373</v>
       </c>
       <c r="B136" s="17">
@@ -15237,8 +15244,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="60">
-      <c r="A137" s="8" t="s">
+    <row r="137" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A137" s="17" t="s">
         <v>375</v>
       </c>
       <c r="B137" s="17">
@@ -15293,8 +15300,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="60">
-      <c r="A138" s="8" t="s">
+    <row r="138" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A138" s="17" t="s">
         <v>377</v>
       </c>
       <c r="B138" s="17">
@@ -15349,8 +15356,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="60">
-      <c r="A139" s="8" t="s">
+    <row r="139" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A139" s="17" t="s">
         <v>379</v>
       </c>
       <c r="B139" s="17">
@@ -15405,8 +15412,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="60">
-      <c r="A140" s="8" t="s">
+    <row r="140" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A140" s="17" t="s">
         <v>382</v>
       </c>
       <c r="B140" s="17">
@@ -15461,8 +15468,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="60">
-      <c r="A141" s="8" t="s">
+    <row r="141" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A141" s="17" t="s">
         <v>385</v>
       </c>
       <c r="B141" s="17">
@@ -15517,8 +15524,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="60">
-      <c r="A142" s="8" t="s">
+    <row r="142" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A142" s="17" t="s">
         <v>387</v>
       </c>
       <c r="B142" s="17">
@@ -15573,8 +15580,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="60">
-      <c r="A143" s="8" t="s">
+    <row r="143" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A143" s="17" t="s">
         <v>389</v>
       </c>
       <c r="B143" s="17">
@@ -15629,8 +15636,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="60">
-      <c r="A144" s="8" t="s">
+    <row r="144" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A144" s="17" t="s">
         <v>391</v>
       </c>
       <c r="B144" s="17">
@@ -15685,8 +15692,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="60">
-      <c r="A145" s="8" t="s">
+    <row r="145" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A145" s="17" t="s">
         <v>394</v>
       </c>
       <c r="B145" s="17">
@@ -15741,8 +15748,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="60">
-      <c r="A146" s="8" t="s">
+    <row r="146" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A146" s="17" t="s">
         <v>397</v>
       </c>
       <c r="B146" s="17">
@@ -15797,8 +15804,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="60">
-      <c r="A147" s="8" t="s">
+    <row r="147" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
         <v>400</v>
       </c>
       <c r="B147" s="17">
@@ -15853,8 +15860,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="60">
-      <c r="A148" s="8" t="s">
+    <row r="148" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A148" s="17" t="s">
         <v>402</v>
       </c>
       <c r="B148" s="17">
@@ -15909,8 +15916,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="60">
-      <c r="A149" s="8" t="s">
+    <row r="149" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
         <v>405</v>
       </c>
       <c r="B149" s="17">
@@ -15965,8 +15972,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="60">
-      <c r="A150" s="8" t="s">
+    <row r="150" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A150" s="17" t="s">
         <v>408</v>
       </c>
       <c r="B150" s="17">
@@ -16021,8 +16028,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="60">
-      <c r="A151" s="8" t="s">
+    <row r="151" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
         <v>411</v>
       </c>
       <c r="B151" s="17">
@@ -16077,8 +16084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="75">
-      <c r="A152" s="8" t="s">
+    <row r="152" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A152" s="17" t="s">
         <v>414</v>
       </c>
       <c r="B152" s="17">
@@ -16133,8 +16140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="60">
-      <c r="A153" s="8" t="s">
+    <row r="153" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A153" s="17" t="s">
         <v>417</v>
       </c>
       <c r="B153" s="17">
@@ -16189,8 +16196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="60">
-      <c r="A154" s="8" t="s">
+    <row r="154" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A154" s="17" t="s">
         <v>420</v>
       </c>
       <c r="B154" s="17">
@@ -16245,8 +16252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="60">
-      <c r="A155" s="8" t="s">
+    <row r="155" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A155" s="17" t="s">
         <v>423</v>
       </c>
       <c r="B155" s="17">
@@ -16301,8 +16308,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="90">
-      <c r="A156" s="8" t="s">
+    <row r="156" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A156" s="17" t="s">
         <v>426</v>
       </c>
       <c r="B156" s="17">
@@ -16357,8 +16364,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="90">
-      <c r="A157" s="8" t="s">
+    <row r="157" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A157" s="17" t="s">
         <v>431</v>
       </c>
       <c r="B157" s="17">
@@ -16413,8 +16420,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="90">
-      <c r="A158" s="8" t="s">
+    <row r="158" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A158" s="17" t="s">
         <v>433</v>
       </c>
       <c r="B158" s="17">
@@ -16469,8 +16476,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="90">
-      <c r="A159" s="8" t="s">
+    <row r="159" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A159" s="17" t="s">
         <v>436</v>
       </c>
       <c r="B159" s="17">
@@ -16525,8 +16532,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="90">
-      <c r="A160" s="8" t="s">
+    <row r="160" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A160" s="17" t="s">
         <v>439</v>
       </c>
       <c r="B160" s="17">
@@ -16581,8 +16588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="90">
-      <c r="A161" s="8" t="s">
+    <row r="161" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A161" s="17" t="s">
         <v>442</v>
       </c>
       <c r="B161" s="17">
@@ -16637,8 +16644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="90">
-      <c r="A162" s="8" t="s">
+    <row r="162" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A162" s="17" t="s">
         <v>445</v>
       </c>
       <c r="B162" s="17">
@@ -16693,8 +16700,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="90">
-      <c r="A163" s="8" t="s">
+    <row r="163" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A163" s="17" t="s">
         <v>448</v>
       </c>
       <c r="B163" s="17">
@@ -16749,8 +16756,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="90">
-      <c r="A164" s="8" t="s">
+    <row r="164" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A164" s="17" t="s">
         <v>451</v>
       </c>
       <c r="B164" s="17">
@@ -16805,8 +16812,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="60">
-      <c r="A165" s="8" t="s">
+    <row r="165" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A165" s="17" t="s">
         <v>454</v>
       </c>
       <c r="B165" s="17">
@@ -16861,8 +16868,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="60">
-      <c r="A166" s="8" t="s">
+    <row r="166" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A166" s="17" t="s">
         <v>457</v>
       </c>
       <c r="B166" s="17">
@@ -16917,8 +16924,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="60">
-      <c r="A167" s="8" t="s">
+    <row r="167" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A167" s="17" t="s">
         <v>460</v>
       </c>
       <c r="B167" s="17">
@@ -16973,8 +16980,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="60">
-      <c r="A168" s="8" t="s">
+    <row r="168" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A168" s="17" t="s">
         <v>463</v>
       </c>
       <c r="B168" s="17">
@@ -17029,8 +17036,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="60">
-      <c r="A169" s="8" t="s">
+    <row r="169" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A169" s="17" t="s">
         <v>466</v>
       </c>
       <c r="B169" s="17">
@@ -17085,8 +17092,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="60">
-      <c r="A170" s="8" t="s">
+    <row r="170" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A170" s="17" t="s">
         <v>469</v>
       </c>
       <c r="B170" s="17">
@@ -17141,8 +17148,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="60">
-      <c r="A171" s="8" t="s">
+    <row r="171" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A171" s="17" t="s">
         <v>472</v>
       </c>
       <c r="B171" s="17">
@@ -17197,8 +17204,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="60">
-      <c r="A172" s="8" t="s">
+    <row r="172" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A172" s="17" t="s">
         <v>475</v>
       </c>
       <c r="B172" s="17">
@@ -17253,8 +17260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="60">
-      <c r="A173" s="8" t="s">
+    <row r="173" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A173" s="17" t="s">
         <v>477</v>
       </c>
       <c r="B173" s="17">
@@ -17309,8 +17316,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="60">
-      <c r="A174" s="8" t="s">
+    <row r="174" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A174" s="17" t="s">
         <v>479</v>
       </c>
       <c r="B174" s="17">
@@ -17365,8 +17372,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="60">
-      <c r="A175" s="8" t="s">
+    <row r="175" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A175" s="17" t="s">
         <v>482</v>
       </c>
       <c r="B175" s="17">
@@ -17421,8 +17428,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="60">
-      <c r="A176" s="8" t="s">
+    <row r="176" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A176" s="17" t="s">
         <v>485</v>
       </c>
       <c r="B176" s="17">
@@ -17477,8 +17484,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="60">
-      <c r="A177" s="8" t="s">
+    <row r="177" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A177" s="17" t="s">
         <v>488</v>
       </c>
       <c r="B177" s="17">
@@ -17533,8 +17540,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="60">
-      <c r="A178" s="8" t="s">
+    <row r="178" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A178" s="17" t="s">
         <v>491</v>
       </c>
       <c r="B178" s="17">
@@ -17589,8 +17596,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="60">
-      <c r="A179" s="8" t="s">
+    <row r="179" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A179" s="17" t="s">
         <v>494</v>
       </c>
       <c r="B179" s="17">
@@ -17645,8 +17652,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="60">
-      <c r="A180" s="8" t="s">
+    <row r="180" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A180" s="17" t="s">
         <v>497</v>
       </c>
       <c r="B180" s="17">
@@ -17701,8 +17708,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="60">
-      <c r="A181" s="8" t="s">
+    <row r="181" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A181" s="17" t="s">
         <v>500</v>
       </c>
       <c r="B181" s="17">
@@ -17757,8 +17764,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="75">
-      <c r="A182" s="8" t="s">
+    <row r="182" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A182" s="17" t="s">
         <v>503</v>
       </c>
       <c r="B182" s="17">
@@ -17813,8 +17820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="75">
-      <c r="A183" s="8" t="s">
+    <row r="183" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A183" s="17" t="s">
         <v>506</v>
       </c>
       <c r="B183" s="17">
@@ -17869,8 +17876,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="75">
-      <c r="A184" s="8" t="s">
+    <row r="184" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A184" s="17" t="s">
         <v>509</v>
       </c>
       <c r="B184" s="17">
@@ -17925,8 +17932,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="75">
-      <c r="A185" s="8" t="s">
+    <row r="185" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A185" s="17" t="s">
         <v>512</v>
       </c>
       <c r="B185" s="17">
@@ -17981,8 +17988,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="60">
-      <c r="A186" s="8" t="s">
+    <row r="186" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A186" s="17" t="s">
         <v>515</v>
       </c>
       <c r="B186" s="17">
@@ -18037,8 +18044,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="60">
-      <c r="A187" s="8" t="s">
+    <row r="187" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A187" s="17" t="s">
         <v>517</v>
       </c>
       <c r="B187" s="17">
@@ -18093,8 +18100,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="60">
-      <c r="A188" s="8" t="s">
+    <row r="188" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A188" s="17" t="s">
         <v>519</v>
       </c>
       <c r="B188" s="17">
@@ -18149,8 +18156,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="60">
-      <c r="A189" s="8" t="s">
+    <row r="189" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A189" s="17" t="s">
         <v>522</v>
       </c>
       <c r="B189" s="17">
@@ -18205,8 +18212,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="60">
-      <c r="A190" s="8" t="s">
+    <row r="190" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A190" s="17" t="s">
         <v>524</v>
       </c>
       <c r="B190" s="17">
@@ -18261,8 +18268,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="60">
-      <c r="A191" s="8" t="s">
+    <row r="191" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A191" s="17" t="s">
         <v>527</v>
       </c>
       <c r="B191" s="17">
@@ -18317,8 +18324,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="60">
-      <c r="A192" s="8" t="s">
+    <row r="192" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A192" s="17" t="s">
         <v>530</v>
       </c>
       <c r="B192" s="17">
@@ -18373,8 +18380,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="60">
-      <c r="A193" s="8" t="s">
+    <row r="193" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A193" s="17" t="s">
         <v>532</v>
       </c>
       <c r="B193" s="17">
@@ -18429,8 +18436,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="60">
-      <c r="A194" s="8" t="s">
+    <row r="194" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A194" s="17" t="s">
         <v>535</v>
       </c>
       <c r="B194" s="17">
@@ -18485,8 +18492,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="60">
-      <c r="A195" s="8" t="s">
+    <row r="195" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A195" s="17" t="s">
         <v>538</v>
       </c>
       <c r="B195" s="17">
@@ -18541,8 +18548,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="60">
-      <c r="A196" s="8" t="s">
+    <row r="196" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A196" s="17" t="s">
         <v>541</v>
       </c>
       <c r="B196" s="17">
@@ -18597,8 +18604,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="60">
-      <c r="A197" s="8" t="s">
+    <row r="197" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A197" s="17" t="s">
         <v>544</v>
       </c>
       <c r="B197" s="17">
@@ -18653,8 +18660,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="60">
-      <c r="A198" s="8" t="s">
+    <row r="198" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A198" s="17" t="s">
         <v>547</v>
       </c>
       <c r="B198" s="17">
@@ -18709,8 +18716,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="60">
-      <c r="A199" s="8" t="s">
+    <row r="199" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A199" s="17" t="s">
         <v>550</v>
       </c>
       <c r="B199" s="17">
@@ -18765,8 +18772,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="60">
-      <c r="A200" s="8" t="s">
+    <row r="200" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A200" s="17" t="s">
         <v>552</v>
       </c>
       <c r="B200" s="17">
@@ -18821,8 +18828,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="60">
-      <c r="A201" s="8" t="s">
+    <row r="201" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A201" s="17" t="s">
         <v>554</v>
       </c>
       <c r="B201" s="17">
@@ -18877,8 +18884,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="60">
-      <c r="A202" s="8" t="s">
+    <row r="202" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A202" s="17" t="s">
         <v>556</v>
       </c>
       <c r="B202" s="17">
@@ -18933,8 +18940,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="60">
-      <c r="A203" s="8" t="s">
+    <row r="203" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A203" s="17" t="s">
         <v>558</v>
       </c>
       <c r="B203" s="17">
@@ -18989,8 +18996,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="60">
-      <c r="A204" s="8" t="s">
+    <row r="204" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A204" s="17" t="s">
         <v>560</v>
       </c>
       <c r="B204" s="17">
@@ -19045,8 +19052,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="60">
-      <c r="A205" s="8" t="s">
+    <row r="205" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A205" s="17" t="s">
         <v>562</v>
       </c>
       <c r="B205" s="17">
@@ -19101,8 +19108,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="60">
-      <c r="A206" s="8" t="s">
+    <row r="206" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A206" s="17" t="s">
         <v>564</v>
       </c>
       <c r="B206" s="17">
@@ -19157,8 +19164,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="60">
-      <c r="A207" s="8" t="s">
+    <row r="207" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A207" s="17" t="s">
         <v>566</v>
       </c>
       <c r="B207" s="17">
@@ -19213,8 +19220,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="60">
-      <c r="A208" s="8" t="s">
+    <row r="208" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A208" s="17" t="s">
         <v>568</v>
       </c>
       <c r="B208" s="17">
@@ -19269,8 +19276,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="60">
-      <c r="A209" s="8" t="s">
+    <row r="209" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A209" s="17" t="s">
         <v>571</v>
       </c>
       <c r="B209" s="17">
@@ -19325,8 +19332,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="60">
-      <c r="A210" s="8" t="s">
+    <row r="210" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A210" s="17" t="s">
         <v>574</v>
       </c>
       <c r="B210" s="17">
@@ -19381,8 +19388,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="60">
-      <c r="A211" s="8" t="s">
+    <row r="211" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A211" s="17" t="s">
         <v>577</v>
       </c>
       <c r="B211" s="17">
@@ -19437,8 +19444,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="75">
-      <c r="A212" s="8" t="s">
+    <row r="212" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A212" s="17" t="s">
         <v>580</v>
       </c>
       <c r="B212" s="17">
@@ -19493,8 +19500,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="75">
-      <c r="A213" s="8" t="s">
+    <row r="213" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A213" s="17" t="s">
         <v>583</v>
       </c>
       <c r="B213" s="17">
@@ -19549,8 +19556,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="75">
-      <c r="A214" s="8" t="s">
+    <row r="214" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A214" s="17" t="s">
         <v>586</v>
       </c>
       <c r="B214" s="17">
@@ -19605,8 +19612,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="75">
-      <c r="A215" s="8" t="s">
+    <row r="215" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A215" s="17" t="s">
         <v>589</v>
       </c>
       <c r="B215" s="17">
@@ -19661,8 +19668,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="60">
-      <c r="A216" s="8" t="s">
+    <row r="216" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A216" s="17" t="s">
         <v>592</v>
       </c>
       <c r="B216" s="17">
@@ -19717,8 +19724,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="60">
-      <c r="A217" s="8" t="s">
+    <row r="217" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A217" s="17" t="s">
         <v>594</v>
       </c>
       <c r="B217" s="17">
@@ -19773,8 +19780,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="60">
-      <c r="A218" s="8" t="s">
+    <row r="218" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A218" s="17" t="s">
         <v>598</v>
       </c>
       <c r="B218" s="17">
@@ -19829,8 +19836,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="60">
-      <c r="A219" s="8" t="s">
+    <row r="219" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A219" s="17" t="s">
         <v>601</v>
       </c>
       <c r="B219" s="17">
@@ -19885,8 +19892,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="60">
-      <c r="A220" s="8" t="s">
+    <row r="220" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A220" s="17" t="s">
         <v>604</v>
       </c>
       <c r="B220" s="17">
@@ -19941,8 +19948,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="60">
-      <c r="A221" s="8" t="s">
+    <row r="221" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A221" s="17" t="s">
         <v>607</v>
       </c>
       <c r="B221" s="17">
@@ -19997,8 +20004,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="60">
-      <c r="A222" s="8" t="s">
+    <row r="222" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A222" s="17" t="s">
         <v>609</v>
       </c>
       <c r="B222" s="17">
@@ -20053,8 +20060,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="60">
-      <c r="A223" s="8" t="s">
+    <row r="223" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A223" s="17" t="s">
         <v>611</v>
       </c>
       <c r="B223" s="17">
@@ -20109,8 +20116,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="60">
-      <c r="A224" s="8" t="s">
+    <row r="224" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A224" s="17" t="s">
         <v>615</v>
       </c>
       <c r="B224" s="17">
@@ -20165,8 +20172,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="60">
-      <c r="A225" s="8" t="s">
+    <row r="225" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A225" s="17" t="s">
         <v>617</v>
       </c>
       <c r="B225" s="17">
@@ -20221,8 +20228,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="60">
-      <c r="A226" s="8" t="s">
+    <row r="226" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A226" s="17" t="s">
         <v>619</v>
       </c>
       <c r="B226" s="17">
@@ -20277,8 +20284,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="60">
-      <c r="A227" s="8" t="s">
+    <row r="227" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A227" s="17" t="s">
         <v>621</v>
       </c>
       <c r="B227" s="17">
@@ -20333,8 +20340,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="345">
-      <c r="A228" s="8" t="s">
+    <row r="228" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A228" s="17" t="s">
         <v>623</v>
       </c>
       <c r="B228" s="17">
@@ -20389,8 +20396,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="345">
-      <c r="A229" s="8" t="s">
+    <row r="229" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A229" s="17" t="s">
         <v>625</v>
       </c>
       <c r="B229" s="17">
@@ -20445,8 +20452,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="345">
-      <c r="A230" s="8" t="s">
+    <row r="230" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A230" s="17" t="s">
         <v>628</v>
       </c>
       <c r="B230" s="17">
@@ -20501,8 +20508,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="345">
-      <c r="A231" s="8" t="s">
+    <row r="231" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A231" s="17" t="s">
         <v>629</v>
       </c>
       <c r="B231" s="17">
@@ -20557,8 +20564,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="345">
-      <c r="A232" s="8" t="s">
+    <row r="232" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A232" s="17" t="s">
         <v>632</v>
       </c>
       <c r="B232" s="17">
@@ -20613,8 +20620,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="345">
-      <c r="A233" s="8" t="s">
+    <row r="233" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A233" s="17" t="s">
         <v>635</v>
       </c>
       <c r="B233" s="17">
@@ -20669,8 +20676,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="345">
-      <c r="A234" s="8" t="s">
+    <row r="234" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A234" s="17" t="s">
         <v>638</v>
       </c>
       <c r="B234" s="17">
@@ -20725,8 +20732,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="345">
-      <c r="A235" s="8" t="s">
+    <row r="235" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A235" s="17" t="s">
         <v>639</v>
       </c>
       <c r="B235" s="17">
@@ -20781,8 +20788,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="345">
-      <c r="A236" s="8" t="s">
+    <row r="236" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A236" s="17" t="s">
         <v>642</v>
       </c>
       <c r="B236" s="17">
@@ -20837,8 +20844,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="345">
-      <c r="A237" s="8" t="s">
+    <row r="237" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A237" s="17" t="s">
         <v>645</v>
       </c>
       <c r="B237" s="17">
@@ -20893,8 +20900,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="345">
-      <c r="A238" s="8" t="s">
+    <row r="238" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A238" s="17" t="s">
         <v>646</v>
       </c>
       <c r="B238" s="17">
@@ -20949,8 +20956,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="345">
-      <c r="A239" s="8" t="s">
+    <row r="239" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A239" s="17" t="s">
         <v>649</v>
       </c>
       <c r="B239" s="17">
@@ -21005,8 +21012,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="345">
-      <c r="A240" s="8" t="s">
+    <row r="240" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A240" s="17" t="s">
         <v>651</v>
       </c>
       <c r="B240" s="17">
@@ -21061,8 +21068,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="345">
-      <c r="A241" s="8" t="s">
+    <row r="241" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A241" s="17" t="s">
         <v>654</v>
       </c>
       <c r="B241" s="17">
@@ -21117,8 +21124,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="345">
-      <c r="A242" s="8" t="s">
+    <row r="242" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A242" s="17" t="s">
         <v>657</v>
       </c>
       <c r="B242" s="17">
@@ -21173,8 +21180,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="345">
-      <c r="A243" s="8" t="s">
+    <row r="243" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A243" s="17" t="s">
         <v>660</v>
       </c>
       <c r="B243" s="17">
@@ -21229,8 +21236,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="345">
-      <c r="A244" s="8" t="s">
+    <row r="244" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A244" s="17" t="s">
         <v>662</v>
       </c>
       <c r="B244" s="17">
@@ -21285,8 +21292,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="345">
-      <c r="A245" s="8" t="s">
+    <row r="245" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A245" s="17" t="s">
         <v>664</v>
       </c>
       <c r="B245" s="17">
@@ -21341,8 +21348,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="345">
-      <c r="A246" s="8" t="s">
+    <row r="246" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A246" s="17" t="s">
         <v>666</v>
       </c>
       <c r="B246" s="17">
@@ -21397,8 +21404,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="345">
-      <c r="A247" s="8" t="s">
+    <row r="247" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A247" s="17" t="s">
         <v>669</v>
       </c>
       <c r="B247" s="17">
@@ -21453,8 +21460,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="345">
-      <c r="A248" s="8" t="s">
+    <row r="248" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A248" s="17" t="s">
         <v>672</v>
       </c>
       <c r="B248" s="17">
@@ -21509,8 +21516,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="345">
-      <c r="A249" s="8" t="s">
+    <row r="249" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A249" s="17" t="s">
         <v>675</v>
       </c>
       <c r="B249" s="17">
@@ -21565,8 +21572,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="345">
-      <c r="A250" s="8" t="s">
+    <row r="250" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A250" s="17" t="s">
         <v>677</v>
       </c>
       <c r="B250" s="17">
@@ -21621,8 +21628,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="345">
-      <c r="A251" s="8" t="s">
+    <row r="251" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A251" s="17" t="s">
         <v>679</v>
       </c>
       <c r="B251" s="17">
@@ -21677,8 +21684,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="345">
-      <c r="A252" s="8" t="s">
+    <row r="252" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A252" s="17" t="s">
         <v>680</v>
       </c>
       <c r="B252" s="17">
@@ -21733,8 +21740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="345">
-      <c r="A253" s="8" t="s">
+    <row r="253" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A253" s="17" t="s">
         <v>682</v>
       </c>
       <c r="B253" s="17">
@@ -21789,8 +21796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="345">
-      <c r="A254" s="8" t="s">
+    <row r="254" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A254" s="17" t="s">
         <v>685</v>
       </c>
       <c r="B254" s="17">
@@ -21845,8 +21852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="345">
-      <c r="A255" s="8" t="s">
+    <row r="255" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A255" s="17" t="s">
         <v>687</v>
       </c>
       <c r="B255" s="17">
@@ -21901,8 +21908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="135">
-      <c r="A256" s="8" t="s">
+    <row r="256" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A256" s="17" t="s">
         <v>690</v>
       </c>
       <c r="B256" s="17">
@@ -21957,8 +21964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="135">
-      <c r="A257" s="8" t="s">
+    <row r="257" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A257" s="17" t="s">
         <v>692</v>
       </c>
       <c r="B257" s="17">
@@ -22013,8 +22020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="135">
-      <c r="A258" s="8" t="s">
+    <row r="258" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A258" s="17" t="s">
         <v>695</v>
       </c>
       <c r="B258" s="17">
@@ -22069,8 +22076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="135">
-      <c r="A259" s="8" t="s">
+    <row r="259" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A259" s="17" t="s">
         <v>697</v>
       </c>
       <c r="B259" s="17">
@@ -22125,8 +22132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="135">
-      <c r="A260" s="8" t="s">
+    <row r="260" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A260" s="17" t="s">
         <v>700</v>
       </c>
       <c r="B260" s="17">
@@ -22181,8 +22188,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="135">
-      <c r="A261" s="8" t="s">
+    <row r="261" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A261" s="17" t="s">
         <v>703</v>
       </c>
       <c r="B261" s="17">
@@ -22237,8 +22244,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="135">
-      <c r="A262" s="8" t="s">
+    <row r="262" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A262" s="17" t="s">
         <v>706</v>
       </c>
       <c r="B262" s="17">
@@ -22293,8 +22300,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="135">
-      <c r="A263" s="8" t="s">
+    <row r="263" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A263" s="17" t="s">
         <v>707</v>
       </c>
       <c r="B263" s="17">
@@ -22349,8 +22356,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="60">
-      <c r="A264" s="8" t="s">
+    <row r="264" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A264" s="17" t="s">
         <v>709</v>
       </c>
       <c r="B264" s="17">
@@ -22405,8 +22412,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="75">
-      <c r="A265" s="8" t="s">
+    <row r="265" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A265" s="17" t="s">
         <v>714</v>
       </c>
       <c r="B265" s="17">
@@ -22461,8 +22468,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="75">
-      <c r="A266" s="8" t="s">
+    <row r="266" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A266" s="17" t="s">
         <v>717</v>
       </c>
       <c r="B266" s="17">
@@ -22517,8 +22524,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="60">
-      <c r="A267" s="8" t="s">
+    <row r="267" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A267" s="17" t="s">
         <v>720</v>
       </c>
       <c r="B267" s="17">
@@ -22573,8 +22580,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="60">
-      <c r="A268" s="8" t="s">
+    <row r="268" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A268" s="17" t="s">
         <v>723</v>
       </c>
       <c r="B268" s="17">
@@ -22629,8 +22636,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="60">
-      <c r="A269" s="8" t="s">
+    <row r="269" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A269" s="17" t="s">
         <v>726</v>
       </c>
       <c r="B269" s="17">
@@ -22685,8 +22692,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="60">
-      <c r="A270" s="8" t="s">
+    <row r="270" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A270" s="17" t="s">
         <v>729</v>
       </c>
       <c r="B270" s="17">
@@ -22741,8 +22748,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="75">
-      <c r="A271" s="8" t="s">
+    <row r="271" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A271" s="17" t="s">
         <v>732</v>
       </c>
       <c r="B271" s="17">
@@ -22797,8 +22804,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="345">
-      <c r="A272" s="8" t="s">
+    <row r="272" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A272" s="17" t="s">
         <v>735</v>
       </c>
       <c r="B272" s="17">
@@ -22853,8 +22860,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="150">
-      <c r="A273" s="8" t="s">
+    <row r="273" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A273" s="17" t="s">
         <v>738</v>
       </c>
       <c r="B273" s="17">
@@ -22909,8 +22916,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="150">
-      <c r="A274" s="8" t="s">
+    <row r="274" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A274" s="17" t="s">
         <v>742</v>
       </c>
       <c r="B274" s="17">
@@ -22965,8 +22972,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="150">
-      <c r="A275" s="8" t="s">
+    <row r="275" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A275" s="17" t="s">
         <v>744</v>
       </c>
       <c r="B275" s="17">
@@ -23021,8 +23028,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="150">
-      <c r="A276" s="8" t="s">
+    <row r="276" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A276" s="17" t="s">
         <v>746</v>
       </c>
       <c r="B276" s="17">
@@ -23077,8 +23084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="150">
-      <c r="A277" s="8" t="s">
+    <row r="277" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A277" s="17" t="s">
         <v>748</v>
       </c>
       <c r="B277" s="17">
@@ -23133,8 +23140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="150">
-      <c r="A278" s="8" t="s">
+    <row r="278" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A278" s="17" t="s">
         <v>750</v>
       </c>
       <c r="B278" s="17">
@@ -23189,8 +23196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="150">
-      <c r="A279" s="8" t="s">
+    <row r="279" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A279" s="17" t="s">
         <v>752</v>
       </c>
       <c r="B279" s="17">
@@ -23245,8 +23252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="150">
-      <c r="A280" s="8" t="s">
+    <row r="280" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A280" s="17" t="s">
         <v>755</v>
       </c>
       <c r="B280" s="17">
@@ -23301,8 +23308,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="150">
-      <c r="A281" s="8" t="s">
+    <row r="281" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A281" s="17" t="s">
         <v>758</v>
       </c>
       <c r="B281" s="17">
@@ -23357,8 +23364,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="150">
-      <c r="A282" s="8" t="s">
+    <row r="282" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A282" s="17" t="s">
         <v>761</v>
       </c>
       <c r="B282" s="17">
@@ -23413,8 +23420,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="150">
-      <c r="A283" s="8" t="s">
+    <row r="283" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A283" s="17" t="s">
         <v>764</v>
       </c>
       <c r="B283" s="17">
@@ -23469,8 +23476,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="150">
-      <c r="A284" s="8" t="s">
+    <row r="284" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A284" s="17" t="s">
         <v>767</v>
       </c>
       <c r="B284" s="17">
@@ -23525,8 +23532,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="150">
-      <c r="A285" s="8" t="s">
+    <row r="285" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A285" s="17" t="s">
         <v>769</v>
       </c>
       <c r="B285" s="17">
@@ -23581,8 +23588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="150">
-      <c r="A286" s="8" t="s">
+    <row r="286" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A286" s="17" t="s">
         <v>772</v>
       </c>
       <c r="B286" s="17">
@@ -23637,8 +23644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="150">
-      <c r="A287" s="8" t="s">
+    <row r="287" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A287" s="17" t="s">
         <v>775</v>
       </c>
       <c r="B287" s="17">
@@ -23693,8 +23700,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="150">
-      <c r="A288" s="8" t="s">
+    <row r="288" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A288" s="17" t="s">
         <v>778</v>
       </c>
       <c r="B288" s="17">
@@ -23749,8 +23756,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="60">
-      <c r="A289" s="8" t="s">
+    <row r="289" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A289" s="17" t="s">
         <v>781</v>
       </c>
       <c r="B289" s="17">
@@ -23805,8 +23812,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="60">
-      <c r="A290" s="8" t="s">
+    <row r="290" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A290" s="17" t="s">
         <v>785</v>
       </c>
       <c r="B290" s="17">
@@ -23861,8 +23868,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="60">
-      <c r="A291" s="8" t="s">
+    <row r="291" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A291" s="17" t="s">
         <v>787</v>
       </c>
       <c r="B291" s="17">
@@ -23917,8 +23924,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="60">
-      <c r="A292" s="8" t="s">
+    <row r="292" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A292" s="17" t="s">
         <v>788</v>
       </c>
       <c r="B292" s="17">
@@ -23973,8 +23980,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="60">
-      <c r="A293" s="8" t="s">
+    <row r="293" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A293" s="17" t="s">
         <v>789</v>
       </c>
       <c r="B293" s="17">
@@ -24029,8 +24036,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="60">
-      <c r="A294" s="8" t="s">
+    <row r="294" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A294" s="17" t="s">
         <v>791</v>
       </c>
       <c r="B294" s="17">
@@ -24085,8 +24092,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="60">
-      <c r="A295" s="8" t="s">
+    <row r="295" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A295" s="17" t="s">
         <v>792</v>
       </c>
       <c r="B295" s="17">
@@ -24141,8 +24148,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="60">
-      <c r="A296" s="8" t="s">
+    <row r="296" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A296" s="17" t="s">
         <v>794</v>
       </c>
       <c r="B296" s="17">
@@ -24197,8 +24204,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="60">
-      <c r="A297" s="8" t="s">
+    <row r="297" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A297" s="17" t="s">
         <v>795</v>
       </c>
       <c r="B297" s="17">
@@ -24253,8 +24260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="60">
-      <c r="A298" s="8" t="s">
+    <row r="298" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A298" s="17" t="s">
         <v>798</v>
       </c>
       <c r="B298" s="17">
@@ -24309,8 +24316,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="60">
-      <c r="A299" s="8" t="s">
+    <row r="299" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A299" s="17" t="s">
         <v>801</v>
       </c>
       <c r="B299" s="17">
@@ -24365,8 +24372,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="60">
-      <c r="A300" s="8" t="s">
+    <row r="300" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A300" s="17" t="s">
         <v>802</v>
       </c>
       <c r="B300" s="17">
@@ -24421,8 +24428,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="60">
-      <c r="A301" s="8" t="s">
+    <row r="301" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A301" s="17" t="s">
         <v>803</v>
       </c>
       <c r="B301" s="17">
@@ -24477,8 +24484,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="60">
-      <c r="A302" s="8" t="s">
+    <row r="302" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A302" s="17" t="s">
         <v>805</v>
       </c>
       <c r="B302" s="17">
@@ -24533,8 +24540,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="60">
-      <c r="A303" s="8" t="s">
+    <row r="303" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A303" s="17" t="s">
         <v>808</v>
       </c>
       <c r="B303" s="17">
@@ -24589,8 +24596,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="135">
-      <c r="A304" s="8" t="s">
+    <row r="304" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A304" s="17" t="s">
         <v>811</v>
       </c>
       <c r="B304" s="17">
@@ -24645,8 +24652,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="135">
-      <c r="A305" s="8" t="s">
+    <row r="305" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A305" s="17" t="s">
         <v>813</v>
       </c>
       <c r="B305" s="17">
@@ -24701,8 +24708,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="135">
-      <c r="A306" s="8" t="s">
+    <row r="306" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A306" s="17" t="s">
         <v>815</v>
       </c>
       <c r="B306" s="17">
@@ -24757,8 +24764,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="135">
-      <c r="A307" s="8" t="s">
+    <row r="307" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A307" s="17" t="s">
         <v>817</v>
       </c>
       <c r="B307" s="17">
@@ -24813,8 +24820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="135">
-      <c r="A308" s="8" t="s">
+    <row r="308" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A308" s="17" t="s">
         <v>819</v>
       </c>
       <c r="B308" s="17">
@@ -24869,8 +24876,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="135">
-      <c r="A309" s="8" t="s">
+    <row r="309" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A309" s="17" t="s">
         <v>822</v>
       </c>
       <c r="B309" s="17">
@@ -24925,8 +24932,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="135">
-      <c r="A310" s="8" t="s">
+    <row r="310" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A310" s="17" t="s">
         <v>824</v>
       </c>
       <c r="B310" s="17">
@@ -24981,8 +24988,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="409.5">
-      <c r="A311" s="8" t="s">
+    <row r="311" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A311" s="17" t="s">
         <v>825</v>
       </c>
       <c r="B311" s="17">
@@ -25037,8 +25044,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="409.5">
-      <c r="A312" s="8" t="s">
+    <row r="312" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="17" t="s">
         <v>827</v>
       </c>
       <c r="B312" s="17">
@@ -25093,8 +25100,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="409.5">
-      <c r="A313" s="8" t="s">
+    <row r="313" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A313" s="17" t="s">
         <v>829</v>
       </c>
       <c r="B313" s="17">
@@ -25149,8 +25156,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="409.5">
-      <c r="A314" s="8" t="s">
+    <row r="314" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A314" s="17" t="s">
         <v>831</v>
       </c>
       <c r="B314" s="17">
@@ -25205,8 +25212,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="409.5">
-      <c r="A315" s="8" t="s">
+    <row r="315" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="17" t="s">
         <v>833</v>
       </c>
       <c r="B315" s="17">
@@ -25261,8 +25268,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="409.5">
-      <c r="A316" s="8" t="s">
+    <row r="316" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A316" s="17" t="s">
         <v>835</v>
       </c>
       <c r="B316" s="17">
@@ -25317,8 +25324,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="409.5">
-      <c r="A317" s="8" t="s">
+    <row r="317" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A317" s="17" t="s">
         <v>838</v>
       </c>
       <c r="B317" s="17">
@@ -25373,8 +25380,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="409.5">
-      <c r="A318" s="8" t="s">
+    <row r="318" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="17" t="s">
         <v>840</v>
       </c>
       <c r="B318" s="17">
@@ -25429,8 +25436,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="409.5">
-      <c r="A319" s="8" t="s">
+    <row r="319" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A319" s="17" t="s">
         <v>843</v>
       </c>
       <c r="B319" s="17">
@@ -25485,8 +25492,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="409.5">
-      <c r="A320" s="8" t="s">
+    <row r="320" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A320" s="17" t="s">
         <v>846</v>
       </c>
       <c r="B320" s="17">
@@ -25541,8 +25548,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="409.5">
-      <c r="A321" s="8" t="s">
+    <row r="321" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="17" t="s">
         <v>849</v>
       </c>
       <c r="B321" s="17">
@@ -25597,8 +25604,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="409.5">
-      <c r="A322" s="8" t="s">
+    <row r="322" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A322" s="17" t="s">
         <v>852</v>
       </c>
       <c r="B322" s="17">
@@ -25653,8 +25660,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="409.5">
-      <c r="A323" s="8" t="s">
+    <row r="323" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A323" s="17" t="s">
         <v>855</v>
       </c>
       <c r="B323" s="17">
@@ -25709,8 +25716,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="409.5">
-      <c r="A324" s="8" t="s">
+    <row r="324" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="17" t="s">
         <v>857</v>
       </c>
       <c r="B324" s="17">
@@ -25765,8 +25772,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="409.5">
-      <c r="A325" s="8" t="s">
+    <row r="325" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A325" s="17" t="s">
         <v>859</v>
       </c>
       <c r="B325" s="17">
@@ -25821,8 +25828,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="409.5">
-      <c r="A326" s="8" t="s">
+    <row r="326" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A326" s="17" t="s">
         <v>861</v>
       </c>
       <c r="B326" s="17">
@@ -25877,8 +25884,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="409.5">
-      <c r="A327" s="8" t="s">
+    <row r="327" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="17" t="s">
         <v>863</v>
       </c>
       <c r="B327" s="17">
@@ -25933,8 +25940,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="409.5">
-      <c r="A328" s="8" t="s">
+    <row r="328" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A328" s="17" t="s">
         <v>865</v>
       </c>
       <c r="B328" s="17">
@@ -25989,8 +25996,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="409.5">
-      <c r="A329" s="8" t="s">
+    <row r="329" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A329" s="17" t="s">
         <v>867</v>
       </c>
       <c r="B329" s="17">
@@ -26045,8 +26052,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="409.5">
-      <c r="A330" s="8" t="s">
+    <row r="330" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="17" t="s">
         <v>869</v>
       </c>
       <c r="B330" s="17">
@@ -26101,8 +26108,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="409.5">
-      <c r="A331" s="8" t="s">
+    <row r="331" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A331" s="17" t="s">
         <v>871</v>
       </c>
       <c r="B331" s="17">
@@ -26157,8 +26164,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="409.5">
-      <c r="A332" s="8" t="s">
+    <row r="332" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A332" s="17" t="s">
         <v>874</v>
       </c>
       <c r="B332" s="17">
@@ -26213,8 +26220,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="409.5">
-      <c r="A333" s="8" t="s">
+    <row r="333" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="17" t="s">
         <v>876</v>
       </c>
       <c r="B333" s="17">
@@ -26269,8 +26276,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="409.5">
-      <c r="A334" s="8" t="s">
+    <row r="334" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A334" s="17" t="s">
         <v>879</v>
       </c>
       <c r="B334" s="17">
@@ -26325,8 +26332,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="409.5">
-      <c r="A335" s="8" t="s">
+    <row r="335" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A335" s="17" t="s">
         <v>882</v>
       </c>
       <c r="B335" s="17">
@@ -26381,8 +26388,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="409.5">
-      <c r="A336" s="8" t="s">
+    <row r="336" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="17" t="s">
         <v>884</v>
       </c>
       <c r="B336" s="17">
@@ -26437,8 +26444,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="60">
-      <c r="A337" s="8" t="s">
+    <row r="337" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A337" s="17" t="s">
         <v>887</v>
       </c>
       <c r="B337" s="17">
@@ -26493,8 +26500,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="60">
-      <c r="A338" s="8" t="s">
+    <row r="338" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A338" s="17" t="s">
         <v>890</v>
       </c>
       <c r="B338" s="17">
@@ -26549,8 +26556,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="60">
-      <c r="A339" s="8" t="s">
+    <row r="339" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A339" s="17" t="s">
         <v>891</v>
       </c>
       <c r="B339" s="17">
@@ -26605,8 +26612,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="60">
-      <c r="A340" s="8" t="s">
+    <row r="340" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A340" s="17" t="s">
         <v>893</v>
       </c>
       <c r="B340" s="17">
@@ -26661,8 +26668,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="60">
-      <c r="A341" s="8" t="s">
+    <row r="341" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A341" s="17" t="s">
         <v>894</v>
       </c>
       <c r="B341" s="17">
@@ -26717,8 +26724,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="60">
-      <c r="A342" s="8" t="s">
+    <row r="342" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A342" s="17" t="s">
         <v>896</v>
       </c>
       <c r="B342" s="17">
@@ -26773,8 +26780,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="60">
-      <c r="A343" s="8" t="s">
+    <row r="343" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A343" s="17" t="s">
         <v>897</v>
       </c>
       <c r="B343" s="17">
@@ -26829,8 +26836,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="60">
-      <c r="A344" s="8" t="s">
+    <row r="344" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A344" s="17" t="s">
         <v>899</v>
       </c>
       <c r="B344" s="17">
@@ -26885,8 +26892,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="60">
-      <c r="A345" s="8" t="s">
+    <row r="345" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A345" s="17" t="s">
         <v>902</v>
       </c>
       <c r="B345" s="17">
@@ -26941,8 +26948,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="60">
-      <c r="A346" s="8" t="s">
+    <row r="346" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A346" s="17" t="s">
         <v>904</v>
       </c>
       <c r="B346" s="17">
@@ -26997,8 +27004,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="75">
-      <c r="A347" s="8" t="s">
+    <row r="347" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A347" s="17" t="s">
         <v>912</v>
       </c>
       <c r="B347" s="17">
@@ -27053,8 +27060,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="60">
-      <c r="A348" s="8" t="s">
+    <row r="348" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A348" s="17" t="s">
         <v>915</v>
       </c>
       <c r="B348" s="17">
@@ -27109,8 +27116,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="75">
-      <c r="A349" s="8" t="s">
+    <row r="349" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A349" s="17" t="s">
         <v>918</v>
       </c>
       <c r="B349" s="17">
@@ -27165,8 +27172,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="75">
-      <c r="A350" s="8" t="s">
+    <row r="350" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A350" s="17" t="s">
         <v>921</v>
       </c>
       <c r="B350" s="17">
@@ -27221,8 +27228,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="60">
-      <c r="A351" s="8" t="s">
+    <row r="351" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A351" s="17" t="s">
         <v>924</v>
       </c>
       <c r="B351" s="17">
@@ -27277,8 +27284,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="60">
-      <c r="A352" s="8" t="s">
+    <row r="352" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A352" s="17" t="s">
         <v>927</v>
       </c>
       <c r="B352" s="17">
@@ -27333,8 +27340,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="60">
-      <c r="A353" s="8" t="s">
+    <row r="353" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A353" s="17" t="s">
         <v>930</v>
       </c>
       <c r="B353" s="17">
@@ -27389,8 +27396,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="60">
-      <c r="A354" s="8" t="s">
+    <row r="354" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A354" s="17" t="s">
         <v>933</v>
       </c>
       <c r="B354" s="17">
@@ -27445,8 +27452,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="75">
-      <c r="A355" s="8" t="s">
+    <row r="355" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A355" s="17" t="s">
         <v>936</v>
       </c>
       <c r="B355" s="17">
@@ -27501,8 +27508,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="75">
-      <c r="A356" s="8" t="s">
+    <row r="356" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A356" s="17" t="s">
         <v>939</v>
       </c>
       <c r="B356" s="17">
@@ -27557,8 +27564,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="75">
-      <c r="A357" s="8" t="s">
+    <row r="357" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A357" s="17" t="s">
         <v>942</v>
       </c>
       <c r="B357" s="17">
@@ -27613,8 +27620,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="75">
-      <c r="A358" s="8" t="s">
+    <row r="358" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A358" s="17" t="s">
         <v>945</v>
       </c>
       <c r="B358" s="17">
@@ -27669,8 +27676,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="60">
-      <c r="A359" s="8" t="s">
+    <row r="359" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A359" s="17" t="s">
         <v>948</v>
       </c>
       <c r="B359" s="17">
@@ -27725,8 +27732,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="60">
-      <c r="A360" s="8" t="s">
+    <row r="360" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A360" s="17" t="s">
         <v>951</v>
       </c>
       <c r="B360" s="17">
@@ -27781,8 +27788,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="60">
-      <c r="A361" s="8" t="s">
+    <row r="361" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A361" s="17" t="s">
         <v>953</v>
       </c>
       <c r="B361" s="17">
@@ -27837,8 +27844,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="60">
-      <c r="A362" s="8" t="s">
+    <row r="362" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A362" s="17" t="s">
         <v>956</v>
       </c>
       <c r="B362" s="17">
@@ -27893,8 +27900,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="60">
-      <c r="A363" s="8" t="s">
+    <row r="363" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A363" s="17" t="s">
         <v>958</v>
       </c>
       <c r="B363" s="17">
@@ -27949,8 +27956,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="60">
-      <c r="A364" s="8" t="s">
+    <row r="364" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A364" s="17" t="s">
         <v>960</v>
       </c>
       <c r="B364" s="17">
@@ -28005,8 +28012,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="60">
-      <c r="A365" s="8" t="s">
+    <row r="365" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A365" s="17" t="s">
         <v>962</v>
       </c>
       <c r="B365" s="17">
@@ -28061,8 +28068,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="60">
-      <c r="A366" s="8" t="s">
+    <row r="366" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A366" s="17" t="s">
         <v>965</v>
       </c>
       <c r="B366" s="17">
@@ -28117,8 +28124,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="60">
-      <c r="A367" s="8" t="s">
+    <row r="367" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A367" s="17" t="s">
         <v>968</v>
       </c>
       <c r="B367" s="17">
@@ -28173,8 +28180,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="60">
-      <c r="A368" s="8" t="s">
+    <row r="368" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A368" s="17" t="s">
         <v>971</v>
       </c>
       <c r="B368" s="17">
@@ -28229,8 +28236,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="60">
-      <c r="A369" s="8" t="s">
+    <row r="369" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A369" s="17" t="s">
         <v>976</v>
       </c>
       <c r="B369" s="17">
@@ -28285,8 +28292,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="60">
-      <c r="A370" s="8" t="s">
+    <row r="370" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A370" s="17" t="s">
         <v>982</v>
       </c>
       <c r="B370" s="17">
@@ -28341,8 +28348,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="60">
-      <c r="A371" s="8" t="s">
+    <row r="371" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A371" s="17" t="s">
         <v>985</v>
       </c>
       <c r="B371" s="17">
@@ -28397,8 +28404,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="60">
-      <c r="A372" s="8" t="s">
+    <row r="372" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A372" s="17" t="s">
         <v>988</v>
       </c>
       <c r="B372" s="17">
@@ -28453,8 +28460,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="60">
-      <c r="A373" s="8" t="s">
+    <row r="373" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A373" s="17" t="s">
         <v>991</v>
       </c>
       <c r="B373" s="17">
@@ -28509,8 +28516,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="60">
-      <c r="A374" s="8" t="s">
+    <row r="374" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A374" s="17" t="s">
         <v>994</v>
       </c>
       <c r="B374" s="17">
@@ -28565,8 +28572,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="60">
-      <c r="A375" s="8" t="s">
+    <row r="375" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A375" s="17" t="s">
         <v>997</v>
       </c>
       <c r="B375" s="17">
@@ -28621,8 +28628,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="60">
-      <c r="A376" s="8" t="s">
+    <row r="376" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A376" s="17" t="s">
         <v>1000</v>
       </c>
       <c r="B376" s="17">
@@ -28677,8 +28684,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="60">
-      <c r="A377" s="8" t="s">
+    <row r="377" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A377" s="17" t="s">
         <v>1003</v>
       </c>
       <c r="B377" s="17">
@@ -28733,8 +28740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="60">
-      <c r="A378" s="8" t="s">
+    <row r="378" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A378" s="17" t="s">
         <v>1006</v>
       </c>
       <c r="B378" s="17">
@@ -28789,8 +28796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="60">
-      <c r="A379" s="8" t="s">
+    <row r="379" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A379" s="17" t="s">
         <v>1009</v>
       </c>
       <c r="B379" s="17">
@@ -28845,8 +28852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="60">
-      <c r="A380" s="8" t="s">
+    <row r="380" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A380" s="17" t="s">
         <v>1014</v>
       </c>
       <c r="B380" s="17">
@@ -28901,8 +28908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="75">
-      <c r="A381" s="8" t="s">
+    <row r="381" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A381" s="17" t="s">
         <v>1016</v>
       </c>
       <c r="B381" s="17">
@@ -28957,8 +28964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="60">
-      <c r="A382" s="8" t="s">
+    <row r="382" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A382" s="17" t="s">
         <v>1019</v>
       </c>
       <c r="B382" s="17">
@@ -29013,8 +29020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="60">
-      <c r="A383" s="8" t="s">
+    <row r="383" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A383" s="17" t="s">
         <v>1022</v>
       </c>
       <c r="B383" s="17">
@@ -29069,8 +29076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="60">
-      <c r="A384" s="8" t="s">
+    <row r="384" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A384" s="17" t="s">
         <v>1025</v>
       </c>
       <c r="B384" s="17">
@@ -29125,8 +29132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="60">
-      <c r="A385" s="8" t="s">
+    <row r="385" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A385" s="17" t="s">
         <v>1028</v>
       </c>
       <c r="B385" s="17">
@@ -29181,8 +29188,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="60">
-      <c r="A386" s="8" t="s">
+    <row r="386" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A386" s="17" t="s">
         <v>1031</v>
       </c>
       <c r="B386" s="17">
@@ -29237,8 +29244,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="60">
-      <c r="A387" s="8" t="s">
+    <row r="387" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A387" s="17" t="s">
         <v>1034</v>
       </c>
       <c r="B387" s="17">
@@ -29293,8 +29300,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="60">
-      <c r="A388" s="8" t="s">
+    <row r="388" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A388" s="17" t="s">
         <v>1037</v>
       </c>
       <c r="B388" s="17">
@@ -29349,8 +29356,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="60">
-      <c r="A389" s="8" t="s">
+    <row r="389" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A389" s="17" t="s">
         <v>1040</v>
       </c>
       <c r="B389" s="17">
@@ -29405,8 +29412,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="60">
-      <c r="A390" s="8" t="s">
+    <row r="390" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A390" s="17" t="s">
         <v>1042</v>
       </c>
       <c r="B390" s="17">
@@ -29461,8 +29468,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="60">
-      <c r="A391" s="8" t="s">
+    <row r="391" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A391" s="17" t="s">
         <v>1044</v>
       </c>
       <c r="B391" s="17">
@@ -29517,8 +29524,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="60">
-      <c r="A392" s="8" t="s">
+    <row r="392" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A392" s="17" t="s">
         <v>1048</v>
       </c>
       <c r="B392" s="17">
@@ -29573,8 +29580,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="60">
-      <c r="A393" s="8" t="s">
+    <row r="393" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A393" s="17" t="s">
         <v>1051</v>
       </c>
       <c r="B393" s="17">
@@ -29629,8 +29636,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="60">
-      <c r="A394" s="8" t="s">
+    <row r="394" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A394" s="17" t="s">
         <v>1054</v>
       </c>
       <c r="B394" s="17">
@@ -29685,8 +29692,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="60">
-      <c r="A395" s="8" t="s">
+    <row r="395" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A395" s="17" t="s">
         <v>1057</v>
       </c>
       <c r="B395" s="17">
@@ -29741,8 +29748,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="60">
-      <c r="A396" s="8" t="s">
+    <row r="396" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A396" s="17" t="s">
         <v>1060</v>
       </c>
       <c r="B396" s="17">
@@ -29797,8 +29804,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="60">
-      <c r="A397" s="8" t="s">
+    <row r="397" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A397" s="17" t="s">
         <v>1063</v>
       </c>
       <c r="B397" s="17">
@@ -29853,8 +29860,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="75">
-      <c r="A398" s="8" t="s">
+    <row r="398" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A398" s="17" t="s">
         <v>1066</v>
       </c>
       <c r="B398" s="17">
@@ -29909,8 +29916,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="60">
-      <c r="A399" s="8" t="s">
+    <row r="399" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A399" s="17" t="s">
         <v>1069</v>
       </c>
       <c r="B399" s="17">
@@ -29965,8 +29972,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="60">
-      <c r="A400" s="8" t="s">
+    <row r="400" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A400" s="17" t="s">
         <v>1072</v>
       </c>
       <c r="B400" s="17">
@@ -30021,8 +30028,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="60">
-      <c r="A401" s="8" t="s">
+    <row r="401" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A401" s="17" t="s">
         <v>1075</v>
       </c>
       <c r="B401" s="17">
@@ -30077,8 +30084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="60">
-      <c r="A402" s="8" t="s">
+    <row r="402" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A402" s="17" t="s">
         <v>1078</v>
       </c>
       <c r="B402" s="17">
@@ -30133,8 +30140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="60">
-      <c r="A403" s="8" t="s">
+    <row r="403" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A403" s="17" t="s">
         <v>1080</v>
       </c>
       <c r="B403" s="17">
@@ -30189,8 +30196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="60">
-      <c r="A404" s="8" t="s">
+    <row r="404" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A404" s="17" t="s">
         <v>1082</v>
       </c>
       <c r="B404" s="17">
@@ -30245,8 +30252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="60">
-      <c r="A405" s="8" t="s">
+    <row r="405" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A405" s="17" t="s">
         <v>1084</v>
       </c>
       <c r="B405" s="17">
@@ -30301,8 +30308,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="60">
-      <c r="A406" s="8" t="s">
+    <row r="406" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A406" s="17" t="s">
         <v>1086</v>
       </c>
       <c r="B406" s="17">
@@ -30357,8 +30364,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="60">
-      <c r="A407" s="8" t="s">
+    <row r="407" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A407" s="17" t="s">
         <v>1088</v>
       </c>
       <c r="B407" s="17">
@@ -30413,8 +30420,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="60">
-      <c r="A408" s="8" t="s">
+    <row r="408" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A408" s="17" t="s">
         <v>1091</v>
       </c>
       <c r="B408" s="17">
@@ -30469,8 +30476,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="60">
-      <c r="A409" s="8" t="s">
+    <row r="409" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A409" s="17" t="s">
         <v>1094</v>
       </c>
       <c r="B409" s="17">
@@ -30525,8 +30532,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="60">
-      <c r="A410" s="8" t="s">
+    <row r="410" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A410" s="17" t="s">
         <v>1097</v>
       </c>
       <c r="B410" s="17">
@@ -30581,8 +30588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="60">
-      <c r="A411" s="8" t="s">
+    <row r="411" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A411" s="17" t="s">
         <v>1099</v>
       </c>
       <c r="B411" s="17">
@@ -30637,8 +30644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="60">
-      <c r="A412" s="8" t="s">
+    <row r="412" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A412" s="17" t="s">
         <v>1102</v>
       </c>
       <c r="B412" s="17">
@@ -30693,8 +30700,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="60">
-      <c r="A413" s="8" t="s">
+    <row r="413" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A413" s="17" t="s">
         <v>1104</v>
       </c>
       <c r="B413" s="17">
@@ -30749,8 +30756,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="60">
-      <c r="A414" s="8" t="s">
+    <row r="414" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A414" s="17" t="s">
         <v>1107</v>
       </c>
       <c r="B414" s="17">
@@ -30805,8 +30812,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="75">
-      <c r="A415" s="8" t="s">
+    <row r="415" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A415" s="17" t="s">
         <v>1110</v>
       </c>
       <c r="B415" s="17">
@@ -30861,8 +30868,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="60">
-      <c r="A416" s="8" t="s">
+    <row r="416" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A416" s="17" t="s">
         <v>1113</v>
       </c>
       <c r="B416" s="17">
@@ -30917,8 +30924,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="60">
-      <c r="A417" s="8" t="s">
+    <row r="417" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A417" s="17" t="s">
         <v>1115</v>
       </c>
       <c r="B417" s="17">
@@ -30973,8 +30980,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="60">
-      <c r="A418" s="8" t="s">
+    <row r="418" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A418" s="17" t="s">
         <v>1117</v>
       </c>
       <c r="B418" s="17">
@@ -31029,8 +31036,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="60">
-      <c r="A419" s="8" t="s">
+    <row r="419" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A419" s="17" t="s">
         <v>1120</v>
       </c>
       <c r="B419" s="17">
@@ -31085,8 +31092,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="60">
-      <c r="A420" s="8" t="s">
+    <row r="420" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A420" s="17" t="s">
         <v>1123</v>
       </c>
       <c r="B420" s="17">
@@ -31141,8 +31148,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="60">
-      <c r="A421" s="8" t="s">
+    <row r="421" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A421" s="17" t="s">
         <v>1126</v>
       </c>
       <c r="B421" s="17">
@@ -31197,8 +31204,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="60">
-      <c r="A422" s="8" t="s">
+    <row r="422" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A422" s="17" t="s">
         <v>1129</v>
       </c>
       <c r="B422" s="17">
@@ -31253,8 +31260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="60">
-      <c r="A423" s="8" t="s">
+    <row r="423" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A423" s="17" t="s">
         <v>1131</v>
       </c>
       <c r="B423" s="17">
@@ -31309,8 +31316,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="90">
-      <c r="A424" s="8" t="s">
+    <row r="424" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A424" s="17" t="s">
         <v>1134</v>
       </c>
       <c r="B424" s="17">
@@ -31365,8 +31372,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="90">
-      <c r="A425" s="8" t="s">
+    <row r="425" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A425" s="17" t="s">
         <v>1137</v>
       </c>
       <c r="B425" s="17">
@@ -31421,8 +31428,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="75">
-      <c r="A426" s="8" t="s">
+    <row r="426" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A426" s="17" t="s">
         <v>1140</v>
       </c>
       <c r="B426" s="17">
@@ -31477,8 +31484,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="75">
-      <c r="A427" s="8" t="s">
+    <row r="427" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A427" s="17" t="s">
         <v>1144</v>
       </c>
       <c r="B427" s="17">
@@ -31533,8 +31540,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="75">
-      <c r="A428" s="8" t="s">
+    <row r="428" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A428" s="17" t="s">
         <v>1147</v>
       </c>
       <c r="B428" s="17">
@@ -31589,8 +31596,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="75">
-      <c r="A429" s="8" t="s">
+    <row r="429" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A429" s="17" t="s">
         <v>1150</v>
       </c>
       <c r="B429" s="17">
@@ -31645,8 +31652,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="75">
-      <c r="A430" s="8" t="s">
+    <row r="430" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A430" s="17" t="s">
         <v>1153</v>
       </c>
       <c r="B430" s="17">
@@ -31701,8 +31708,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="75">
-      <c r="A431" s="8" t="s">
+    <row r="431" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A431" s="17" t="s">
         <v>1155</v>
       </c>
       <c r="B431" s="17">
@@ -31757,8 +31764,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="75">
-      <c r="A432" s="8" t="s">
+    <row r="432" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A432" s="17" t="s">
         <v>1158</v>
       </c>
       <c r="B432" s="17">
@@ -31813,8 +31820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="75">
-      <c r="A433" s="8" t="s">
+    <row r="433" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A433" s="17" t="s">
         <v>1161</v>
       </c>
       <c r="B433" s="17">
@@ -31869,8 +31876,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="75">
-      <c r="A434" s="8" t="s">
+    <row r="434" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A434" s="17" t="s">
         <v>1164</v>
       </c>
       <c r="B434" s="17">
@@ -31925,8 +31932,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="75">
-      <c r="A435" s="8" t="s">
+    <row r="435" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A435" s="17" t="s">
         <v>1167</v>
       </c>
       <c r="B435" s="17">
@@ -31981,8 +31988,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="75">
-      <c r="A436" s="8" t="s">
+    <row r="436" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A436" s="17" t="s">
         <v>1170</v>
       </c>
       <c r="B436" s="17">
@@ -32037,8 +32044,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="75">
-      <c r="A437" s="8" t="s">
+    <row r="437" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A437" s="17" t="s">
         <v>1173</v>
       </c>
       <c r="B437" s="17">
@@ -32093,8 +32100,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="60">
-      <c r="A438" s="8" t="s">
+    <row r="438" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A438" s="17" t="s">
         <v>1176</v>
       </c>
       <c r="B438" s="17">
@@ -32149,8 +32156,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="60">
-      <c r="A439" s="8" t="s">
+    <row r="439" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A439" s="17" t="s">
         <v>1180</v>
       </c>
       <c r="B439" s="17">
@@ -32205,8 +32212,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="60">
-      <c r="A440" s="8" t="s">
+    <row r="440" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A440" s="17" t="s">
         <v>1183</v>
       </c>
       <c r="B440" s="17">
@@ -32261,8 +32268,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="60">
-      <c r="A441" s="8" t="s">
+    <row r="441" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A441" s="17" t="s">
         <v>1186</v>
       </c>
       <c r="B441" s="17">
@@ -32317,8 +32324,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="60">
-      <c r="A442" s="8" t="s">
+    <row r="442" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A442" s="17" t="s">
         <v>1189</v>
       </c>
       <c r="B442" s="17">
@@ -32373,8 +32380,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="60">
-      <c r="A443" s="8" t="s">
+    <row r="443" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A443" s="17" t="s">
         <v>1192</v>
       </c>
       <c r="B443" s="17">
@@ -32429,8 +32436,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="60">
-      <c r="A444" s="8" t="s">
+    <row r="444" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A444" s="17" t="s">
         <v>1195</v>
       </c>
       <c r="B444" s="17">
@@ -32485,8 +32492,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="60">
-      <c r="A445" s="8" t="s">
+    <row r="445" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A445" s="17" t="s">
         <v>1198</v>
       </c>
       <c r="B445" s="17">
@@ -32541,8 +32548,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="60">
-      <c r="A446" s="8" t="s">
+    <row r="446" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A446" s="17" t="s">
         <v>1201</v>
       </c>
       <c r="B446" s="17">
@@ -32597,8 +32604,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="60">
-      <c r="A447" s="8" t="s">
+    <row r="447" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A447" s="17" t="s">
         <v>1204</v>
       </c>
       <c r="B447" s="17">
@@ -32653,8 +32660,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="60">
-      <c r="A448" s="8" t="s">
+    <row r="448" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A448" s="17" t="s">
         <v>1207</v>
       </c>
       <c r="B448" s="17">
@@ -32709,8 +32716,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="60">
-      <c r="A449" s="8" t="s">
+    <row r="449" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A449" s="17" t="s">
         <v>1210</v>
       </c>
       <c r="B449" s="17">
@@ -32765,8 +32772,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="60">
-      <c r="A450" s="8" t="s">
+    <row r="450" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A450" s="17" t="s">
         <v>1213</v>
       </c>
       <c r="B450" s="17">
@@ -32821,8 +32828,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="195">
-      <c r="A451" s="8" t="s">
+    <row r="451" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A451" s="17" t="s">
         <v>1216</v>
       </c>
       <c r="B451" s="17">
@@ -32877,8 +32884,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="195">
-      <c r="A452" s="8" t="s">
+    <row r="452" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A452" s="17" t="s">
         <v>1219</v>
       </c>
       <c r="B452" s="17">
@@ -32933,8 +32940,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="195">
-      <c r="A453" s="8" t="s">
+    <row r="453" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A453" s="17" t="s">
         <v>1222</v>
       </c>
       <c r="B453" s="17">
@@ -32989,8 +32996,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="75">
-      <c r="A454" s="8" t="s">
+    <row r="454" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A454" s="17" t="s">
         <v>1224</v>
       </c>
       <c r="B454" s="17">
@@ -33045,8 +33052,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="75">
-      <c r="A455" s="8" t="s">
+    <row r="455" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A455" s="17" t="s">
         <v>1228</v>
       </c>
       <c r="B455" s="17">
@@ -33101,8 +33108,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="75">
-      <c r="A456" s="8" t="s">
+    <row r="456" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A456" s="17" t="s">
         <v>1231</v>
       </c>
       <c r="B456" s="17">
@@ -33157,8 +33164,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="75">
-      <c r="A457" s="8" t="s">
+    <row r="457" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A457" s="17" t="s">
         <v>1234</v>
       </c>
       <c r="B457" s="17">
@@ -33213,8 +33220,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="75">
-      <c r="A458" s="8" t="s">
+    <row r="458" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A458" s="17" t="s">
         <v>1237</v>
       </c>
       <c r="B458" s="17">
@@ -33269,8 +33276,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="75">
-      <c r="A459" s="8" t="s">
+    <row r="459" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A459" s="17" t="s">
         <v>1240</v>
       </c>
       <c r="B459" s="17">
@@ -33325,8 +33332,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="75">
-      <c r="A460" s="8" t="s">
+    <row r="460" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A460" s="17" t="s">
         <v>1243</v>
       </c>
       <c r="B460" s="17">
@@ -33381,8 +33388,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="75">
-      <c r="A461" s="8" t="s">
+    <row r="461" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A461" s="17" t="s">
         <v>1246</v>
       </c>
       <c r="B461" s="17">
@@ -33437,8 +33444,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="75">
-      <c r="A462" s="8" t="s">
+    <row r="462" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A462" s="17" t="s">
         <v>1249</v>
       </c>
       <c r="B462" s="17">
@@ -33493,8 +33500,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="75">
-      <c r="A463" s="8" t="s">
+    <row r="463" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A463" s="17" t="s">
         <v>1252</v>
       </c>
       <c r="B463" s="17">
@@ -33549,8 +33556,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="75">
-      <c r="A464" s="8" t="s">
+    <row r="464" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A464" s="17" t="s">
         <v>1255</v>
       </c>
       <c r="B464" s="17">
@@ -33605,8 +33612,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="60">
-      <c r="A465" s="8" t="s">
+    <row r="465" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A465" s="17" t="s">
         <v>1258</v>
       </c>
       <c r="B465" s="17">
@@ -33661,8 +33668,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="60">
-      <c r="A466" s="8" t="s">
+    <row r="466" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A466" s="17" t="s">
         <v>1261</v>
       </c>
       <c r="B466" s="17">
@@ -33717,8 +33724,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="345">
-      <c r="A467" s="8" t="s">
+    <row r="467" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A467" s="17" t="s">
         <v>1263</v>
       </c>
       <c r="B467" s="17">
@@ -33773,8 +33780,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="345">
-      <c r="A468" s="8" t="s">
+    <row r="468" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A468" s="17" t="s">
         <v>1266</v>
       </c>
       <c r="B468" s="17">
@@ -33829,8 +33836,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="345">
-      <c r="A469" s="8" t="s">
+    <row r="469" spans="1:18" ht="345" x14ac:dyDescent="0.25">
+      <c r="A469" s="17" t="s">
         <v>1269</v>
       </c>
       <c r="B469" s="17">
@@ -33885,8 +33892,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="75">
-      <c r="A470" s="8" t="s">
+    <row r="470" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A470" s="17" t="s">
         <v>1272</v>
       </c>
       <c r="B470" s="17">
@@ -33941,8 +33948,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="60">
-      <c r="A471" s="8" t="s">
+    <row r="471" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A471" s="17" t="s">
         <v>1276</v>
       </c>
       <c r="B471" s="17">
@@ -33997,8 +34004,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="60">
-      <c r="A472" s="8" t="s">
+    <row r="472" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A472" s="17" t="s">
         <v>1279</v>
       </c>
       <c r="B472" s="17">
@@ -34053,8 +34060,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="60">
-      <c r="A473" s="8" t="s">
+    <row r="473" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A473" s="17" t="s">
         <v>1282</v>
       </c>
       <c r="B473" s="17">
@@ -34109,8 +34116,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="60">
-      <c r="A474" s="8" t="s">
+    <row r="474" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A474" s="17" t="s">
         <v>1285</v>
       </c>
       <c r="B474" s="17">
@@ -34165,8 +34172,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="75">
-      <c r="A475" s="8" t="s">
+    <row r="475" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A475" s="17" t="s">
         <v>1288</v>
       </c>
       <c r="B475" s="17">
@@ -34221,8 +34228,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="75">
-      <c r="A476" s="8" t="s">
+    <row r="476" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A476" s="17" t="s">
         <v>1291</v>
       </c>
       <c r="B476" s="17">
@@ -34277,8 +34284,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="60">
-      <c r="A477" s="8" t="s">
+    <row r="477" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A477" s="17" t="s">
         <v>1296</v>
       </c>
       <c r="B477" s="17">
@@ -34333,8 +34340,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="60">
-      <c r="A478" s="8" t="s">
+    <row r="478" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A478" s="17" t="s">
         <v>1300</v>
       </c>
       <c r="B478" s="17">
@@ -34389,8 +34396,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="60">
-      <c r="A479" s="8" t="s">
+    <row r="479" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A479" s="17" t="s">
         <v>1303</v>
       </c>
       <c r="B479" s="17">
@@ -34445,8 +34452,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="60">
-      <c r="A480" s="8" t="s">
+    <row r="480" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A480" s="17" t="s">
         <v>1306</v>
       </c>
       <c r="B480" s="17">
@@ -34501,8 +34508,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="60">
-      <c r="A481" s="8" t="s">
+    <row r="481" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A481" s="17" t="s">
         <v>1309</v>
       </c>
       <c r="B481" s="17">
@@ -34557,8 +34564,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="60">
-      <c r="A482" s="8" t="s">
+    <row r="482" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A482" s="17" t="s">
         <v>1312</v>
       </c>
       <c r="B482" s="17">
@@ -34613,8 +34620,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="60">
-      <c r="A483" s="8" t="s">
+    <row r="483" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A483" s="17" t="s">
         <v>1315</v>
       </c>
       <c r="B483" s="17">
@@ -34669,8 +34676,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="60">
-      <c r="A484" s="8" t="s">
+    <row r="484" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A484" s="17" t="s">
         <v>1318</v>
       </c>
       <c r="B484" s="17">
@@ -34725,8 +34732,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="60">
-      <c r="A485" s="8" t="s">
+    <row r="485" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A485" s="17" t="s">
         <v>1321</v>
       </c>
       <c r="B485" s="17">
@@ -34781,8 +34788,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="60">
-      <c r="A486" s="8" t="s">
+    <row r="486" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A486" s="17" t="s">
         <v>1324</v>
       </c>
       <c r="B486" s="17">
@@ -34837,8 +34844,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="60">
-      <c r="A487" s="8" t="s">
+    <row r="487" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A487" s="17" t="s">
         <v>1326</v>
       </c>
       <c r="B487" s="17">
@@ -34893,8 +34900,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="60">
-      <c r="A488" s="8" t="s">
+    <row r="488" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A488" s="17" t="s">
         <v>1328</v>
       </c>
       <c r="B488" s="17">
@@ -34949,8 +34956,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="60">
-      <c r="A489" s="8" t="s">
+    <row r="489" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A489" s="17" t="s">
         <v>1330</v>
       </c>
       <c r="B489" s="17">
@@ -35005,8 +35012,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="60">
-      <c r="A490" s="8" t="s">
+    <row r="490" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A490" s="17" t="s">
         <v>1332</v>
       </c>
       <c r="B490" s="17">
@@ -35061,8 +35068,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="60">
-      <c r="A491" s="8" t="s">
+    <row r="491" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A491" s="17" t="s">
         <v>1335</v>
       </c>
       <c r="B491" s="17">
@@ -35117,8 +35124,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="60">
-      <c r="A492" s="8" t="s">
+    <row r="492" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A492" s="17" t="s">
         <v>1337</v>
       </c>
       <c r="B492" s="17">
@@ -35173,8 +35180,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="60">
-      <c r="A493" s="8" t="s">
+    <row r="493" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A493" s="17" t="s">
         <v>1339</v>
       </c>
       <c r="B493" s="17">
@@ -35229,8 +35236,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="60">
-      <c r="A494" s="8" t="s">
+    <row r="494" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A494" s="17" t="s">
         <v>1341</v>
       </c>
       <c r="B494" s="17">
@@ -35285,8 +35292,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="60">
-      <c r="A495" s="8" t="s">
+    <row r="495" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A495" s="17" t="s">
         <v>1344</v>
       </c>
       <c r="B495" s="17">
@@ -35341,8 +35348,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="60">
-      <c r="A496" s="8" t="s">
+    <row r="496" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A496" s="17" t="s">
         <v>1346</v>
       </c>
       <c r="B496" s="17">
@@ -35397,8 +35404,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="60">
-      <c r="A497" s="8" t="s">
+    <row r="497" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A497" s="17" t="s">
         <v>1349</v>
       </c>
       <c r="B497" s="17">
@@ -35453,8 +35460,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="409.5">
-      <c r="A498" s="8" t="s">
+    <row r="498" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A498" s="17" t="s">
         <v>1352</v>
       </c>
       <c r="B498" s="17">
@@ -35509,8 +35516,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="409.5">
-      <c r="A499" s="8" t="s">
+    <row r="499" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A499" s="17" t="s">
         <v>1354</v>
       </c>
       <c r="B499" s="17">
@@ -35565,8 +35572,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="409.5">
-      <c r="A500" s="8" t="s">
+    <row r="500" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A500" s="17" t="s">
         <v>1356</v>
       </c>
       <c r="B500" s="17">
@@ -35621,8 +35628,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="409.5">
-      <c r="A501" s="8" t="s">
+    <row r="501" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A501" s="17" t="s">
         <v>1358</v>
       </c>
       <c r="B501" s="17">
@@ -35677,8 +35684,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="409.5">
-      <c r="A502" s="8" t="s">
+    <row r="502" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A502" s="17" t="s">
         <v>1360</v>
       </c>
       <c r="B502" s="17">
@@ -35733,8 +35740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="409.5">
-      <c r="A503" s="8" t="s">
+    <row r="503" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A503" s="17" t="s">
         <v>1362</v>
       </c>
       <c r="B503" s="17">
@@ -35789,8 +35796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="409.5">
-      <c r="A504" s="8" t="s">
+    <row r="504" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A504" s="17" t="s">
         <v>1363</v>
       </c>
       <c r="B504" s="17">
@@ -35845,8 +35852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="409.5">
-      <c r="A505" s="8" t="s">
+    <row r="505" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A505" s="17" t="s">
         <v>1366</v>
       </c>
       <c r="B505" s="17">
@@ -35901,8 +35908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="409.5">
-      <c r="A506" s="8" t="s">
+    <row r="506" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A506" s="17" t="s">
         <v>1368</v>
       </c>
       <c r="B506" s="17">
@@ -35957,8 +35964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="409.5">
-      <c r="A507" s="8" t="s">
+    <row r="507" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A507" s="17" t="s">
         <v>1370</v>
       </c>
       <c r="B507" s="17">
@@ -36013,8 +36020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="409.5">
-      <c r="A508" s="8" t="s">
+    <row r="508" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A508" s="17" t="s">
         <v>1372</v>
       </c>
       <c r="B508" s="17">
@@ -36069,8 +36076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="409.5">
-      <c r="A509" s="8" t="s">
+    <row r="509" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A509" s="17" t="s">
         <v>1374</v>
       </c>
       <c r="B509" s="17">
@@ -36125,8 +36132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="409.5">
-      <c r="A510" s="8" t="s">
+    <row r="510" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A510" s="17" t="s">
         <v>1377</v>
       </c>
       <c r="B510" s="17">
@@ -36181,8 +36188,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="409.5">
-      <c r="A511" s="8" t="s">
+    <row r="511" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A511" s="17" t="s">
         <v>1380</v>
       </c>
       <c r="B511" s="17">
@@ -36237,8 +36244,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="409.5">
-      <c r="A512" s="8" t="s">
+    <row r="512" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A512" s="17" t="s">
         <v>1383</v>
       </c>
       <c r="B512" s="17">
@@ -36293,8 +36300,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="409.5">
-      <c r="A513" s="8" t="s">
+    <row r="513" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A513" s="17" t="s">
         <v>1386</v>
       </c>
       <c r="B513" s="17">
@@ -36349,8 +36356,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="409.5">
-      <c r="A514" s="8" t="s">
+    <row r="514" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A514" s="17" t="s">
         <v>1389</v>
       </c>
       <c r="B514" s="17">
@@ -36405,8 +36412,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="75">
-      <c r="A515" s="8" t="s">
+    <row r="515" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A515" s="17" t="s">
         <v>1392</v>
       </c>
       <c r="B515" s="17">
@@ -36461,8 +36468,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="330">
-      <c r="A516" s="8" t="s">
+    <row r="516" spans="1:18" ht="330" x14ac:dyDescent="0.25">
+      <c r="A516" s="17" t="s">
         <v>1395</v>
       </c>
       <c r="B516" s="17">
@@ -36517,8 +36524,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="75">
-      <c r="A517" s="8" t="s">
+    <row r="517" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A517" s="17" t="s">
         <v>1397</v>
       </c>
       <c r="B517" s="17">
@@ -36573,8 +36580,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="60">
-      <c r="A518" s="8" t="s">
+    <row r="518" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A518" s="17" t="s">
         <v>1404</v>
       </c>
       <c r="B518" s="17">
@@ -36629,8 +36636,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="75">
-      <c r="A519" s="8" t="s">
+    <row r="519" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A519" s="17" t="s">
         <v>1407</v>
       </c>
       <c r="B519" s="17">
@@ -36685,8 +36692,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="75">
-      <c r="A520" s="8" t="s">
+    <row r="520" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A520" s="17" t="s">
         <v>1410</v>
       </c>
       <c r="B520" s="17">
@@ -36741,8 +36748,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="75">
-      <c r="A521" s="8" t="s">
+    <row r="521" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A521" s="17" t="s">
         <v>1413</v>
       </c>
       <c r="B521" s="17">
@@ -36797,8 +36804,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="60">
-      <c r="A522" s="8" t="s">
+    <row r="522" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A522" s="17" t="s">
         <v>1416</v>
       </c>
       <c r="B522" s="17">
@@ -36853,8 +36860,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="60">
-      <c r="A523" s="8" t="s">
+    <row r="523" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A523" s="17" t="s">
         <v>1421</v>
       </c>
       <c r="B523" s="17">
@@ -36909,8 +36916,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="60">
-      <c r="A524" s="8" t="s">
+    <row r="524" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A524" s="17" t="s">
         <v>1424</v>
       </c>
       <c r="B524" s="17">
@@ -36965,8 +36972,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="60">
-      <c r="A525" s="8" t="s">
+    <row r="525" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A525" s="17" t="s">
         <v>1427</v>
       </c>
       <c r="B525" s="17">
@@ -37021,8 +37028,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="60">
-      <c r="A526" s="8" t="s">
+    <row r="526" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A526" s="17" t="s">
         <v>1429</v>
       </c>
       <c r="B526" s="17">
@@ -37077,8 +37084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="60">
-      <c r="A527" s="8" t="s">
+    <row r="527" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A527" s="17" t="s">
         <v>1431</v>
       </c>
       <c r="B527" s="17">
@@ -37133,8 +37140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="75">
-      <c r="A528" s="8" t="s">
+    <row r="528" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A528" s="17" t="s">
         <v>1433</v>
       </c>
       <c r="B528" s="17">
@@ -37189,8 +37196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="60">
-      <c r="A529" s="8" t="s">
+    <row r="529" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A529" s="17" t="s">
         <v>1436</v>
       </c>
       <c r="B529" s="17">
@@ -37245,8 +37252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="60">
-      <c r="A530" s="8" t="s">
+    <row r="530" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A530" s="17" t="s">
         <v>1439</v>
       </c>
       <c r="B530" s="17">
@@ -37301,8 +37308,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="60">
-      <c r="A531" s="8" t="s">
+    <row r="531" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A531" s="17" t="s">
         <v>1442</v>
       </c>
       <c r="B531" s="17">
@@ -37357,8 +37364,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="60">
-      <c r="A532" s="8" t="s">
+    <row r="532" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A532" s="17" t="s">
         <v>1444</v>
       </c>
       <c r="B532" s="17">
@@ -37413,8 +37420,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="60">
-      <c r="A533" s="8" t="s">
+    <row r="533" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A533" s="17" t="s">
         <v>1446</v>
       </c>
       <c r="B533" s="17">
@@ -37469,8 +37476,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="60">
-      <c r="A534" s="8" t="s">
+    <row r="534" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A534" s="17" t="s">
         <v>1448</v>
       </c>
       <c r="B534" s="17">
@@ -37525,8 +37532,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="60">
-      <c r="A535" s="8" t="s">
+    <row r="535" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A535" s="17" t="s">
         <v>1450</v>
       </c>
       <c r="B535" s="17">
@@ -37581,8 +37588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="60">
-      <c r="A536" s="8" t="s">
+    <row r="536" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A536" s="17" t="s">
         <v>1452</v>
       </c>
       <c r="B536" s="17">
@@ -37637,8 +37644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="60">
-      <c r="A537" s="8" t="s">
+    <row r="537" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A537" s="17" t="s">
         <v>1454</v>
       </c>
       <c r="B537" s="17">
@@ -37693,8 +37700,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="60">
-      <c r="A538" s="8" t="s">
+    <row r="538" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A538" s="17" t="s">
         <v>1456</v>
       </c>
       <c r="B538" s="17">
@@ -37749,8 +37756,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="60">
-      <c r="A539" s="8" t="s">
+    <row r="539" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A539" s="17" t="s">
         <v>1458</v>
       </c>
       <c r="B539" s="17">
@@ -37805,8 +37812,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="90">
-      <c r="A540" s="8" t="s">
+    <row r="540" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A540" s="17" t="s">
         <v>1460</v>
       </c>
       <c r="B540" s="17">
@@ -37861,8 +37868,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="60">
-      <c r="A541" s="8" t="s">
+    <row r="541" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A541" s="17" t="s">
         <v>1463</v>
       </c>
       <c r="B541" s="17">
@@ -37917,8 +37924,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="60">
-      <c r="A542" s="8" t="s">
+    <row r="542" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A542" s="17" t="s">
         <v>1466</v>
       </c>
       <c r="B542" s="17">
@@ -37973,8 +37980,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="60">
-      <c r="A543" s="8" t="s">
+    <row r="543" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A543" s="17" t="s">
         <v>1468</v>
       </c>
       <c r="B543" s="17">
@@ -38029,8 +38036,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="60">
-      <c r="A544" s="8" t="s">
+    <row r="544" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A544" s="17" t="s">
         <v>1470</v>
       </c>
       <c r="B544" s="17">
@@ -38085,8 +38092,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="60">
-      <c r="A545" s="8" t="s">
+    <row r="545" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A545" s="17" t="s">
         <v>1472</v>
       </c>
       <c r="B545" s="17">
@@ -38141,8 +38148,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="60">
-      <c r="A546" s="8" t="s">
+    <row r="546" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A546" s="17" t="s">
         <v>1474</v>
       </c>
       <c r="B546" s="17">
@@ -38197,8 +38204,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="60">
-      <c r="A547" s="8" t="s">
+    <row r="547" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A547" s="17" t="s">
         <v>1476</v>
       </c>
       <c r="B547" s="17">
@@ -38253,8 +38260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="60">
-      <c r="A548" s="8" t="s">
+    <row r="548" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A548" s="17" t="s">
         <v>1478</v>
       </c>
       <c r="B548" s="17">
@@ -38309,8 +38316,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="60">
-      <c r="A549" s="8" t="s">
+    <row r="549" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A549" s="17" t="s">
         <v>1480</v>
       </c>
       <c r="B549" s="17">
@@ -38365,8 +38372,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="60">
-      <c r="A550" s="8" t="s">
+    <row r="550" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A550" s="17" t="s">
         <v>1482</v>
       </c>
       <c r="B550" s="17">
@@ -38421,8 +38428,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="60">
-      <c r="A551" s="8" t="s">
+    <row r="551" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A551" s="17" t="s">
         <v>1484</v>
       </c>
       <c r="B551" s="17">
@@ -38477,8 +38484,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="60">
-      <c r="A552" s="8" t="s">
+    <row r="552" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A552" s="17" t="s">
         <v>1487</v>
       </c>
       <c r="B552" s="17">
@@ -38533,8 +38540,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="60">
-      <c r="A553" s="8" t="s">
+    <row r="553" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A553" s="17" t="s">
         <v>1489</v>
       </c>
       <c r="B553" s="17">
@@ -38589,8 +38596,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="210">
-      <c r="A554" s="8" t="s">
+    <row r="554" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A554" s="17" t="s">
         <v>1492</v>
       </c>
       <c r="B554" s="17">
@@ -38645,8 +38652,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="210">
-      <c r="A555" s="8" t="s">
+    <row r="555" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A555" s="17" t="s">
         <v>1497</v>
       </c>
       <c r="B555" s="17">
@@ -38701,8 +38708,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="556" spans="1:18" ht="210">
-      <c r="A556" s="8" t="s">
+    <row r="556" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A556" s="17" t="s">
         <v>1500</v>
       </c>
       <c r="B556" s="17">
@@ -38757,8 +38764,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="210">
-      <c r="A557" s="8" t="s">
+    <row r="557" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A557" s="17" t="s">
         <v>1501</v>
       </c>
       <c r="B557" s="17">
@@ -38813,8 +38820,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="210">
-      <c r="A558" s="8" t="s">
+    <row r="558" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A558" s="17" t="s">
         <v>1502</v>
       </c>
       <c r="B558" s="17">
@@ -38869,8 +38876,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="210">
-      <c r="A559" s="8" t="s">
+    <row r="559" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A559" s="17" t="s">
         <v>1503</v>
       </c>
       <c r="B559" s="17">
@@ -38925,8 +38932,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="210">
-      <c r="A560" s="8" t="s">
+    <row r="560" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A560" s="17" t="s">
         <v>1506</v>
       </c>
       <c r="B560" s="17">
@@ -38981,8 +38988,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="210">
-      <c r="A561" s="8" t="s">
+    <row r="561" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A561" s="17" t="s">
         <v>1508</v>
       </c>
       <c r="B561" s="17">
@@ -39037,8 +39044,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="210">
-      <c r="A562" s="8" t="s">
+    <row r="562" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A562" s="17" t="s">
         <v>1510</v>
       </c>
       <c r="B562" s="17">
@@ -39093,8 +39100,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="210">
-      <c r="A563" s="8" t="s">
+    <row r="563" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A563" s="17" t="s">
         <v>1512</v>
       </c>
       <c r="B563" s="17">
@@ -39149,8 +39156,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="210">
-      <c r="A564" s="8" t="s">
+    <row r="564" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A564" s="17" t="s">
         <v>1514</v>
       </c>
       <c r="B564" s="17">
@@ -39205,8 +39212,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="210">
-      <c r="A565" s="8" t="s">
+    <row r="565" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A565" s="17" t="s">
         <v>1517</v>
       </c>
       <c r="B565" s="17">
@@ -39261,8 +39268,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="210">
-      <c r="A566" s="8" t="s">
+    <row r="566" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A566" s="17" t="s">
         <v>1520</v>
       </c>
       <c r="B566" s="17">
@@ -39317,8 +39324,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="210">
-      <c r="A567" s="8" t="s">
+    <row r="567" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A567" s="17" t="s">
         <v>1523</v>
       </c>
       <c r="B567" s="17">
@@ -39373,8 +39380,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="210">
-      <c r="A568" s="8" t="s">
+    <row r="568" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A568" s="17" t="s">
         <v>1526</v>
       </c>
       <c r="B568" s="17">
@@ -39429,8 +39436,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="210">
-      <c r="A569" s="8" t="s">
+    <row r="569" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A569" s="17" t="s">
         <v>1529</v>
       </c>
       <c r="B569" s="17">
@@ -39485,8 +39492,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="210">
-      <c r="A570" s="8" t="s">
+    <row r="570" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A570" s="17" t="s">
         <v>1532</v>
       </c>
       <c r="B570" s="17">
@@ -39541,8 +39548,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="210">
-      <c r="A571" s="8" t="s">
+    <row r="571" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A571" s="17" t="s">
         <v>1535</v>
       </c>
       <c r="B571" s="17">
@@ -39597,8 +39604,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="210">
-      <c r="A572" s="8" t="s">
+    <row r="572" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A572" s="17" t="s">
         <v>1538</v>
       </c>
       <c r="B572" s="17">
@@ -39653,8 +39660,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="210">
-      <c r="A573" s="8" t="s">
+    <row r="573" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A573" s="17" t="s">
         <v>1541</v>
       </c>
       <c r="B573" s="17">
@@ -39709,8 +39716,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="210">
-      <c r="A574" s="8" t="s">
+    <row r="574" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A574" s="17" t="s">
         <v>1544</v>
       </c>
       <c r="B574" s="17">
@@ -39765,8 +39772,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="210">
-      <c r="A575" s="8" t="s">
+    <row r="575" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A575" s="17" t="s">
         <v>1547</v>
       </c>
       <c r="B575" s="17">
@@ -39821,8 +39828,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="210">
-      <c r="A576" s="8" t="s">
+    <row r="576" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A576" s="17" t="s">
         <v>1550</v>
       </c>
       <c r="B576" s="17">
@@ -39877,8 +39884,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="210">
-      <c r="A577" s="8" t="s">
+    <row r="577" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A577" s="17" t="s">
         <v>1553</v>
       </c>
       <c r="B577" s="17">
@@ -39933,8 +39940,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="210">
-      <c r="A578" s="8" t="s">
+    <row r="578" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A578" s="17" t="s">
         <v>1556</v>
       </c>
       <c r="B578" s="17">
@@ -39989,8 +39996,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="210">
-      <c r="A579" s="8" t="s">
+    <row r="579" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A579" s="17" t="s">
         <v>1559</v>
       </c>
       <c r="B579" s="17">
@@ -40045,8 +40052,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="210">
-      <c r="A580" s="8" t="s">
+    <row r="580" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A580" s="17" t="s">
         <v>1562</v>
       </c>
       <c r="B580" s="17">
@@ -40101,8 +40108,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="210">
-      <c r="A581" s="8" t="s">
+    <row r="581" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A581" s="17" t="s">
         <v>1565</v>
       </c>
       <c r="B581" s="17">
@@ -40157,8 +40164,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="210">
-      <c r="A582" s="8" t="s">
+    <row r="582" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A582" s="17" t="s">
         <v>1568</v>
       </c>
       <c r="B582" s="17">
@@ -40213,8 +40220,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="210">
-      <c r="A583" s="8" t="s">
+    <row r="583" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A583" s="17" t="s">
         <v>1571</v>
       </c>
       <c r="B583" s="17">
@@ -40269,8 +40276,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="210">
-      <c r="A584" s="8" t="s">
+    <row r="584" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A584" s="17" t="s">
         <v>1574</v>
       </c>
       <c r="B584" s="17">
@@ -40325,8 +40332,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="210">
-      <c r="A585" s="8" t="s">
+    <row r="585" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A585" s="17" t="s">
         <v>1577</v>
       </c>
       <c r="B585" s="17">
@@ -40381,8 +40388,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="210">
-      <c r="A586" s="8" t="s">
+    <row r="586" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A586" s="17" t="s">
         <v>1580</v>
       </c>
       <c r="B586" s="17">
@@ -40437,8 +40444,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="210">
-      <c r="A587" s="8" t="s">
+    <row r="587" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A587" s="17" t="s">
         <v>1583</v>
       </c>
       <c r="B587" s="17">
@@ -40493,8 +40500,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="210">
-      <c r="A588" s="8" t="s">
+    <row r="588" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A588" s="17" t="s">
         <v>1586</v>
       </c>
       <c r="B588" s="17">
@@ -40549,8 +40556,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="210">
-      <c r="A589" s="8" t="s">
+    <row r="589" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A589" s="17" t="s">
         <v>1589</v>
       </c>
       <c r="B589" s="17">
@@ -40605,8 +40612,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="210">
-      <c r="A590" s="8" t="s">
+    <row r="590" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A590" s="17" t="s">
         <v>1592</v>
       </c>
       <c r="B590" s="17">
@@ -40661,8 +40668,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="210">
-      <c r="A591" s="8" t="s">
+    <row r="591" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A591" s="17" t="s">
         <v>1594</v>
       </c>
       <c r="B591" s="17">
@@ -40717,8 +40724,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="210">
-      <c r="A592" s="8" t="s">
+    <row r="592" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A592" s="17" t="s">
         <v>1596</v>
       </c>
       <c r="B592" s="17">
@@ -40773,8 +40780,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="210">
-      <c r="A593" s="8" t="s">
+    <row r="593" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A593" s="17" t="s">
         <v>1598</v>
       </c>
       <c r="B593" s="17">
@@ -40829,8 +40836,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="210">
-      <c r="A594" s="8" t="s">
+    <row r="594" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A594" s="17" t="s">
         <v>1601</v>
       </c>
       <c r="B594" s="17">
@@ -40885,8 +40892,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="60">
-      <c r="A595" s="8" t="s">
+    <row r="595" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A595" s="17" t="s">
         <v>1604</v>
       </c>
       <c r="B595" s="17">
@@ -40941,8 +40948,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="60">
-      <c r="A596" s="8" t="s">
+    <row r="596" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A596" s="17" t="s">
         <v>1607</v>
       </c>
       <c r="B596" s="17">
@@ -40997,8 +41004,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="60">
-      <c r="A597" s="8" t="s">
+    <row r="597" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A597" s="17" t="s">
         <v>1610</v>
       </c>
       <c r="B597" s="17">
@@ -41053,8 +41060,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="60">
-      <c r="A598" s="8" t="s">
+    <row r="598" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A598" s="17" t="s">
         <v>1612</v>
       </c>
       <c r="B598" s="17">
@@ -41109,8 +41116,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="60">
-      <c r="A599" s="8" t="s">
+    <row r="599" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A599" s="17" t="s">
         <v>1614</v>
       </c>
       <c r="B599" s="17">
@@ -41165,8 +41172,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="60">
-      <c r="A600" s="8" t="s">
+    <row r="600" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A600" s="17" t="s">
         <v>1616</v>
       </c>
       <c r="B600" s="17">
@@ -41221,8 +41228,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="60">
-      <c r="A601" s="8" t="s">
+    <row r="601" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A601" s="17" t="s">
         <v>1618</v>
       </c>
       <c r="B601" s="17">
@@ -41277,8 +41284,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="60">
-      <c r="A602" s="8" t="s">
+    <row r="602" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A602" s="17" t="s">
         <v>1619</v>
       </c>
       <c r="B602" s="17">
@@ -41333,8 +41340,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="60">
-      <c r="A603" s="8" t="s">
+    <row r="603" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A603" s="17" t="s">
         <v>1622</v>
       </c>
       <c r="B603" s="17">
@@ -41389,8 +41396,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="60">
-      <c r="A604" s="8" t="s">
+    <row r="604" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A604" s="17" t="s">
         <v>1625</v>
       </c>
       <c r="B604" s="17">
@@ -41445,8 +41452,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="60">
-      <c r="A605" s="8" t="s">
+    <row r="605" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A605" s="17" t="s">
         <v>1628</v>
       </c>
       <c r="B605" s="17">
@@ -41501,8 +41508,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="60">
-      <c r="A606" s="8" t="s">
+    <row r="606" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A606" s="17" t="s">
         <v>1631</v>
       </c>
       <c r="B606" s="17">
@@ -41557,8 +41564,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="75">
-      <c r="A607" s="8" t="s">
+    <row r="607" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A607" s="17" t="s">
         <v>1634</v>
       </c>
       <c r="B607" s="17">
@@ -41613,8 +41620,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="60">
-      <c r="A608" s="8" t="s">
+    <row r="608" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A608" s="17" t="s">
         <v>1637</v>
       </c>
       <c r="B608" s="17">
@@ -41669,8 +41676,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="90">
-      <c r="A609" s="8" t="s">
+    <row r="609" spans="1:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="A609" s="17" t="s">
         <v>1640</v>
       </c>
       <c r="B609" s="17">
@@ -41725,8 +41732,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="75">
-      <c r="A610" s="8" t="s">
+    <row r="610" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A610" s="17" t="s">
         <v>1643</v>
       </c>
       <c r="B610" s="17">
@@ -41781,8 +41788,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="75">
-      <c r="A611" s="8" t="s">
+    <row r="611" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A611" s="17" t="s">
         <v>1646</v>
       </c>
       <c r="B611" s="17">
@@ -41837,8 +41844,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="60">
-      <c r="A612" s="8" t="s">
+    <row r="612" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A612" s="17" t="s">
         <v>1649</v>
       </c>
       <c r="B612" s="17">
@@ -41893,8 +41900,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="60">
-      <c r="A613" s="8" t="s">
+    <row r="613" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A613" s="17" t="s">
         <v>1652</v>
       </c>
       <c r="B613" s="17">
@@ -41949,8 +41956,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="60">
-      <c r="A614" s="8" t="s">
+    <row r="614" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A614" s="17" t="s">
         <v>1655</v>
       </c>
       <c r="B614" s="17">
@@ -42005,8 +42012,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="60">
-      <c r="A615" s="8" t="s">
+    <row r="615" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A615" s="17" t="s">
         <v>1658</v>
       </c>
       <c r="B615" s="17">
@@ -42061,8 +42068,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="60">
-      <c r="A616" s="8" t="s">
+    <row r="616" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A616" s="17" t="s">
         <v>1661</v>
       </c>
       <c r="B616" s="17">
@@ -42117,8 +42124,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="60">
-      <c r="A617" s="8" t="s">
+    <row r="617" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A617" s="17" t="s">
         <v>1665</v>
       </c>
       <c r="B617" s="17">
@@ -42173,8 +42180,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="60">
-      <c r="A618" s="8" t="s">
+    <row r="618" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A618" s="17" t="s">
         <v>1668</v>
       </c>
       <c r="B618" s="17">
@@ -42229,8 +42236,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="60">
-      <c r="A619" s="8" t="s">
+    <row r="619" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A619" s="17" t="s">
         <v>1671</v>
       </c>
       <c r="B619" s="17">
@@ -42285,8 +42292,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="60">
-      <c r="A620" s="8" t="s">
+    <row r="620" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A620" s="17" t="s">
         <v>1674</v>
       </c>
       <c r="B620" s="17">
@@ -42341,8 +42348,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="60">
-      <c r="A621" s="8" t="s">
+    <row r="621" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A621" s="17" t="s">
         <v>1677</v>
       </c>
       <c r="B621" s="17">
@@ -42397,8 +42404,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="60">
-      <c r="A622" s="8" t="s">
+    <row r="622" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A622" s="17" t="s">
         <v>1680</v>
       </c>
       <c r="B622" s="17">
@@ -42453,8 +42460,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="60">
-      <c r="A623" s="8" t="s">
+    <row r="623" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A623" s="17" t="s">
         <v>1683</v>
       </c>
       <c r="B623" s="17">
@@ -42509,8 +42516,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="60">
-      <c r="A624" s="8" t="s">
+    <row r="624" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A624" s="17" t="s">
         <v>1686</v>
       </c>
       <c r="B624" s="17">
@@ -42565,8 +42572,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="75">
-      <c r="A625" s="8" t="s">
+    <row r="625" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A625" s="17" t="s">
         <v>1689</v>
       </c>
       <c r="B625" s="17">
@@ -42621,8 +42628,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="60">
-      <c r="A626" s="8" t="s">
+    <row r="626" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A626" s="17" t="s">
         <v>1692</v>
       </c>
       <c r="B626" s="17">
@@ -42677,8 +42684,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="60">
-      <c r="A627" s="8" t="s">
+    <row r="627" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A627" s="17" t="s">
         <v>1694</v>
       </c>
       <c r="B627" s="17">
@@ -42733,8 +42740,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="60">
-      <c r="A628" s="8" t="s">
+    <row r="628" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A628" s="17" t="s">
         <v>1696</v>
       </c>
       <c r="B628" s="17">
@@ -42789,8 +42796,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="629" spans="1:18" ht="75">
-      <c r="A629" s="8" t="s">
+    <row r="629" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A629" s="17" t="s">
         <v>1699</v>
       </c>
       <c r="B629" s="17">
@@ -42845,8 +42852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="75">
-      <c r="A630" s="8" t="s">
+    <row r="630" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A630" s="17" t="s">
         <v>1702</v>
       </c>
       <c r="B630" s="17">
@@ -42901,8 +42908,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="60">
-      <c r="A631" s="8" t="s">
+    <row r="631" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A631" s="17" t="s">
         <v>1705</v>
       </c>
       <c r="B631" s="17">
@@ -42957,8 +42964,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="60">
-      <c r="A632" s="8" t="s">
+    <row r="632" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A632" s="17" t="s">
         <v>1708</v>
       </c>
       <c r="B632" s="17">
@@ -43013,8 +43020,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="633" spans="1:18" ht="60">
-      <c r="A633" s="8" t="s">
+    <row r="633" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A633" s="17" t="s">
         <v>1711</v>
       </c>
       <c r="B633" s="17">
@@ -43069,8 +43076,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="60">
-      <c r="A634" s="8" t="s">
+    <row r="634" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A634" s="17" t="s">
         <v>1714</v>
       </c>
       <c r="B634" s="17">
@@ -43125,8 +43132,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="60">
-      <c r="A635" s="8" t="s">
+    <row r="635" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A635" s="17" t="s">
         <v>1717</v>
       </c>
       <c r="B635" s="17">
@@ -43181,8 +43188,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="60">
-      <c r="A636" s="8" t="s">
+    <row r="636" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A636" s="17" t="s">
         <v>1720</v>
       </c>
       <c r="B636" s="17">
@@ -43237,8 +43244,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="637" spans="1:18" ht="60">
-      <c r="A637" s="8" t="s">
+    <row r="637" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A637" s="17" t="s">
         <v>1723</v>
       </c>
       <c r="B637" s="17">
@@ -43293,8 +43300,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="638" spans="1:18" ht="195">
-      <c r="A638" s="8" t="s">
+    <row r="638" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A638" s="17" t="s">
         <v>1726</v>
       </c>
       <c r="B638" s="17">
@@ -43349,8 +43356,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="60">
-      <c r="A639" s="8" t="s">
+    <row r="639" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A639" s="17" t="s">
         <v>1729</v>
       </c>
       <c r="B639" s="17">
@@ -43405,8 +43412,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="60">
-      <c r="A640" s="8" t="s">
+    <row r="640" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A640" s="17" t="s">
         <v>1732</v>
       </c>
       <c r="B640" s="17">
@@ -43461,8 +43468,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="641" spans="1:18" ht="60">
-      <c r="A641" s="8" t="s">
+    <row r="641" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A641" s="17" t="s">
         <v>1735</v>
       </c>
       <c r="B641" s="17">
@@ -43517,8 +43524,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="642" spans="1:18" ht="60">
-      <c r="A642" s="8" t="s">
+    <row r="642" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A642" s="17" t="s">
         <v>1739</v>
       </c>
       <c r="B642" s="17">
@@ -43573,8 +43580,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="643" spans="1:18" ht="60">
-      <c r="A643" s="8" t="s">
+    <row r="643" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A643" s="17" t="s">
         <v>1741</v>
       </c>
       <c r="B643" s="17">
@@ -43629,8 +43636,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="644" spans="1:18" ht="60">
-      <c r="A644" s="8" t="s">
+    <row r="644" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A644" s="17" t="s">
         <v>1743</v>
       </c>
       <c r="B644" s="17">
@@ -43685,8 +43692,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="645" spans="1:18" ht="60">
-      <c r="A645" s="8" t="s">
+    <row r="645" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A645" s="17" t="s">
         <v>1746</v>
       </c>
       <c r="B645" s="17">
@@ -43741,8 +43748,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="646" spans="1:18" ht="60">
-      <c r="A646" s="8" t="s">
+    <row r="646" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A646" s="17" t="s">
         <v>1749</v>
       </c>
       <c r="B646" s="17">
@@ -43797,8 +43804,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="647" spans="1:18" ht="60">
-      <c r="A647" s="8" t="s">
+    <row r="647" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A647" s="17" t="s">
         <v>1752</v>
       </c>
       <c r="B647" s="17">
@@ -43853,8 +43860,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="648" spans="1:18" ht="60">
-      <c r="A648" s="8" t="s">
+    <row r="648" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A648" s="17" t="s">
         <v>1755</v>
       </c>
       <c r="B648" s="17">
@@ -43909,8 +43916,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="649" spans="1:18" ht="75">
-      <c r="A649" s="8" t="s">
+    <row r="649" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A649" s="17" t="s">
         <v>1757</v>
       </c>
       <c r="B649" s="17">
@@ -43965,8 +43972,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="650" spans="1:18" ht="75">
-      <c r="A650" s="8" t="s">
+    <row r="650" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A650" s="17" t="s">
         <v>1760</v>
       </c>
       <c r="B650" s="17">
@@ -44021,8 +44028,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="651" spans="1:18" ht="75">
-      <c r="A651" s="8" t="s">
+    <row r="651" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A651" s="17" t="s">
         <v>1763</v>
       </c>
       <c r="B651" s="17">
@@ -44077,8 +44084,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="75">
-      <c r="A652" s="8" t="s">
+    <row r="652" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A652" s="17" t="s">
         <v>1766</v>
       </c>
       <c r="B652" s="17">
@@ -44133,8 +44140,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="653" spans="1:18" ht="409.5">
-      <c r="A653" s="8" t="s">
+    <row r="653" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A653" s="17" t="s">
         <v>1769</v>
       </c>
       <c r="B653" s="17">
@@ -44189,8 +44196,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="654" spans="1:18" ht="60">
-      <c r="A654" s="8" t="s">
+    <row r="654" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A654" s="17" t="s">
         <v>1772</v>
       </c>
       <c r="B654" s="17">
@@ -44245,8 +44252,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="655" spans="1:18" ht="60">
-      <c r="A655" s="8" t="s">
+    <row r="655" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A655" s="17" t="s">
         <v>1776</v>
       </c>
       <c r="B655" s="17">
@@ -44301,8 +44308,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="656" spans="1:18" ht="60">
-      <c r="A656" s="8" t="s">
+    <row r="656" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A656" s="17" t="s">
         <v>1779</v>
       </c>
       <c r="B656" s="17">
@@ -44357,8 +44364,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="657" spans="1:18" ht="60">
-      <c r="A657" s="8" t="s">
+    <row r="657" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A657" s="17" t="s">
         <v>1782</v>
       </c>
       <c r="B657" s="17">
@@ -44413,8 +44420,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="75">
-      <c r="A658" s="8" t="s">
+    <row r="658" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A658" s="17" t="s">
         <v>1785</v>
       </c>
       <c r="B658" s="17">
@@ -44469,8 +44476,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="75">
-      <c r="A659" s="8" t="s">
+    <row r="659" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A659" s="17" t="s">
         <v>1788</v>
       </c>
       <c r="B659" s="17">
@@ -44525,8 +44532,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="60">
-      <c r="A660" s="8" t="s">
+    <row r="660" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A660" s="17" t="s">
         <v>1791</v>
       </c>
       <c r="B660" s="17">
@@ -44581,8 +44588,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="60">
-      <c r="A661" s="8" t="s">
+    <row r="661" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A661" s="17" t="s">
         <v>1794</v>
       </c>
       <c r="B661" s="17">
@@ -44637,8 +44644,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="60">
-      <c r="A662" s="8" t="s">
+    <row r="662" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A662" s="17" t="s">
         <v>1797</v>
       </c>
       <c r="B662" s="17">
@@ -44726,7 +44733,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -44736,7 +44743,7 @@
     <col min="6" max="6" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="105.75" customHeight="1">
+    <row r="3" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>1801</v>
       </c>
@@ -44746,7 +44753,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>1940</v>
       </c>
@@ -44767,7 +44774,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" ht="33.75">
+    <row r="5" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -44788,7 +44795,7 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="22.5">
+    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -44809,7 +44816,7 @@
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -44830,7 +44837,7 @@
       </c>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" ht="22.5">
+    <row r="8" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -44851,7 +44858,7 @@
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="22.5">
+    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>5</v>
       </c>
@@ -44872,7 +44879,7 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="22.5">
+    <row r="10" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -44893,7 +44900,7 @@
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="22.5">
+    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>7</v>
       </c>
@@ -44914,7 +44921,7 @@
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="22.5">
+    <row r="12" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -44935,7 +44942,7 @@
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" ht="22.5">
+    <row r="13" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>9</v>
       </c>
@@ -44956,7 +44963,7 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="22.5">
+    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -44977,7 +44984,7 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" ht="22.5">
+    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>11</v>
       </c>
@@ -44998,7 +45005,7 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>12</v>
       </c>
@@ -45019,7 +45026,7 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" ht="22.5">
+    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>13</v>
       </c>
@@ -45040,7 +45047,7 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" ht="22.5">
+    <row r="18" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>14</v>
       </c>
@@ -45061,7 +45068,7 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>15</v>
       </c>
@@ -45082,7 +45089,7 @@
       </c>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>16</v>
       </c>
@@ -45103,7 +45110,7 @@
       </c>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" ht="22.5">
+    <row r="21" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>17</v>
       </c>
@@ -45124,7 +45131,7 @@
       </c>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>18</v>
       </c>
@@ -45145,7 +45152,7 @@
       </c>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" ht="22.5">
+    <row r="23" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>19</v>
       </c>
@@ -45166,7 +45173,7 @@
       </c>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" ht="22.5">
+    <row r="24" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>20</v>
       </c>
@@ -45187,7 +45194,7 @@
       </c>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>21</v>
       </c>
@@ -45208,7 +45215,7 @@
       </c>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" ht="22.5">
+    <row r="26" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>22</v>
       </c>
@@ -45229,7 +45236,7 @@
       </c>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" ht="22.5">
+    <row r="27" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>23</v>
       </c>
@@ -45250,7 +45257,7 @@
       </c>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>24</v>
       </c>
@@ -45271,7 +45278,7 @@
       </c>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>25</v>
       </c>
@@ -45292,7 +45299,7 @@
       </c>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" ht="22.5">
+    <row r="30" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>26</v>
       </c>
@@ -45313,7 +45320,7 @@
       </c>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" ht="22.5">
+    <row r="31" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>27</v>
       </c>
@@ -45334,7 +45341,7 @@
       </c>
       <c r="G31" s="8"/>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
         <v>1941</v>
       </c>
@@ -45348,7 +45355,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>1942</v>
       </c>
@@ -45362,7 +45369,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
         <v>1945</v>
       </c>
@@ -45376,7 +45383,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="30">
+    <row r="39" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
         <v>1947</v>
       </c>
@@ -45390,7 +45397,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>1498</v>
       </c>
@@ -45404,7 +45411,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="6" t="s">
         <v>812</v>
       </c>
@@ -45418,7 +45425,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="6" t="s">
         <v>1950</v>
       </c>
@@ -45432,7 +45439,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="6" t="s">
         <v>1951</v>
       </c>
@@ -45446,7 +45453,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="6" t="s">
         <v>665</v>
       </c>
@@ -45460,7 +45467,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="6" t="s">
         <v>1952</v>
       </c>
@@ -45474,7 +45481,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="6" t="s">
         <v>1953</v>
       </c>
@@ -45488,7 +45495,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="6" t="s">
         <v>1838</v>
       </c>
@@ -45514,13 +45521,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>1956</v>
       </c>
@@ -45528,7 +45535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1960</v>
       </c>
@@ -45536,7 +45543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1958</v>
       </c>
@@ -45544,7 +45551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1957</v>
       </c>
@@ -45552,7 +45559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1959</v>
       </c>
@@ -45560,7 +45567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>1961</v>
       </c>
@@ -45568,7 +45575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>1962</v>
       </c>
@@ -45576,7 +45583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>1963</v>
       </c>
@@ -45584,7 +45591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>1964</v>
       </c>
@@ -45592,7 +45599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1965</v>
       </c>
@@ -45600,7 +45607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1966</v>
       </c>
@@ -45608,7 +45615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1967</v>
       </c>
@@ -45616,7 +45623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1968</v>
       </c>
@@ -45624,7 +45631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1969</v>
       </c>
@@ -45632,7 +45639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30">
+    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1970</v>
       </c>
@@ -45640,42 +45647,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1971</v>
+      </c>
       <c r="B16" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>-1</v>
       </c>

--- a/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
+++ b/docs/Airmius_Use_Cases_Testmatrix_testfreundlich.xlsx
@@ -7219,7 +7219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -8080,7 +8080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R666"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" customWidth="1"/>
@@ -8098,10 +8098,10 @@
     <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="22"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="7" t="s">
         <v>1973</v>
@@ -8111,27 +8111,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="7" t="s">
         <v>1974</v>
       </c>
       <c r="C3" s="18">
         <f>COUNTIF(B5:B800,"&gt;0")</f>
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="7" t="s">
         <v>1975</v>
       </c>
       <c r="C4" s="18">
         <f>COUNTIF(B5:B800,"=0")</f>
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>0</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>82</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
+    <row r="7" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>241</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
+    <row r="8" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>264</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1">
+    <row r="9" spans="1:18" s="11" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>343</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>99</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1">
+    <row r="11" spans="1:18" s="11" customFormat="1" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>101</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="195" hidden="1">
+    <row r="12" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>103</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="75" hidden="1">
+    <row r="13" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>122</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="75">
+    <row r="14" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="75">
+    <row r="15" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>135</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="75">
+    <row r="16" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>151</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="60">
+    <row r="17" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>221</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="75">
+    <row r="18" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>226</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="75">
+    <row r="19" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>1972</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="60">
+    <row r="20" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>415</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="60">
+    <row r="21" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>418</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="60">
+    <row r="22" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>421</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="90">
+    <row r="23" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>431</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="90">
+    <row r="24" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>440</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="90">
+    <row r="25" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>443</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="90">
+    <row r="26" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>446</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="90">
+    <row r="27" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>449</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="60" hidden="1">
+    <row r="28" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>458</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="60" hidden="1">
+    <row r="29" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>461</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="60" hidden="1">
+    <row r="30" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>464</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="60" hidden="1">
+    <row r="31" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>467</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="60">
+    <row r="32" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>495</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="75" hidden="1">
+    <row r="33" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>501</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="75">
+    <row r="34" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>504</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="60">
+    <row r="35" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>515</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="60">
+    <row r="36" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>564</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="60">
+    <row r="37" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
         <v>566</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="60">
+    <row r="38" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
         <v>575</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="75">
+    <row r="39" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
         <v>578</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="75">
+    <row r="40" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>581</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="75">
+    <row r="41" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
         <v>584</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="75">
+    <row r="42" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>587</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="60">
+    <row r="43" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
         <v>590</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="60" hidden="1">
+    <row r="44" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
         <v>592</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="60" hidden="1">
+    <row r="45" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
         <v>596</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="60" hidden="1">
+    <row r="46" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
         <v>599</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="60" hidden="1">
+    <row r="47" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
         <v>602</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="27" customFormat="1" ht="60" hidden="1">
+    <row r="48" spans="1:18" s="27" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
         <v>605</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="60" hidden="1">
+    <row r="49" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
         <v>607</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="60">
+    <row r="50" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
         <v>609</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="60">
+    <row r="51" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
         <v>613</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="60">
+    <row r="52" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
         <v>615</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="60">
+    <row r="53" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
         <v>617</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="60">
+    <row r="54" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
         <v>619</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="345">
+    <row r="55" spans="1:18" ht="345" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
         <v>685</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="135">
+    <row r="56" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
         <v>688</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="135">
+    <row r="57" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
         <v>690</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="135">
+    <row r="58" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A58" s="22" t="s">
         <v>693</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="135">
+    <row r="59" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A59" s="22" t="s">
         <v>701</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="135">
+    <row r="60" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="22" t="s">
         <v>704</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="135">
+    <row r="61" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A61" s="22" t="s">
         <v>705</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="60">
+    <row r="62" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="22" t="s">
         <v>707</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="75">
+    <row r="63" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
         <v>712</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="75">
+    <row r="64" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="22" t="s">
         <v>715</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="60">
+    <row r="65" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="22" t="s">
         <v>718</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="60">
+    <row r="66" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="22" t="s">
         <v>721</v>
       </c>
@@ -11603,7 +11603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="60">
+    <row r="67" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="22" t="s">
         <v>724</v>
       </c>
@@ -11659,7 +11659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="60">
+    <row r="68" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
         <v>727</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="75">
+    <row r="69" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
         <v>730</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="150" hidden="1">
+    <row r="70" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
         <v>746</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="150" hidden="1">
+    <row r="71" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
         <v>750</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="150" hidden="1">
+    <row r="72" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
         <v>753</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="150" hidden="1">
+    <row r="73" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
         <v>756</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="150" hidden="1">
+    <row r="74" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
         <v>759</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="150" hidden="1">
+    <row r="75" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
         <v>762</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="150" hidden="1">
+    <row r="76" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
         <v>765</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="150" hidden="1">
+    <row r="77" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
         <v>767</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="150">
+    <row r="78" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
         <v>770</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="150">
+    <row r="79" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
         <v>773</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="150">
+    <row r="80" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
         <v>776</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="60">
+    <row r="81" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
         <v>779</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="60">
+    <row r="82" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
         <v>787</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="60">
+    <row r="83" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
         <v>789</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="60">
+    <row r="84" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
         <v>790</v>
       </c>
@@ -12611,7 +12611,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="60">
+    <row r="85" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="22" t="s">
         <v>792</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="60">
+    <row r="86" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="22" t="s">
         <v>793</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="60" hidden="1">
+    <row r="87" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
         <v>796</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="60" hidden="1">
+    <row r="88" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
         <v>799</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="60" hidden="1">
+    <row r="89" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
         <v>800</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="60" hidden="1">
+    <row r="90" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
         <v>801</v>
       </c>
@@ -12947,7 +12947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="60" hidden="1">
+    <row r="91" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="22" t="s">
         <v>803</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="60" hidden="1">
+    <row r="92" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="22" t="s">
         <v>806</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="135" hidden="1">
+    <row r="93" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
         <v>809</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="135" hidden="1">
+    <row r="94" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22" t="s">
         <v>811</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="135">
+    <row r="95" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A95" s="22" t="s">
         <v>813</v>
       </c>
@@ -13227,7 +13227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="135">
+    <row r="96" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A96" s="22" t="s">
         <v>815</v>
       </c>
@@ -13283,7 +13283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="135">
+    <row r="97" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="s">
         <v>817</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="135">
+    <row r="98" spans="1:18" ht="135" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
         <v>820</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="135" hidden="1">
+    <row r="99" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="s">
         <v>822</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="409.5" hidden="1">
+    <row r="100" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="22" t="s">
         <v>833</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="409.5">
+    <row r="101" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
         <v>836</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="409.5" hidden="1">
+    <row r="102" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="22" t="s">
         <v>853</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="409.5" hidden="1">
+    <row r="103" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
         <v>855</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="409.5" hidden="1">
+    <row r="104" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
         <v>857</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="409.5" hidden="1">
+    <row r="105" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="22" t="s">
         <v>859</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="409.5" hidden="1">
+    <row r="106" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="s">
         <v>861</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="409.5">
+    <row r="107" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A107" s="22" t="s">
         <v>867</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="409.5">
+    <row r="108" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="s">
         <v>869</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="409.5">
+    <row r="109" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
         <v>872</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="409.5">
+    <row r="110" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="s">
         <v>874</v>
       </c>
@@ -14067,7 +14067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="409.5">
+    <row r="111" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
         <v>880</v>
       </c>
@@ -14123,7 +14123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="409.5">
+    <row r="112" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
         <v>882</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="60">
+    <row r="113" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
         <v>885</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="60">
+    <row r="114" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="22" t="s">
         <v>891</v>
       </c>
@@ -14291,7 +14291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="60">
+    <row r="115" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
         <v>894</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="60">
+    <row r="116" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
         <v>895</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="60">
+    <row r="117" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
         <v>897</v>
       </c>
@@ -14459,12 +14459,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="60">
+    <row r="118" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="22" t="s">
         <v>902</v>
       </c>
       <c r="B118" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" s="18" t="s">
         <v>906</v>
@@ -14515,12 +14515,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="75">
+    <row r="119" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
         <v>910</v>
       </c>
       <c r="B119" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" s="18" t="s">
         <v>911</v>
@@ -14571,12 +14571,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="60">
+    <row r="120" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="22" t="s">
         <v>913</v>
       </c>
       <c r="B120" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" s="18" t="s">
         <v>914</v>
@@ -14627,12 +14627,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="75">
+    <row r="121" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
         <v>916</v>
       </c>
       <c r="B121" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="18" t="s">
         <v>917</v>
@@ -14683,12 +14683,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="75">
+    <row r="122" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="22" t="s">
         <v>919</v>
       </c>
       <c r="B122" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" s="18" t="s">
         <v>920</v>
@@ -14739,7 +14739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="60">
+    <row r="123" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="22" t="s">
         <v>922</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="60">
+    <row r="124" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A124" s="22" t="s">
         <v>925</v>
       </c>
@@ -14851,7 +14851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="60">
+    <row r="125" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
         <v>928</v>
       </c>
@@ -14907,12 +14907,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="60">
+    <row r="126" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="22" t="s">
         <v>931</v>
       </c>
       <c r="B126" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126" s="18" t="s">
         <v>932</v>
@@ -14963,7 +14963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="75">
+    <row r="127" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A127" s="22" t="s">
         <v>934</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="75">
+    <row r="128" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A128" s="22" t="s">
         <v>937</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="75">
+    <row r="129" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A129" s="22" t="s">
         <v>940</v>
       </c>
@@ -15131,7 +15131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="75">
+    <row r="130" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A130" s="22" t="s">
         <v>943</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="60">
+    <row r="131" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="22" t="s">
         <v>946</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="60">
+    <row r="132" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="22" t="s">
         <v>949</v>
       </c>
@@ -15299,7 +15299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="60">
+    <row r="133" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="22" t="s">
         <v>951</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="60">
+    <row r="134" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" s="22" t="s">
         <v>954</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="60">
+    <row r="135" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A135" s="22" t="s">
         <v>956</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="60">
+    <row r="136" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" s="22" t="s">
         <v>958</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="60">
+    <row r="137" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="22" t="s">
         <v>960</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="60">
+    <row r="138" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A138" s="22" t="s">
         <v>963</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="60">
+    <row r="139" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A139" s="22" t="s">
         <v>966</v>
       </c>
@@ -15691,7 +15691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="60">
+    <row r="140" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" s="22" t="s">
         <v>969</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="60">
+    <row r="141" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="22" t="s">
         <v>974</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="60">
+    <row r="142" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="22" t="s">
         <v>980</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="60">
+    <row r="143" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" s="22" t="s">
         <v>983</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="60">
+    <row r="144" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="22" t="s">
         <v>986</v>
       </c>
@@ -15971,7 +15971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="60">
+    <row r="145" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="22" t="s">
         <v>989</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="60">
+    <row r="146" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" s="22" t="s">
         <v>992</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="60">
+    <row r="147" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" s="22" t="s">
         <v>995</v>
       </c>
@@ -16139,7 +16139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="60">
+    <row r="148" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="22" t="s">
         <v>998</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="60">
+    <row r="149" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="22" t="s">
         <v>1001</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="60">
+    <row r="150" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A150" s="22" t="s">
         <v>1004</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="60">
+    <row r="151" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A151" s="22" t="s">
         <v>1007</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="60">
+    <row r="152" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="22" t="s">
         <v>1012</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="75">
+    <row r="153" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A153" s="22" t="s">
         <v>1014</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="60">
+    <row r="154" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A154" s="22" t="s">
         <v>1017</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="60">
+    <row r="155" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" s="22" t="s">
         <v>1020</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="60">
+    <row r="156" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="22" t="s">
         <v>1023</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="60">
+    <row r="157" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="22" t="s">
         <v>1026</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="60">
+    <row r="158" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="22" t="s">
         <v>1029</v>
       </c>
@@ -16755,7 +16755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="60">
+    <row r="159" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A159" s="22" t="s">
         <v>1032</v>
       </c>
@@ -16811,7 +16811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="60">
+    <row r="160" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="22" t="s">
         <v>1035</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="60">
+    <row r="161" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="22" t="s">
         <v>1038</v>
       </c>
@@ -16923,7 +16923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="60">
+    <row r="162" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A162" s="22" t="s">
         <v>1040</v>
       </c>
@@ -16979,7 +16979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="60">
+    <row r="163" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A163" s="22" t="s">
         <v>1042</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="60">
+    <row r="164" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="22" t="s">
         <v>1046</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="60">
+    <row r="165" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" s="22" t="s">
         <v>1049</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="60">
+    <row r="166" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A166" s="22" t="s">
         <v>1052</v>
       </c>
@@ -17203,7 +17203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="60">
+    <row r="167" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A167" s="22" t="s">
         <v>1055</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="60">
+    <row r="168" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A168" s="22" t="s">
         <v>1058</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="60">
+    <row r="169" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A169" s="22" t="s">
         <v>1061</v>
       </c>
@@ -17371,7 +17371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="75">
+    <row r="170" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="22" t="s">
         <v>1064</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="60">
+    <row r="171" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A171" s="22" t="s">
         <v>1067</v>
       </c>
@@ -17483,7 +17483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="60">
+    <row r="172" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A172" s="22" t="s">
         <v>1070</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="60">
+    <row r="173" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A173" s="22" t="s">
         <v>1073</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="60">
+    <row r="174" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A174" s="22" t="s">
         <v>1076</v>
       </c>
@@ -17651,7 +17651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="60">
+    <row r="175" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A175" s="22" t="s">
         <v>1078</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="60">
+    <row r="176" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A176" s="22" t="s">
         <v>1080</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="60">
+    <row r="177" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A177" s="22" t="s">
         <v>1082</v>
       </c>
@@ -17819,7 +17819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="60">
+    <row r="178" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A178" s="22" t="s">
         <v>1084</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="60">
+    <row r="179" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A179" s="22" t="s">
         <v>1086</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="60">
+    <row r="180" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A180" s="22" t="s">
         <v>1089</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="60">
+    <row r="181" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A181" s="22" t="s">
         <v>1092</v>
       </c>
@@ -18043,7 +18043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="60">
+    <row r="182" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="22" t="s">
         <v>1095</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="60">
+    <row r="183" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A183" s="22" t="s">
         <v>1097</v>
       </c>
@@ -18155,7 +18155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="60">
+    <row r="184" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="22" t="s">
         <v>1100</v>
       </c>
@@ -18211,7 +18211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="60">
+    <row r="185" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A185" s="22" t="s">
         <v>1102</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="60">
+    <row r="186" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="22" t="s">
         <v>1105</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="75">
+    <row r="187" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A187" s="22" t="s">
         <v>1108</v>
       </c>
@@ -18379,7 +18379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="60">
+    <row r="188" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="22" t="s">
         <v>1111</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="60">
+    <row r="189" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A189" s="22" t="s">
         <v>1113</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="60">
+    <row r="190" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A190" s="22" t="s">
         <v>1115</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="60">
+    <row r="191" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A191" s="22" t="s">
         <v>1118</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="60">
+    <row r="192" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="22" t="s">
         <v>1121</v>
       </c>
@@ -18659,7 +18659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="60">
+    <row r="193" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A193" s="22" t="s">
         <v>1124</v>
       </c>
@@ -18715,7 +18715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="60">
+    <row r="194" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A194" s="22" t="s">
         <v>1127</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="60">
+    <row r="195" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A195" s="22" t="s">
         <v>1129</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="90">
+    <row r="196" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A196" s="22" t="s">
         <v>1132</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="90">
+    <row r="197" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A197" s="22" t="s">
         <v>1135</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="75">
+    <row r="198" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A198" s="22" t="s">
         <v>1138</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="75">
+    <row r="199" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A199" s="22" t="s">
         <v>1142</v>
       </c>
@@ -19051,7 +19051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="75">
+    <row r="200" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A200" s="22" t="s">
         <v>1145</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="75">
+    <row r="201" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A201" s="22" t="s">
         <v>1148</v>
       </c>
@@ -19163,7 +19163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="75">
+    <row r="202" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A202" s="22" t="s">
         <v>1151</v>
       </c>
@@ -19219,7 +19219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="75">
+    <row r="203" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A203" s="22" t="s">
         <v>1153</v>
       </c>
@@ -19275,7 +19275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="75">
+    <row r="204" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A204" s="22" t="s">
         <v>1156</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="75">
+    <row r="205" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A205" s="22" t="s">
         <v>1159</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="75">
+    <row r="206" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A206" s="22" t="s">
         <v>1162</v>
       </c>
@@ -19443,7 +19443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="75">
+    <row r="207" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A207" s="22" t="s">
         <v>1165</v>
       </c>
@@ -19499,7 +19499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="75">
+    <row r="208" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A208" s="22" t="s">
         <v>1168</v>
       </c>
@@ -19555,7 +19555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="75">
+    <row r="209" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A209" s="22" t="s">
         <v>1171</v>
       </c>
@@ -19611,7 +19611,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="60">
+    <row r="210" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="22" t="s">
         <v>1174</v>
       </c>
@@ -19667,7 +19667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="60">
+    <row r="211" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A211" s="22" t="s">
         <v>1178</v>
       </c>
@@ -19723,7 +19723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="60">
+    <row r="212" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A212" s="22" t="s">
         <v>1181</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="60">
+    <row r="213" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A213" s="22" t="s">
         <v>1184</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="60">
+    <row r="214" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A214" s="22" t="s">
         <v>1187</v>
       </c>
@@ -19891,7 +19891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="60">
+    <row r="215" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A215" s="22" t="s">
         <v>1190</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="60">
+    <row r="216" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A216" s="22" t="s">
         <v>1193</v>
       </c>
@@ -20003,7 +20003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="60">
+    <row r="217" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A217" s="22" t="s">
         <v>1196</v>
       </c>
@@ -20059,7 +20059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="60">
+    <row r="218" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A218" s="22" t="s">
         <v>1199</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="60">
+    <row r="219" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A219" s="22" t="s">
         <v>1202</v>
       </c>
@@ -20171,7 +20171,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="60">
+    <row r="220" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A220" s="22" t="s">
         <v>1205</v>
       </c>
@@ -20227,7 +20227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="60">
+    <row r="221" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A221" s="22" t="s">
         <v>1208</v>
       </c>
@@ -20283,7 +20283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="60">
+    <row r="222" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A222" s="22" t="s">
         <v>1211</v>
       </c>
@@ -20339,7 +20339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="195">
+    <row r="223" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A223" s="22" t="s">
         <v>1214</v>
       </c>
@@ -20395,7 +20395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="195">
+    <row r="224" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A224" s="22" t="s">
         <v>1217</v>
       </c>
@@ -20451,7 +20451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="195">
+    <row r="225" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A225" s="22" t="s">
         <v>1220</v>
       </c>
@@ -20507,7 +20507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="75">
+    <row r="226" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A226" s="22" t="s">
         <v>1222</v>
       </c>
@@ -20563,7 +20563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="75">
+    <row r="227" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A227" s="22" t="s">
         <v>1226</v>
       </c>
@@ -20619,7 +20619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="75">
+    <row r="228" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A228" s="22" t="s">
         <v>1229</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="75">
+    <row r="229" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A229" s="22" t="s">
         <v>1232</v>
       </c>
@@ -20731,7 +20731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="75">
+    <row r="230" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A230" s="22" t="s">
         <v>1235</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="75">
+    <row r="231" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A231" s="22" t="s">
         <v>1238</v>
       </c>
@@ -20843,7 +20843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="75">
+    <row r="232" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A232" s="22" t="s">
         <v>1241</v>
       </c>
@@ -20899,7 +20899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="75">
+    <row r="233" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A233" s="22" t="s">
         <v>1244</v>
       </c>
@@ -20955,7 +20955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="75">
+    <row r="234" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A234" s="22" t="s">
         <v>1247</v>
       </c>
@@ -21011,7 +21011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="75">
+    <row r="235" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A235" s="22" t="s">
         <v>1250</v>
       </c>
@@ -21067,7 +21067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="75">
+    <row r="236" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A236" s="22" t="s">
         <v>1253</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="60">
+    <row r="237" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A237" s="22" t="s">
         <v>1256</v>
       </c>
@@ -21179,7 +21179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="60">
+    <row r="238" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A238" s="22" t="s">
         <v>1259</v>
       </c>
@@ -21235,7 +21235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="345">
+    <row r="239" spans="1:18" ht="345" x14ac:dyDescent="0.25">
       <c r="A239" s="22" t="s">
         <v>1261</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="345">
+    <row r="240" spans="1:18" ht="345" x14ac:dyDescent="0.25">
       <c r="A240" s="22" t="s">
         <v>1264</v>
       </c>
@@ -21347,7 +21347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="345">
+    <row r="241" spans="1:18" ht="345" x14ac:dyDescent="0.25">
       <c r="A241" s="22" t="s">
         <v>1267</v>
       </c>
@@ -21403,7 +21403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="75">
+    <row r="242" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A242" s="22" t="s">
         <v>1270</v>
       </c>
@@ -21459,7 +21459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="60">
+    <row r="243" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A243" s="22" t="s">
         <v>1274</v>
       </c>
@@ -21515,7 +21515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="60">
+    <row r="244" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A244" s="22" t="s">
         <v>1277</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="60">
+    <row r="245" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A245" s="22" t="s">
         <v>1280</v>
       </c>
@@ -21627,7 +21627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="60">
+    <row r="246" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A246" s="22" t="s">
         <v>1283</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="75">
+    <row r="247" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A247" s="22" t="s">
         <v>1286</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="75">
+    <row r="248" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A248" s="22" t="s">
         <v>1289</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="60">
+    <row r="249" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A249" s="22" t="s">
         <v>1294</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="60">
+    <row r="250" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A250" s="22" t="s">
         <v>1298</v>
       </c>
@@ -21907,7 +21907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="60">
+    <row r="251" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A251" s="22" t="s">
         <v>1301</v>
       </c>
@@ -21963,7 +21963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="60">
+    <row r="252" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A252" s="22" t="s">
         <v>1304</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="60">
+    <row r="253" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A253" s="22" t="s">
         <v>1307</v>
       </c>
@@ -22075,7 +22075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="60">
+    <row r="254" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A254" s="22" t="s">
         <v>1310</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="60">
+    <row r="255" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A255" s="22" t="s">
         <v>1313</v>
       </c>
@@ -22187,7 +22187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="60">
+    <row r="256" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A256" s="22" t="s">
         <v>1316</v>
       </c>
@@ -22243,7 +22243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="60">
+    <row r="257" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A257" s="22" t="s">
         <v>1319</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="60">
+    <row r="258" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A258" s="22" t="s">
         <v>1322</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="60">
+    <row r="259" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A259" s="22" t="s">
         <v>1324</v>
       </c>
@@ -22411,7 +22411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="60">
+    <row r="260" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="22" t="s">
         <v>1326</v>
       </c>
@@ -22467,7 +22467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="60">
+    <row r="261" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A261" s="22" t="s">
         <v>1328</v>
       </c>
@@ -22523,7 +22523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="60">
+    <row r="262" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A262" s="22" t="s">
         <v>1330</v>
       </c>
@@ -22579,7 +22579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="60">
+    <row r="263" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A263" s="22" t="s">
         <v>1333</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="60">
+    <row r="264" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A264" s="22" t="s">
         <v>1335</v>
       </c>
@@ -22691,7 +22691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="60">
+    <row r="265" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A265" s="22" t="s">
         <v>1337</v>
       </c>
@@ -22747,7 +22747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="60">
+    <row r="266" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A266" s="22" t="s">
         <v>1339</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="60">
+    <row r="267" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A267" s="22" t="s">
         <v>1342</v>
       </c>
@@ -22859,7 +22859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="60">
+    <row r="268" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A268" s="22" t="s">
         <v>1344</v>
       </c>
@@ -22915,7 +22915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="60">
+    <row r="269" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A269" s="22" t="s">
         <v>1347</v>
       </c>
@@ -22971,7 +22971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="409.5">
+    <row r="270" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A270" s="22" t="s">
         <v>1350</v>
       </c>
@@ -23027,7 +23027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="409.5">
+    <row r="271" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A271" s="22" t="s">
         <v>1352</v>
       </c>
@@ -23083,7 +23083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="409.5">
+    <row r="272" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A272" s="22" t="s">
         <v>1354</v>
       </c>
@@ -23139,7 +23139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="409.5">
+    <row r="273" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A273" s="22" t="s">
         <v>1356</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="409.5">
+    <row r="274" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A274" s="22" t="s">
         <v>1358</v>
       </c>
@@ -23251,7 +23251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="409.5">
+    <row r="275" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A275" s="22" t="s">
         <v>1360</v>
       </c>
@@ -23307,7 +23307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="409.5">
+    <row r="276" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A276" s="22" t="s">
         <v>1361</v>
       </c>
@@ -23363,7 +23363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="409.5">
+    <row r="277" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A277" s="22" t="s">
         <v>1364</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="409.5">
+    <row r="278" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A278" s="22" t="s">
         <v>1366</v>
       </c>
@@ -23475,7 +23475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="409.5">
+    <row r="279" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A279" s="22" t="s">
         <v>1368</v>
       </c>
@@ -23531,7 +23531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="409.5">
+    <row r="280" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A280" s="22" t="s">
         <v>1370</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="409.5">
+    <row r="281" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A281" s="22" t="s">
         <v>1372</v>
       </c>
@@ -23643,7 +23643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="409.5">
+    <row r="282" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A282" s="22" t="s">
         <v>1375</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="409.5">
+    <row r="283" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A283" s="22" t="s">
         <v>1378</v>
       </c>
@@ -23755,7 +23755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="409.5">
+    <row r="284" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A284" s="22" t="s">
         <v>1381</v>
       </c>
@@ -23811,7 +23811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="409.5">
+    <row r="285" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A285" s="22" t="s">
         <v>1384</v>
       </c>
@@ -23867,7 +23867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="409.5">
+    <row r="286" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A286" s="22" t="s">
         <v>1387</v>
       </c>
@@ -23923,7 +23923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="75">
+    <row r="287" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A287" s="22" t="s">
         <v>1390</v>
       </c>
@@ -23979,7 +23979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="330">
+    <row r="288" spans="1:18" ht="330" x14ac:dyDescent="0.25">
       <c r="A288" s="22" t="s">
         <v>1393</v>
       </c>
@@ -24035,7 +24035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="75">
+    <row r="289" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A289" s="22" t="s">
         <v>1395</v>
       </c>
@@ -24091,7 +24091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="60">
+    <row r="290" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A290" s="22" t="s">
         <v>1402</v>
       </c>
@@ -24147,7 +24147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="75">
+    <row r="291" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A291" s="22" t="s">
         <v>1405</v>
       </c>
@@ -24203,7 +24203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="75">
+    <row r="292" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A292" s="22" t="s">
         <v>1408</v>
       </c>
@@ -24259,7 +24259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="75">
+    <row r="293" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A293" s="22" t="s">
         <v>1411</v>
       </c>
@@ -24315,7 +24315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="60">
+    <row r="294" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A294" s="22" t="s">
         <v>1414</v>
       </c>
@@ -24371,7 +24371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="60">
+    <row r="295" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A295" s="22" t="s">
         <v>1419</v>
       </c>
@@ -24427,7 +24427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="60">
+    <row r="296" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A296" s="22" t="s">
         <v>1422</v>
       </c>
@@ -24483,7 +24483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="60">
+    <row r="297" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A297" s="22" t="s">
         <v>1425</v>
       </c>
@@ -24539,7 +24539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="60">
+    <row r="298" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A298" s="22" t="s">
         <v>1427</v>
       </c>
@@ -24595,7 +24595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="60">
+    <row r="299" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A299" s="22" t="s">
         <v>1429</v>
       </c>
@@ -24651,7 +24651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="75">
+    <row r="300" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A300" s="22" t="s">
         <v>1431</v>
       </c>
@@ -24707,7 +24707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="60">
+    <row r="301" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A301" s="22" t="s">
         <v>1434</v>
       </c>
@@ -24763,7 +24763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="60">
+    <row r="302" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A302" s="22" t="s">
         <v>1437</v>
       </c>
@@ -24819,7 +24819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="60">
+    <row r="303" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A303" s="22" t="s">
         <v>1440</v>
       </c>
@@ -24875,7 +24875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="60">
+    <row r="304" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A304" s="22" t="s">
         <v>1442</v>
       </c>
@@ -24931,7 +24931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="60">
+    <row r="305" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A305" s="22" t="s">
         <v>1444</v>
       </c>
@@ -24987,7 +24987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="60">
+    <row r="306" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A306" s="22" t="s">
         <v>1446</v>
       </c>
@@ -25043,7 +25043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="60">
+    <row r="307" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A307" s="22" t="s">
         <v>1448</v>
       </c>
@@ -25099,7 +25099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="60">
+    <row r="308" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A308" s="22" t="s">
         <v>1450</v>
       </c>
@@ -25155,7 +25155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="60">
+    <row r="309" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A309" s="22" t="s">
         <v>1452</v>
       </c>
@@ -25211,7 +25211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="60">
+    <row r="310" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A310" s="22" t="s">
         <v>1454</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="60">
+    <row r="311" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A311" s="22" t="s">
         <v>1456</v>
       </c>
@@ -25323,7 +25323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="90">
+    <row r="312" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A312" s="22" t="s">
         <v>1458</v>
       </c>
@@ -25379,7 +25379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="60">
+    <row r="313" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A313" s="22" t="s">
         <v>1461</v>
       </c>
@@ -25435,7 +25435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="60">
+    <row r="314" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A314" s="22" t="s">
         <v>1464</v>
       </c>
@@ -25491,7 +25491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="60">
+    <row r="315" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A315" s="22" t="s">
         <v>1466</v>
       </c>
@@ -25547,7 +25547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="60">
+    <row r="316" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A316" s="22" t="s">
         <v>1468</v>
       </c>
@@ -25603,7 +25603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="60">
+    <row r="317" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A317" s="22" t="s">
         <v>1470</v>
       </c>
@@ -25659,7 +25659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="60">
+    <row r="318" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A318" s="22" t="s">
         <v>1472</v>
       </c>
@@ -25715,7 +25715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="60">
+    <row r="319" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A319" s="22" t="s">
         <v>1474</v>
       </c>
@@ -25771,7 +25771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="60">
+    <row r="320" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A320" s="22" t="s">
         <v>1476</v>
       </c>
@@ -25827,7 +25827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="60">
+    <row r="321" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A321" s="22" t="s">
         <v>1478</v>
       </c>
@@ -25883,7 +25883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="60">
+    <row r="322" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A322" s="22" t="s">
         <v>1480</v>
       </c>
@@ -25939,7 +25939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="60">
+    <row r="323" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A323" s="22" t="s">
         <v>1482</v>
       </c>
@@ -25995,7 +25995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="60">
+    <row r="324" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A324" s="22" t="s">
         <v>1485</v>
       </c>
@@ -26051,7 +26051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="60">
+    <row r="325" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A325" s="22" t="s">
         <v>1487</v>
       </c>
@@ -26107,7 +26107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="210">
+    <row r="326" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A326" s="22" t="s">
         <v>1490</v>
       </c>
@@ -26163,7 +26163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="210">
+    <row r="327" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A327" s="22" t="s">
         <v>1495</v>
       </c>
@@ -26219,7 +26219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="210">
+    <row r="328" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A328" s="22" t="s">
         <v>1498</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="210">
+    <row r="329" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A329" s="22" t="s">
         <v>1499</v>
       </c>
@@ -26331,7 +26331,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="210">
+    <row r="330" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A330" s="22" t="s">
         <v>1500</v>
       </c>
@@ -26387,7 +26387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="210">
+    <row r="331" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A331" s="22" t="s">
         <v>1501</v>
       </c>
@@ -26443,7 +26443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="210">
+    <row r="332" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A332" s="22" t="s">
         <v>1504</v>
       </c>
@@ -26499,7 +26499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="210">
+    <row r="333" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A333" s="22" t="s">
         <v>1506</v>
       </c>
@@ -26555,7 +26555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="210">
+    <row r="334" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A334" s="22" t="s">
         <v>1508</v>
       </c>
@@ -26611,7 +26611,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="210">
+    <row r="335" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A335" s="22" t="s">
         <v>1510</v>
       </c>
@@ -26667,7 +26667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="210">
+    <row r="336" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A336" s="22" t="s">
         <v>1512</v>
       </c>
@@ -26723,7 +26723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="210">
+    <row r="337" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A337" s="22" t="s">
         <v>1515</v>
       </c>
@@ -26779,7 +26779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="210">
+    <row r="338" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A338" s="22" t="s">
         <v>1518</v>
       </c>
@@ -26835,7 +26835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="210">
+    <row r="339" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A339" s="22" t="s">
         <v>1521</v>
       </c>
@@ -26891,7 +26891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="210">
+    <row r="340" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A340" s="22" t="s">
         <v>1524</v>
       </c>
@@ -26947,7 +26947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="210">
+    <row r="341" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A341" s="22" t="s">
         <v>1527</v>
       </c>
@@ -27003,7 +27003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="210">
+    <row r="342" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A342" s="22" t="s">
         <v>1530</v>
       </c>
@@ -27059,7 +27059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="210">
+    <row r="343" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A343" s="22" t="s">
         <v>1533</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="210">
+    <row r="344" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A344" s="22" t="s">
         <v>1536</v>
       </c>
@@ -27171,7 +27171,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="210">
+    <row r="345" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A345" s="22" t="s">
         <v>1539</v>
       </c>
@@ -27227,7 +27227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="210">
+    <row r="346" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A346" s="22" t="s">
         <v>1542</v>
       </c>
@@ -27283,7 +27283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="210">
+    <row r="347" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A347" s="22" t="s">
         <v>1545</v>
       </c>
@@ -27339,7 +27339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="210">
+    <row r="348" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A348" s="22" t="s">
         <v>1548</v>
       </c>
@@ -27395,7 +27395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="210">
+    <row r="349" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A349" s="22" t="s">
         <v>1551</v>
       </c>
@@ -27451,7 +27451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="210">
+    <row r="350" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A350" s="22" t="s">
         <v>1554</v>
       </c>
@@ -27507,7 +27507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="210">
+    <row r="351" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A351" s="22" t="s">
         <v>1557</v>
       </c>
@@ -27563,7 +27563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="210">
+    <row r="352" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A352" s="22" t="s">
         <v>1560</v>
       </c>
@@ -27619,7 +27619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="210">
+    <row r="353" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A353" s="22" t="s">
         <v>1563</v>
       </c>
@@ -27675,7 +27675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="210">
+    <row r="354" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A354" s="22" t="s">
         <v>1566</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="210">
+    <row r="355" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A355" s="22" t="s">
         <v>1569</v>
       </c>
@@ -27787,7 +27787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="210">
+    <row r="356" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A356" s="22" t="s">
         <v>1572</v>
       </c>
@@ -27843,7 +27843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="210">
+    <row r="357" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A357" s="22" t="s">
         <v>1575</v>
       </c>
@@ -27899,7 +27899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="210">
+    <row r="358" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A358" s="22" t="s">
         <v>1578</v>
       </c>
@@ -27955,7 +27955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="210">
+    <row r="359" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A359" s="22" t="s">
         <v>1581</v>
       </c>
@@ -28011,7 +28011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="210">
+    <row r="360" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A360" s="22" t="s">
         <v>1584</v>
       </c>
@@ -28067,7 +28067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="210">
+    <row r="361" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A361" s="22" t="s">
         <v>1587</v>
       </c>
@@ -28123,7 +28123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="210">
+    <row r="362" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A362" s="22" t="s">
         <v>1590</v>
       </c>
@@ -28179,7 +28179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="210">
+    <row r="363" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A363" s="22" t="s">
         <v>1592</v>
       </c>
@@ -28235,7 +28235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="210">
+    <row r="364" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A364" s="22" t="s">
         <v>1594</v>
       </c>
@@ -28291,7 +28291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="210">
+    <row r="365" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A365" s="22" t="s">
         <v>1596</v>
       </c>
@@ -28347,7 +28347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="210">
+    <row r="366" spans="1:18" ht="210" x14ac:dyDescent="0.25">
       <c r="A366" s="22" t="s">
         <v>1599</v>
       </c>
@@ -28403,7 +28403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="60">
+    <row r="367" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A367" s="22" t="s">
         <v>1602</v>
       </c>
@@ -28459,7 +28459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="60">
+    <row r="368" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A368" s="22" t="s">
         <v>1605</v>
       </c>
@@ -28515,7 +28515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="60">
+    <row r="369" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A369" s="22" t="s">
         <v>1608</v>
       </c>
@@ -28571,7 +28571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="60">
+    <row r="370" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A370" s="22" t="s">
         <v>1610</v>
       </c>
@@ -28627,7 +28627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="60">
+    <row r="371" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A371" s="22" t="s">
         <v>1612</v>
       </c>
@@ -28683,7 +28683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="60">
+    <row r="372" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A372" s="22" t="s">
         <v>1614</v>
       </c>
@@ -28739,7 +28739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="60">
+    <row r="373" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A373" s="22" t="s">
         <v>1616</v>
       </c>
@@ -28795,7 +28795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="60">
+    <row r="374" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A374" s="22" t="s">
         <v>1617</v>
       </c>
@@ -28851,7 +28851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="60">
+    <row r="375" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A375" s="22" t="s">
         <v>1620</v>
       </c>
@@ -28907,7 +28907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="60">
+    <row r="376" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A376" s="22" t="s">
         <v>1623</v>
       </c>
@@ -28963,7 +28963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="60">
+    <row r="377" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A377" s="22" t="s">
         <v>1626</v>
       </c>
@@ -29019,7 +29019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="60">
+    <row r="378" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A378" s="22" t="s">
         <v>1629</v>
       </c>
@@ -29075,7 +29075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="75">
+    <row r="379" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A379" s="22" t="s">
         <v>1632</v>
       </c>
@@ -29131,7 +29131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="60">
+    <row r="380" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A380" s="22" t="s">
         <v>1635</v>
       </c>
@@ -29187,7 +29187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="90">
+    <row r="381" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A381" s="22" t="s">
         <v>1638</v>
       </c>
@@ -29243,7 +29243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="75">
+    <row r="382" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A382" s="22" t="s">
         <v>1641</v>
       </c>
@@ -29299,7 +29299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="75">
+    <row r="383" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A383" s="22" t="s">
         <v>1644</v>
       </c>
@@ -29355,7 +29355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="60">
+    <row r="384" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A384" s="22" t="s">
         <v>1647</v>
       </c>
@@ -29411,7 +29411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="60">
+    <row r="385" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A385" s="22" t="s">
         <v>1650</v>
       </c>
@@ -29467,7 +29467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" spans="1:18" ht="60">
+    <row r="386" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A386" s="22" t="s">
         <v>1653</v>
       </c>
@@ -29523,7 +29523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="60">
+    <row r="387" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A387" s="22" t="s">
         <v>1656</v>
       </c>
@@ -29579,7 +29579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="60">
+    <row r="388" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A388" s="22" t="s">
         <v>1659</v>
       </c>
@@ -29635,7 +29635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="60">
+    <row r="389" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A389" s="22" t="s">
         <v>1663</v>
       </c>
@@ -29691,7 +29691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="60">
+    <row r="390" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A390" s="22" t="s">
         <v>1666</v>
       </c>
@@ -29747,7 +29747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="60">
+    <row r="391" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A391" s="22" t="s">
         <v>1669</v>
       </c>
@@ -29803,7 +29803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="60">
+    <row r="392" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A392" s="22" t="s">
         <v>1672</v>
       </c>
@@ -29859,7 +29859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="60">
+    <row r="393" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A393" s="22" t="s">
         <v>1675</v>
       </c>
@@ -29915,7 +29915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="60">
+    <row r="394" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A394" s="22" t="s">
         <v>1678</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="60">
+    <row r="395" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A395" s="22" t="s">
         <v>1681</v>
       </c>
@@ -30027,7 +30027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="60">
+    <row r="396" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A396" s="22" t="s">
         <v>1684</v>
       </c>
@@ -30083,7 +30083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="75">
+    <row r="397" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A397" s="22" t="s">
         <v>1687</v>
       </c>
@@ -30139,7 +30139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="60">
+    <row r="398" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A398" s="22" t="s">
         <v>1690</v>
       </c>
@@ -30195,7 +30195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="60">
+    <row r="399" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A399" s="22" t="s">
         <v>1692</v>
       </c>
@@ -30251,7 +30251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="60">
+    <row r="400" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A400" s="22" t="s">
         <v>1694</v>
       </c>
@@ -30307,7 +30307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="75">
+    <row r="401" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A401" s="22" t="s">
         <v>1697</v>
       </c>
@@ -30363,7 +30363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="75">
+    <row r="402" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A402" s="22" t="s">
         <v>1700</v>
       </c>
@@ -30419,7 +30419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="60">
+    <row r="403" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A403" s="22" t="s">
         <v>1703</v>
       </c>
@@ -30475,7 +30475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="60">
+    <row r="404" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A404" s="22" t="s">
         <v>1706</v>
       </c>
@@ -30531,7 +30531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="60">
+    <row r="405" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A405" s="22" t="s">
         <v>1709</v>
       </c>
@@ -30587,7 +30587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="60">
+    <row r="406" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A406" s="22" t="s">
         <v>1712</v>
       </c>
@@ -30643,7 +30643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="60">
+    <row r="407" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A407" s="22" t="s">
         <v>1715</v>
       </c>
@@ -30699,7 +30699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="60">
+    <row r="408" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A408" s="22" t="s">
         <v>1718</v>
       </c>
@@ -30755,7 +30755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="60">
+    <row r="409" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A409" s="22" t="s">
         <v>1721</v>
       </c>
@@ -30811,7 +30811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="195">
+    <row r="410" spans="1:18" ht="195" x14ac:dyDescent="0.25">
       <c r="A410" s="22" t="s">
         <v>1724</v>
       </c>
@@ -30867,7 +30867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="60">
+    <row r="411" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A411" s="22" t="s">
         <v>1727</v>
       </c>
@@ -30923,7 +30923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="60">
+    <row r="412" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A412" s="22" t="s">
         <v>1730</v>
       </c>
@@ -30979,7 +30979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="60">
+    <row r="413" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A413" s="22" t="s">
         <v>1733</v>
       </c>
@@ -31035,7 +31035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="60">
+    <row r="414" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A414" s="22" t="s">
         <v>1737</v>
       </c>
@@ -31091,7 +31091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="60">
+    <row r="415" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A415" s="22" t="s">
         <v>1739</v>
       </c>
@@ -31147,7 +31147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="60">
+    <row r="416" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A416" s="22" t="s">
         <v>1741</v>
       </c>
@@ -31203,7 +31203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="60">
+    <row r="417" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A417" s="22" t="s">
         <v>1744</v>
       </c>
@@ -31259,7 +31259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="60">
+    <row r="418" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A418" s="22" t="s">
         <v>1747</v>
       </c>
@@ -31315,7 +31315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="60">
+    <row r="419" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A419" s="22" t="s">
         <v>1750</v>
       </c>
@@ -31371,7 +31371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="60">
+    <row r="420" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A420" s="22" t="s">
         <v>1753</v>
       </c>
@@ -31427,7 +31427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="75">
+    <row r="421" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A421" s="22" t="s">
         <v>1755</v>
       </c>
@@ -31483,7 +31483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="75">
+    <row r="422" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A422" s="22" t="s">
         <v>1758</v>
       </c>
@@ -31539,7 +31539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="75">
+    <row r="423" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A423" s="22" t="s">
         <v>1761</v>
       </c>
@@ -31595,7 +31595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="75">
+    <row r="424" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A424" s="22" t="s">
         <v>1764</v>
       </c>
@@ -31651,7 +31651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="409.5">
+    <row r="425" spans="1:18" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A425" s="22" t="s">
         <v>1767</v>
       </c>
@@ -31707,7 +31707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="60">
+    <row r="426" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A426" s="22" t="s">
         <v>1770</v>
       </c>
@@ -31763,7 +31763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="60">
+    <row r="427" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A427" s="22" t="s">
         <v>1774</v>
       </c>
@@ -31819,7 +31819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="60">
+    <row r="428" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A428" s="22" t="s">
         <v>1777</v>
       </c>
@@ -31875,7 +31875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="60">
+    <row r="429" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A429" s="22" t="s">
         <v>1780</v>
       </c>
@@ -31931,7 +31931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="75">
+    <row r="430" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A430" s="22" t="s">
         <v>1783</v>
       </c>
@@ -31987,7 +31987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="75">
+    <row r="431" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A431" s="22" t="s">
         <v>1786</v>
       </c>
@@ -32043,7 +32043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="60">
+    <row r="432" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A432" s="22" t="s">
         <v>1789</v>
       </c>
@@ -32099,7 +32099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="60">
+    <row r="433" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A433" s="22" t="s">
         <v>1792</v>
       </c>
@@ -32155,7 +32155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="60">
+    <row r="434" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A434" s="22" t="s">
         <v>1795</v>
       </c>
@@ -32211,7 +32211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="330" hidden="1">
+    <row r="435" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="22" t="s">
         <v>190</v>
       </c>
@@ -32267,7 +32267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="330" hidden="1">
+    <row r="436" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="22" t="s">
         <v>196</v>
       </c>
@@ -32323,7 +32323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="437" spans="1:18" ht="105" hidden="1">
+    <row r="437" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="22" t="s">
         <v>311</v>
       </c>
@@ -32379,7 +32379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="105" hidden="1">
+    <row r="438" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="22" t="s">
         <v>314</v>
       </c>
@@ -32435,7 +32435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="105" hidden="1">
+    <row r="439" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="22" t="s">
         <v>316</v>
       </c>
@@ -32491,7 +32491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="105" hidden="1">
+    <row r="440" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="22" t="s">
         <v>319</v>
       </c>
@@ -32547,7 +32547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="60" hidden="1">
+    <row r="441" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="22" t="s">
         <v>354</v>
       </c>
@@ -32603,7 +32603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="60" hidden="1">
+    <row r="442" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="22" t="s">
         <v>357</v>
       </c>
@@ -32659,7 +32659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="60" hidden="1">
+    <row r="443" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="22" t="s">
         <v>362</v>
       </c>
@@ -32715,7 +32715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="90" hidden="1">
+    <row r="444" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="22" t="s">
         <v>434</v>
       </c>
@@ -32771,7 +32771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="90" hidden="1">
+    <row r="445" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="22" t="s">
         <v>437</v>
       </c>
@@ -32827,7 +32827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="75" hidden="1">
+    <row r="446" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="22" t="s">
         <v>507</v>
       </c>
@@ -32883,7 +32883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="75" hidden="1">
+    <row r="447" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="22" t="s">
         <v>510</v>
       </c>
@@ -32939,7 +32939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="60" hidden="1">
+    <row r="448" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="24" t="s">
         <v>513</v>
       </c>
@@ -32995,7 +32995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="60" hidden="1">
+    <row r="449" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="22" t="s">
         <v>550</v>
       </c>
@@ -33051,7 +33051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="60" hidden="1">
+    <row r="450" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="22" t="s">
         <v>552</v>
       </c>
@@ -33107,7 +33107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="60" hidden="1">
+    <row r="451" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="22" t="s">
         <v>554</v>
       </c>
@@ -33163,7 +33163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="60" hidden="1">
+    <row r="452" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="22" t="s">
         <v>556</v>
       </c>
@@ -33219,7 +33219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="60" hidden="1">
+    <row r="453" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="22" t="s">
         <v>558</v>
       </c>
@@ -33275,7 +33275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="60" hidden="1">
+    <row r="454" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="22" t="s">
         <v>560</v>
       </c>
@@ -33331,7 +33331,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="60" hidden="1">
+    <row r="455" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="22" t="s">
         <v>562</v>
       </c>
@@ -33387,7 +33387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="60" hidden="1">
+    <row r="456" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="22" t="s">
         <v>569</v>
       </c>
@@ -33443,7 +33443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="60" hidden="1">
+    <row r="457" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="22" t="s">
         <v>572</v>
       </c>
@@ -33499,7 +33499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="345" hidden="1">
+    <row r="458" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="22" t="s">
         <v>680</v>
       </c>
@@ -33555,7 +33555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="345" hidden="1">
+    <row r="459" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="22" t="s">
         <v>683</v>
       </c>
@@ -33611,7 +33611,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="150" hidden="1">
+    <row r="460" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="22" t="s">
         <v>748</v>
       </c>
@@ -33667,7 +33667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="60" hidden="1">
+    <row r="461" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="22" t="s">
         <v>347</v>
       </c>
@@ -33723,7 +33723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="60" hidden="1">
+    <row r="462" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="22" t="s">
         <v>351</v>
       </c>
@@ -33779,7 +33779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="60" hidden="1">
+    <row r="463" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="22" t="s">
         <v>360</v>
       </c>
@@ -33835,7 +33835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="345" hidden="1">
+    <row r="464" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="22" t="s">
         <v>678</v>
       </c>
@@ -33891,7 +33891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="409.5" hidden="1">
+    <row r="465" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="22" t="s">
         <v>863</v>
       </c>
@@ -33947,7 +33947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="409.5" hidden="1">
+    <row r="466" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="22" t="s">
         <v>865</v>
       </c>
@@ -34003,7 +34003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="409.5" hidden="1">
+    <row r="467" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="22" t="s">
         <v>877</v>
       </c>
@@ -34059,7 +34059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="60" hidden="1">
+    <row r="468" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="22" t="s">
         <v>888</v>
       </c>
@@ -34115,7 +34115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="60" hidden="1">
+    <row r="469" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="22" t="s">
         <v>889</v>
       </c>
@@ -34171,7 +34171,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="60" hidden="1">
+    <row r="470" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="22" t="s">
         <v>892</v>
       </c>
@@ -34227,7 +34227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="60" hidden="1">
+    <row r="471" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="22" t="s">
         <v>900</v>
       </c>
@@ -34283,7 +34283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="345" hidden="1">
+    <row r="472" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="22" t="s">
         <v>733</v>
       </c>
@@ -34339,7 +34339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="150" hidden="1">
+    <row r="473" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="22" t="s">
         <v>742</v>
       </c>
@@ -34395,7 +34395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="150" hidden="1">
+    <row r="474" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="22" t="s">
         <v>744</v>
       </c>
@@ -34451,7 +34451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="60" hidden="1">
+    <row r="475" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="22" t="s">
         <v>783</v>
       </c>
@@ -34507,7 +34507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="60" hidden="1">
+    <row r="476" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="22" t="s">
         <v>785</v>
       </c>
@@ -34563,7 +34563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="60" hidden="1">
+    <row r="477" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="22" t="s">
         <v>786</v>
       </c>
@@ -34619,7 +34619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="409.5" hidden="1">
+    <row r="478" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="22" t="s">
         <v>823</v>
       </c>
@@ -34675,7 +34675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="409.5" hidden="1">
+    <row r="479" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="22" t="s">
         <v>825</v>
       </c>
@@ -34731,7 +34731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="409.5" hidden="1">
+    <row r="480" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="22" t="s">
         <v>827</v>
       </c>
@@ -34787,7 +34787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="409.5" hidden="1">
+    <row r="481" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="22" t="s">
         <v>829</v>
       </c>
@@ -34843,7 +34843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="409.5" hidden="1">
+    <row r="482" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="22" t="s">
         <v>831</v>
       </c>
@@ -34899,7 +34899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="409.5" hidden="1">
+    <row r="483" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="22" t="s">
         <v>838</v>
       </c>
@@ -34955,7 +34955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="409.5" hidden="1">
+    <row r="484" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="22" t="s">
         <v>841</v>
       </c>
@@ -35011,7 +35011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="409.5" hidden="1">
+    <row r="485" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="22" t="s">
         <v>844</v>
       </c>
@@ -35067,7 +35067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="409.5" hidden="1">
+    <row r="486" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="22" t="s">
         <v>847</v>
       </c>
@@ -35123,7 +35123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="409.5" hidden="1">
+    <row r="487" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="22" t="s">
         <v>850</v>
       </c>
@@ -35179,7 +35179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="60" hidden="1">
+    <row r="488" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="22" t="s">
         <v>525</v>
       </c>
@@ -35235,7 +35235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="60" hidden="1">
+    <row r="489" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="22" t="s">
         <v>528</v>
       </c>
@@ -35291,7 +35291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="60" hidden="1">
+    <row r="490" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="22" t="s">
         <v>530</v>
       </c>
@@ -35347,7 +35347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="60" hidden="1">
+    <row r="491" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="22" t="s">
         <v>533</v>
       </c>
@@ -35403,7 +35403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="60" hidden="1">
+    <row r="492" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="22" t="s">
         <v>536</v>
       </c>
@@ -35459,7 +35459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="60" hidden="1">
+    <row r="493" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="22" t="s">
         <v>539</v>
       </c>
@@ -35515,7 +35515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="60" hidden="1">
+    <row r="494" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="22" t="s">
         <v>542</v>
       </c>
@@ -35571,7 +35571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="60" hidden="1">
+    <row r="495" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="22" t="s">
         <v>545</v>
       </c>
@@ -35627,7 +35627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="60" hidden="1">
+    <row r="496" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="22" t="s">
         <v>548</v>
       </c>
@@ -35683,7 +35683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="345" hidden="1">
+    <row r="497" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="22" t="s">
         <v>621</v>
       </c>
@@ -35739,7 +35739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="345" hidden="1">
+    <row r="498" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="22" t="s">
         <v>623</v>
       </c>
@@ -35795,7 +35795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="345" hidden="1">
+    <row r="499" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="22" t="s">
         <v>626</v>
       </c>
@@ -35851,7 +35851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="345" hidden="1">
+    <row r="500" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="22" t="s">
         <v>627</v>
       </c>
@@ -35907,7 +35907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="345" hidden="1">
+    <row r="501" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="22" t="s">
         <v>630</v>
       </c>
@@ -35963,7 +35963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="345" hidden="1">
+    <row r="502" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="22" t="s">
         <v>633</v>
       </c>
@@ -36019,7 +36019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="345" hidden="1">
+    <row r="503" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="22" t="s">
         <v>637</v>
       </c>
@@ -36075,7 +36075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="345" hidden="1">
+    <row r="504" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="22" t="s">
         <v>667</v>
       </c>
@@ -36131,7 +36131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="345" hidden="1">
+    <row r="505" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="22" t="s">
         <v>670</v>
       </c>
@@ -36187,7 +36187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="506" spans="1:18" ht="345" hidden="1">
+    <row r="506" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="22" t="s">
         <v>673</v>
       </c>
@@ -36243,7 +36243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="345" hidden="1">
+    <row r="507" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="22" t="s">
         <v>675</v>
       </c>
@@ -36299,7 +36299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="345" hidden="1">
+    <row r="508" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="22" t="s">
         <v>677</v>
       </c>
@@ -36355,7 +36355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="60" hidden="1">
+    <row r="509" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="22" t="s">
         <v>489</v>
       </c>
@@ -36411,7 +36411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="60" hidden="1">
+    <row r="510" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="22" t="s">
         <v>492</v>
       </c>
@@ -36467,7 +36467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="60" hidden="1">
+    <row r="511" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="22" t="s">
         <v>498</v>
       </c>
@@ -36523,7 +36523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="60" hidden="1">
+    <row r="512" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="22" t="s">
         <v>517</v>
       </c>
@@ -36579,7 +36579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="60" hidden="1">
+    <row r="513" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="22" t="s">
         <v>520</v>
       </c>
@@ -36635,7 +36635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="60" hidden="1">
+    <row r="514" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="22" t="s">
         <v>522</v>
       </c>
@@ -36691,7 +36691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="60" hidden="1">
+    <row r="515" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="22" t="s">
         <v>373</v>
       </c>
@@ -36747,7 +36747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="60" hidden="1">
+    <row r="516" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="22" t="s">
         <v>389</v>
       </c>
@@ -36803,7 +36803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="60" hidden="1">
+    <row r="517" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="22" t="s">
         <v>470</v>
       </c>
@@ -36859,7 +36859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="60" hidden="1">
+    <row r="518" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="22" t="s">
         <v>473</v>
       </c>
@@ -36915,7 +36915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="60" hidden="1">
+    <row r="519" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="22" t="s">
         <v>475</v>
       </c>
@@ -36971,7 +36971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="60" hidden="1">
+    <row r="520" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="22" t="s">
         <v>477</v>
       </c>
@@ -37027,7 +37027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="60" hidden="1">
+    <row r="521" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="22" t="s">
         <v>480</v>
       </c>
@@ -37083,7 +37083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="60" hidden="1">
+    <row r="522" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="22" t="s">
         <v>483</v>
       </c>
@@ -37139,7 +37139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="60" hidden="1">
+    <row r="523" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="22" t="s">
         <v>486</v>
       </c>
@@ -37195,7 +37195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="345" hidden="1">
+    <row r="524" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="22" t="s">
         <v>636</v>
       </c>
@@ -37251,7 +37251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="345" hidden="1">
+    <row r="525" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="22" t="s">
         <v>640</v>
       </c>
@@ -37307,7 +37307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="345" hidden="1">
+    <row r="526" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="22" t="s">
         <v>643</v>
       </c>
@@ -37363,7 +37363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="345" hidden="1">
+    <row r="527" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="22" t="s">
         <v>644</v>
       </c>
@@ -37419,7 +37419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="345" hidden="1">
+    <row r="528" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="22" t="s">
         <v>647</v>
       </c>
@@ -37475,7 +37475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="345" hidden="1">
+    <row r="529" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="22" t="s">
         <v>649</v>
       </c>
@@ -37531,7 +37531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="345" hidden="1">
+    <row r="530" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="22" t="s">
         <v>652</v>
       </c>
@@ -37587,7 +37587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="345" hidden="1">
+    <row r="531" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="22" t="s">
         <v>655</v>
       </c>
@@ -37643,7 +37643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="345" hidden="1">
+    <row r="532" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="22" t="s">
         <v>658</v>
       </c>
@@ -37699,7 +37699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="345" hidden="1">
+    <row r="533" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="22" t="s">
         <v>660</v>
       </c>
@@ -37755,7 +37755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="345" hidden="1">
+    <row r="534" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="22" t="s">
         <v>662</v>
       </c>
@@ -37811,7 +37811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="345" hidden="1">
+    <row r="535" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="22" t="s">
         <v>664</v>
       </c>
@@ -37867,7 +37867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="135" hidden="1">
+    <row r="536" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="22" t="s">
         <v>695</v>
       </c>
@@ -37923,7 +37923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="135" hidden="1">
+    <row r="537" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="22" t="s">
         <v>698</v>
       </c>
@@ -37979,7 +37979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="150" hidden="1">
+    <row r="538" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="22" t="s">
         <v>736</v>
       </c>
@@ -38035,7 +38035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="150" hidden="1">
+    <row r="539" spans="1:18" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="22" t="s">
         <v>740</v>
       </c>
@@ -38091,7 +38091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="60" hidden="1">
+    <row r="540" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="22" t="s">
         <v>387</v>
       </c>
@@ -38147,7 +38147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="60" hidden="1">
+    <row r="541" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="22" t="s">
         <v>395</v>
       </c>
@@ -38203,7 +38203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="60" hidden="1">
+    <row r="542" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="22" t="s">
         <v>398</v>
       </c>
@@ -38259,7 +38259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="60" hidden="1">
+    <row r="543" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="22" t="s">
         <v>400</v>
       </c>
@@ -38315,7 +38315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="60" hidden="1">
+    <row r="544" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="22" t="s">
         <v>403</v>
       </c>
@@ -38371,7 +38371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="60" hidden="1">
+    <row r="545" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="22" t="s">
         <v>406</v>
       </c>
@@ -38427,7 +38427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="60" hidden="1">
+    <row r="546" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="22" t="s">
         <v>409</v>
       </c>
@@ -38483,7 +38483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="75" hidden="1">
+    <row r="547" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="22" t="s">
         <v>412</v>
       </c>
@@ -38539,7 +38539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="90" hidden="1">
+    <row r="548" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="22" t="s">
         <v>424</v>
       </c>
@@ -38595,7 +38595,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="90" hidden="1">
+    <row r="549" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="22" t="s">
         <v>429</v>
       </c>
@@ -38651,7 +38651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="60" hidden="1">
+    <row r="550" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="22" t="s">
         <v>452</v>
       </c>
@@ -38707,7 +38707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="60" hidden="1">
+    <row r="551" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="22" t="s">
         <v>455</v>
       </c>
@@ -38763,7 +38763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="330" hidden="1">
+    <row r="552" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="22" t="s">
         <v>188</v>
       </c>
@@ -38819,7 +38819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="60" hidden="1">
+    <row r="553" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="22" t="s">
         <v>332</v>
       </c>
@@ -38875,7 +38875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="60" hidden="1">
+    <row r="554" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="22" t="s">
         <v>337</v>
       </c>
@@ -38931,7 +38931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="60" hidden="1">
+    <row r="555" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="22" t="s">
         <v>365</v>
       </c>
@@ -38987,7 +38987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="556" spans="1:18" ht="60" hidden="1">
+    <row r="556" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="22" t="s">
         <v>368</v>
       </c>
@@ -39043,7 +39043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="60" hidden="1">
+    <row r="557" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="22" t="s">
         <v>371</v>
       </c>
@@ -39099,7 +39099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="60" hidden="1">
+    <row r="558" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="22" t="s">
         <v>375</v>
       </c>
@@ -39155,7 +39155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="60" hidden="1">
+    <row r="559" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="22" t="s">
         <v>377</v>
       </c>
@@ -39211,7 +39211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="60" hidden="1">
+    <row r="560" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="22" t="s">
         <v>380</v>
       </c>
@@ -39267,7 +39267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="60" hidden="1">
+    <row r="561" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="22" t="s">
         <v>383</v>
       </c>
@@ -39323,7 +39323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="60" hidden="1">
+    <row r="562" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="22" t="s">
         <v>385</v>
       </c>
@@ -39379,7 +39379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="60" hidden="1">
+    <row r="563" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="22" t="s">
         <v>392</v>
       </c>
@@ -39435,7 +39435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="60" hidden="1">
+    <row r="564" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="22" t="s">
         <v>326</v>
       </c>
@@ -39491,7 +39491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="60" hidden="1">
+    <row r="565" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="22" t="s">
         <v>330</v>
       </c>
@@ -39547,7 +39547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="60" hidden="1">
+    <row r="566" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="22" t="s">
         <v>322</v>
       </c>
@@ -39603,7 +39603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="60" hidden="1">
+    <row r="567" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="22" t="s">
         <v>328</v>
       </c>
@@ -39659,7 +39659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="60" hidden="1">
+    <row r="568" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="22" t="s">
         <v>334</v>
       </c>
@@ -39715,7 +39715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="60" hidden="1">
+    <row r="569" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="22" t="s">
         <v>340</v>
       </c>
@@ -39771,7 +39771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="75" hidden="1">
+    <row r="570" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="22" t="s">
         <v>105</v>
       </c>
@@ -39827,7 +39827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="75" hidden="1">
+    <row r="571" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="22" t="s">
         <v>118</v>
       </c>
@@ -39883,7 +39883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="75" hidden="1">
+    <row r="572" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="22" t="s">
         <v>131</v>
       </c>
@@ -39939,7 +39939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="75" hidden="1">
+    <row r="573" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="22" t="s">
         <v>165</v>
       </c>
@@ -39995,7 +39995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="330" hidden="1">
+    <row r="574" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="22" t="s">
         <v>178</v>
       </c>
@@ -40051,7 +40051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="330" hidden="1">
+    <row r="575" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="22" t="s">
         <v>180</v>
       </c>
@@ -40107,7 +40107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="330" hidden="1">
+    <row r="576" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="22" t="s">
         <v>198</v>
       </c>
@@ -40163,7 +40163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="330" hidden="1">
+    <row r="577" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="22" t="s">
         <v>200</v>
       </c>
@@ -40219,7 +40219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="75" hidden="1">
+    <row r="578" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="21" t="s">
         <v>18</v>
       </c>
@@ -40275,7 +40275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="75" hidden="1">
+    <row r="579" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="21" t="s">
         <v>33</v>
       </c>
@@ -40331,7 +40331,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="105" hidden="1">
+    <row r="580" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="21" t="s">
         <v>35</v>
       </c>
@@ -40387,7 +40387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="75" hidden="1">
+    <row r="581" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="21" t="s">
         <v>43</v>
       </c>
@@ -40443,7 +40443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="75" hidden="1">
+    <row r="582" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="21" t="s">
         <v>47</v>
       </c>
@@ -40499,7 +40499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="75" hidden="1">
+    <row r="583" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="21" t="s">
         <v>50</v>
       </c>
@@ -40555,7 +40555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="75" hidden="1">
+    <row r="584" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="22" t="s">
         <v>53</v>
       </c>
@@ -40611,7 +40611,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="75" hidden="1">
+    <row r="585" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="22" t="s">
         <v>55</v>
       </c>
@@ -40667,7 +40667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="75" hidden="1">
+    <row r="586" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="22" t="s">
         <v>57</v>
       </c>
@@ -40723,7 +40723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="75" hidden="1">
+    <row r="587" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="22" t="s">
         <v>59</v>
       </c>
@@ -40779,7 +40779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="75" hidden="1">
+    <row r="588" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="22" t="s">
         <v>61</v>
       </c>
@@ -40835,7 +40835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="75" hidden="1">
+    <row r="589" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="22" t="s">
         <v>66</v>
       </c>
@@ -40891,7 +40891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="75" hidden="1">
+    <row r="590" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="22" t="s">
         <v>68</v>
       </c>
@@ -40947,7 +40947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="195" hidden="1">
+    <row r="591" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="22" t="s">
         <v>71</v>
       </c>
@@ -41003,7 +41003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="195" hidden="1">
+    <row r="592" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="22" t="s">
         <v>75</v>
       </c>
@@ -41059,7 +41059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="195" hidden="1">
+    <row r="593" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="22" t="s">
         <v>77</v>
       </c>
@@ -41115,7 +41115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="195" hidden="1">
+    <row r="594" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="22" t="s">
         <v>80</v>
       </c>
@@ -41171,7 +41171,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="195" hidden="1">
+    <row r="595" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="22" t="s">
         <v>84</v>
       </c>
@@ -41227,7 +41227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="195" hidden="1">
+    <row r="596" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="22" t="s">
         <v>87</v>
       </c>
@@ -41283,7 +41283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="195" hidden="1">
+    <row r="597" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="22" t="s">
         <v>89</v>
       </c>
@@ -41339,7 +41339,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="195" hidden="1">
+    <row r="598" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="22" t="s">
         <v>91</v>
       </c>
@@ -41395,7 +41395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="195" hidden="1">
+    <row r="599" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="22" t="s">
         <v>93</v>
       </c>
@@ -41451,7 +41451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="195" hidden="1">
+    <row r="600" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="22" t="s">
         <v>95</v>
       </c>
@@ -41507,7 +41507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="195" hidden="1">
+    <row r="601" spans="1:18" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="22" t="s">
         <v>97</v>
       </c>
@@ -41563,7 +41563,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="75" hidden="1">
+    <row r="602" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="22" t="s">
         <v>108</v>
       </c>
@@ -41619,7 +41619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="75" hidden="1">
+    <row r="603" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="22" t="s">
         <v>110</v>
       </c>
@@ -41675,7 +41675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="75" hidden="1">
+    <row r="604" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="22" t="s">
         <v>112</v>
       </c>
@@ -41731,7 +41731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="75" hidden="1">
+    <row r="605" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="22" t="s">
         <v>114</v>
       </c>
@@ -41787,7 +41787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="606" spans="1:18" ht="75" hidden="1">
+    <row r="606" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="22" t="s">
         <v>116</v>
       </c>
@@ -41843,7 +41843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="75" hidden="1">
+    <row r="607" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="22" t="s">
         <v>120</v>
       </c>
@@ -41899,7 +41899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="75" hidden="1">
+    <row r="608" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="22" t="s">
         <v>125</v>
       </c>
@@ -41955,7 +41955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="75" hidden="1">
+    <row r="609" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="22" t="s">
         <v>127</v>
       </c>
@@ -42011,7 +42011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="75" hidden="1">
+    <row r="610" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="22" t="s">
         <v>137</v>
       </c>
@@ -42067,7 +42067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="75" hidden="1">
+    <row r="611" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="22" t="s">
         <v>139</v>
       </c>
@@ -42123,7 +42123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="75" hidden="1">
+    <row r="612" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="22" t="s">
         <v>141</v>
       </c>
@@ -42179,7 +42179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="75" hidden="1">
+    <row r="613" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="22" t="s">
         <v>143</v>
       </c>
@@ -42235,7 +42235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="75" hidden="1">
+    <row r="614" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="22" t="s">
         <v>145</v>
       </c>
@@ -42291,7 +42291,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="75" hidden="1">
+    <row r="615" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="22" t="s">
         <v>147</v>
       </c>
@@ -42347,7 +42347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="75" hidden="1">
+    <row r="616" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="22" t="s">
         <v>149</v>
       </c>
@@ -42403,7 +42403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="345" hidden="1">
+    <row r="617" spans="1:18" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="22" t="s">
         <v>153</v>
       </c>
@@ -42459,7 +42459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="135" hidden="1">
+    <row r="618" spans="1:18" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="22" t="s">
         <v>157</v>
       </c>
@@ -42515,7 +42515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="409.5" hidden="1">
+    <row r="619" spans="1:18" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="22" t="s">
         <v>161</v>
       </c>
@@ -42571,7 +42571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="75" hidden="1">
+    <row r="620" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="22" t="s">
         <v>168</v>
       </c>
@@ -42627,7 +42627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="75" hidden="1">
+    <row r="621" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="22" t="s">
         <v>170</v>
       </c>
@@ -42683,7 +42683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="75" hidden="1">
+    <row r="622" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="22" t="s">
         <v>173</v>
       </c>
@@ -42739,7 +42739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="330" hidden="1">
+    <row r="623" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="22" t="s">
         <v>175</v>
       </c>
@@ -42795,7 +42795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="330" hidden="1">
+    <row r="624" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="22" t="s">
         <v>182</v>
       </c>
@@ -42851,7 +42851,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="330" hidden="1">
+    <row r="625" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="22" t="s">
         <v>184</v>
       </c>
@@ -42907,7 +42907,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="330" hidden="1">
+    <row r="626" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="22" t="s">
         <v>186</v>
       </c>
@@ -42963,7 +42963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="330" hidden="1">
+    <row r="627" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="22" t="s">
         <v>192</v>
       </c>
@@ -43019,7 +43019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="330" hidden="1">
+    <row r="628" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="22" t="s">
         <v>194</v>
       </c>
@@ -43075,7 +43075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="629" spans="1:18" ht="330" hidden="1">
+    <row r="629" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="22" t="s">
         <v>201</v>
       </c>
@@ -43131,7 +43131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="630" spans="1:18" ht="330" hidden="1">
+    <row r="630" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="22" t="s">
         <v>203</v>
       </c>
@@ -43187,7 +43187,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="631" spans="1:18" ht="330" hidden="1">
+    <row r="631" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="22" t="s">
         <v>205</v>
       </c>
@@ -43243,7 +43243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="632" spans="1:18" ht="330" hidden="1">
+    <row r="632" spans="1:18" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="22" t="s">
         <v>207</v>
       </c>
@@ -43299,7 +43299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="633" spans="1:18" ht="60" hidden="1">
+    <row r="633" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="22" t="s">
         <v>209</v>
       </c>
@@ -43355,7 +43355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="634" spans="1:18" ht="60" hidden="1">
+    <row r="634" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="22" t="s">
         <v>216</v>
       </c>
@@ -43411,7 +43411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="635" spans="1:18" ht="60" hidden="1">
+    <row r="635" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="22" t="s">
         <v>217</v>
       </c>
@@ -43467,7 +43467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="636" spans="1:18" ht="60" hidden="1">
+    <row r="636" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="22" t="s">
         <v>218</v>
       </c>
@@ -43523,7 +43523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="637" spans="1:18" ht="60" hidden="1">
+    <row r="637" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="22" t="s">
         <v>233</v>
       </c>
@@ -43579,7 +43579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="638" spans="1:18" ht="60" hidden="1">
+    <row r="638" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="22" t="s">
         <v>235</v>
       </c>
@@ -43635,7 +43635,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="60" hidden="1">
+    <row r="639" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="22" t="s">
         <v>238</v>
       </c>
@@ -43691,7 +43691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="60" hidden="1">
+    <row r="640" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="22" t="s">
         <v>243</v>
       </c>
@@ -43747,7 +43747,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="641" spans="1:18" ht="60" hidden="1">
+    <row r="641" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="22" t="s">
         <v>246</v>
       </c>
@@ -43803,7 +43803,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="642" spans="1:18" ht="60" hidden="1">
+    <row r="642" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="22" t="s">
         <v>249</v>
       </c>
@@ -43859,7 +43859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="643" spans="1:18" ht="60" hidden="1">
+    <row r="643" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="22" t="s">
         <v>251</v>
       </c>
@@ -43915,7 +43915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="644" spans="1:18" ht="60" hidden="1">
+    <row r="644" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="22" t="s">
         <v>254</v>
       </c>
@@ -43971,7 +43971,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="645" spans="1:18" ht="60" hidden="1">
+    <row r="645" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="22" t="s">
         <v>255</v>
       </c>
@@ -44027,7 +44027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="646" spans="1:18" ht="60" hidden="1">
+    <row r="646" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="22" t="s">
         <v>257</v>
       </c>
@@ -44083,7 +44083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="647" spans="1:18" ht="60" hidden="1">
+    <row r="647" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="22" t="s">
         <v>259</v>
       </c>
@@ -44139,7 +44139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="648" spans="1:18" ht="60" hidden="1">
+    <row r="648" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="22" t="s">
         <v>261</v>
       </c>
@@ -44195,7 +44195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="649" spans="1:18" ht="60" hidden="1">
+    <row r="649" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="22" t="s">
         <v>265</v>
       </c>
@@ -44251,7 +44251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="650" spans="1:18" ht="60" hidden="1">
+    <row r="650" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="22" t="s">
         <v>268</v>
       </c>
@@ -44307,7 +44307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="651" spans="1:18" ht="75" hidden="1">
+    <row r="651" spans="1:18" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="22" t="s">
         <v>269</v>
       </c>
@@ -44363,7 +44363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="60" hidden="1">
+    <row r="652" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="22" t="s">
         <v>272</v>
       </c>
@@ -44419,7 +44419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="653" spans="1:18" ht="60" hidden="1">
+    <row r="653" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="22" t="s">
         <v>274</v>
       </c>
@@ -44475,7 +44475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="654" spans="1:18" ht="60" hidden="1">
+    <row r="654" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="22" t="s">
         <v>277</v>
       </c>
@@ -44531,7 +44531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="655" spans="1:18" ht="60" hidden="1">
+    <row r="655" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="22" t="s">
         <v>280</v>
       </c>
@@ -44587,7 +44587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="656" spans="1:18" ht="60" hidden="1">
+    <row r="656" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="22" t="s">
         <v>283</v>
       </c>
@@ -44643,7 +44643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="657" spans="1:18" ht="60" hidden="1">
+    <row r="657" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="22" t="s">
         <v>286</v>
       </c>
@@ -44699,7 +44699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="658" spans="1:18" ht="60" hidden="1">
+    <row r="658" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="22" t="s">
         <v>288</v>
       </c>
@@ -44755,7 +44755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="659" spans="1:18" ht="60" hidden="1">
+    <row r="659" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="22" t="s">
         <v>290</v>
       </c>
@@ -44811,7 +44811,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="660" spans="1:18" ht="60" hidden="1">
+    <row r="660" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="22" t="s">
         <v>293</v>
       </c>
@@ -44867,7 +44867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="661" spans="1:18" ht="105" hidden="1">
+    <row r="661" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="22" t="s">
         <v>295</v>
       </c>
@@ -44923,7 +44923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="662" spans="1:18" ht="105" hidden="1">
+    <row r="662" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="22" t="s">
         <v>297</v>
       </c>
@@ -44979,7 +44979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="663" spans="1:18" ht="105" hidden="1">
+    <row r="663" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="22" t="s">
         <v>300</v>
       </c>
@@ -45035,7 +45035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="664" spans="1:18" ht="105" hidden="1">
+    <row r="664" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="22" t="s">
         <v>303</v>
       </c>
@@ -45091,7 +45091,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="665" spans="1:18" ht="105" hidden="1">
+    <row r="665" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="22" t="s">
         <v>306</v>
       </c>
@@ -45147,7 +45147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="666" spans="1:18" ht="105" hidden="1">
+    <row r="666" spans="1:18" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="22" t="s">
         <v>309</v>
       </c>
@@ -45240,7 +45240,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -45250,7 +45250,7 @@
     <col min="6" max="6" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="105.75" customHeight="1">
+    <row r="3" spans="1:7" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="23" t="s">
         <v>1799</v>
       </c>
@@ -45260,7 +45260,7 @@
       <c r="F3" s="23"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1938</v>
       </c>
@@ -45281,7 +45281,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="22.5">
+    <row r="5" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -45302,7 +45302,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="22.5">
+    <row r="6" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -45323,7 +45323,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -45344,7 +45344,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -45365,7 +45365,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="22.5">
+    <row r="9" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -45407,7 +45407,7 @@
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" ht="22.5">
+    <row r="11" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -45428,7 +45428,7 @@
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -45449,7 +45449,7 @@
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>9</v>
       </c>
@@ -45470,7 +45470,7 @@
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="22.5">
+    <row r="14" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>10</v>
       </c>
@@ -45491,7 +45491,7 @@
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="22.5">
+    <row r="15" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>11</v>
       </c>
@@ -45512,7 +45512,7 @@
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>12</v>
       </c>
@@ -45533,7 +45533,7 @@
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" ht="22.5">
+    <row r="17" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>13</v>
       </c>
@@ -45554,7 +45554,7 @@
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" ht="22.5">
+    <row r="18" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>14</v>
       </c>
@@ -45575,7 +45575,7 @@
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>15</v>
       </c>
@@ -45596,7 +45596,7 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>16</v>
       </c>
@@ -45617,7 +45617,7 @@
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="22.5">
+    <row r="21" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>17</v>
       </c>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>18</v>
       </c>
@@ -45659,7 +45659,7 @@
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="22.5">
+    <row r="23" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -45680,7 +45680,7 @@
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="22.5">
+    <row r="24" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>20</v>
       </c>
@@ -45701,7 +45701,7 @@
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>21</v>
       </c>
@@ -45722,7 +45722,7 @@
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" ht="22.5">
+    <row r="26" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>22</v>
       </c>
@@ -45743,7 +45743,7 @@
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="22.5">
+    <row r="27" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>23</v>
       </c>
@@ -45764,7 +45764,7 @@
       </c>
       <c r="G27" s="7"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>24</v>
       </c>
@@ -45785,7 +45785,7 @@
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>25</v>
       </c>
@@ -45806,7 +45806,7 @@
       </c>
       <c r="G29" s="7"/>
     </row>
-    <row r="30" spans="1:7" ht="22.5">
+    <row r="30" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>26</v>
       </c>
@@ -45827,7 +45827,7 @@
       </c>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7" ht="22.5">
+    <row r="31" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>27</v>
       </c>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="G31" s="7"/>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="10" t="s">
         <v>1939</v>
       </c>
@@ -45862,7 +45862,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>1940</v>
       </c>
@@ -45876,7 +45876,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>1943</v>
       </c>
@@ -45890,7 +45890,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="30">
+    <row r="39" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>1945</v>
       </c>
@@ -45904,7 +45904,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
         <v>1496</v>
       </c>
@@ -45918,7 +45918,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>810</v>
       </c>
@@ -45932,7 +45932,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>1948</v>
       </c>
@@ -45946,7 +45946,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>1949</v>
       </c>
@@ -45960,7 +45960,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
         <v>663</v>
       </c>
@@ -45974,7 +45974,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>1950</v>
       </c>
@@ -45988,7 +45988,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
         <v>1951</v>
       </c>
@@ -46002,7 +46002,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>1836</v>
       </c>
@@ -46028,13 +46028,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="103.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>1954</v>
       </c>
@@ -46042,7 +46042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1958</v>
       </c>
@@ -46050,7 +46050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1956</v>
       </c>
@@ -46058,7 +46058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1955</v>
       </c>
@@ -46066,7 +46066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1957</v>
       </c>
@@ -46074,7 +46074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>1959</v>
       </c>
@@ -46082,7 +46082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>1960</v>
       </c>
@@ -46090,7 +46090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>1961</v>
       </c>
@@ -46098,7 +46098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>1962</v>
       </c>
@@ -46106,7 +46106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1963</v>
       </c>
@@ -46114,7 +46114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1964</v>
       </c>
@@ -46122,7 +46122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1965</v>
       </c>
@@ -46130,7 +46130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1966</v>
       </c>
@@ -46138,7 +46138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1967</v>
       </c>
@@ -46146,7 +46146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30">
+    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1968</v>
       </c>
@@ -46154,7 +46154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30">
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1969</v>
       </c>
@@ -46162,37 +46162,37 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>-1</v>
       </c>
